--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125374008</v>
+        <v>125373932</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>78194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809443</v>
+        <v>809662</v>
       </c>
       <c r="R3" t="n">
-        <v>7349560</v>
+        <v>7349760</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125374539</v>
+        <v>125374179</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>809604</v>
+        <v>809720</v>
       </c>
       <c r="R4" t="n">
-        <v>7349636</v>
+        <v>7349861</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125373986</v>
+        <v>125376406</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>79399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>809663</v>
+        <v>809747</v>
       </c>
       <c r="R5" t="n">
-        <v>7349767</v>
+        <v>7349847</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,28 +1065,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125374533</v>
+        <v>125374008</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1096,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>809958</v>
+        <v>809443</v>
       </c>
       <c r="R6" t="n">
-        <v>7350004</v>
+        <v>7349560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,19 +1174,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125374878</v>
+        <v>125374539</v>
       </c>
       <c r="B7" t="n">
         <v>92293</v>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>809856</v>
+        <v>809604</v>
       </c>
       <c r="R7" t="n">
-        <v>7349729</v>
+        <v>7349636</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1269,29 +1270,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125373932</v>
+        <v>125373986</v>
       </c>
       <c r="B8" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>809662</v>
+        <v>809663</v>
       </c>
       <c r="R8" t="n">
-        <v>7349760</v>
+        <v>7349767</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1378,22 +1378,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125374179</v>
+        <v>125374533</v>
       </c>
       <c r="B9" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>809720</v>
+        <v>809958</v>
       </c>
       <c r="R9" t="n">
-        <v>7349861</v>
+        <v>7350004</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,22 +1480,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125376406</v>
+        <v>125374878</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>92293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1504,25 +1504,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>809747</v>
+        <v>809856</v>
       </c>
       <c r="R10" t="n">
-        <v>7349847</v>
+        <v>7349729</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1583,12 +1583,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125373906</v>
+        <v>125374870</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>91172</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2639,25 +2639,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>809624</v>
+        <v>809852</v>
       </c>
       <c r="R21" t="n">
-        <v>7349838</v>
+        <v>7350051</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2717,22 +2717,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125374870</v>
+        <v>125374077</v>
       </c>
       <c r="B22" t="n">
-        <v>91172</v>
+        <v>92490</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2741,25 +2741,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>809852</v>
+        <v>809749</v>
       </c>
       <c r="R22" t="n">
-        <v>7350051</v>
+        <v>7349919</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2819,22 +2819,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125374077</v>
+        <v>125374104</v>
       </c>
       <c r="B23" t="n">
-        <v>92490</v>
+        <v>92293</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2843,25 +2843,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>809749</v>
+        <v>809676</v>
       </c>
       <c r="R23" t="n">
-        <v>7349919</v>
+        <v>7349681</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374104</v>
+        <v>125373973</v>
       </c>
       <c r="B24" t="n">
         <v>92293</v>
@@ -2973,13 +2973,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>809676</v>
+        <v>809732</v>
       </c>
       <c r="R24" t="n">
-        <v>7349681</v>
+        <v>7349587</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3023,19 +3023,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125373973</v>
+        <v>125374350</v>
       </c>
       <c r="B25" t="n">
         <v>92293</v>
@@ -3075,13 +3075,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>809732</v>
+        <v>809853</v>
       </c>
       <c r="R25" t="n">
-        <v>7349587</v>
+        <v>7349814</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3125,19 +3125,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374350</v>
+        <v>125373979</v>
       </c>
       <c r="B26" t="n">
         <v>92293</v>
@@ -3177,13 +3177,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>809853</v>
+        <v>809860</v>
       </c>
       <c r="R26" t="n">
-        <v>7349814</v>
+        <v>7350016</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3227,22 +3227,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125373979</v>
+        <v>125374178</v>
       </c>
       <c r="B27" t="n">
-        <v>92293</v>
+        <v>92321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3251,25 +3251,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>809860</v>
+        <v>809681</v>
       </c>
       <c r="R27" t="n">
-        <v>7350016</v>
+        <v>7349834</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3329,22 +3329,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374178</v>
+        <v>125374038</v>
       </c>
       <c r="B28" t="n">
-        <v>92321</v>
+        <v>78194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,21 +3357,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>809681</v>
+        <v>809896</v>
       </c>
       <c r="R28" t="n">
-        <v>7349834</v>
+        <v>7350047</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,22 +3431,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374038</v>
+        <v>125373906</v>
       </c>
       <c r="B29" t="n">
-        <v>78194</v>
+        <v>78547</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3459,21 +3459,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3483,13 +3483,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>809896</v>
+        <v>809624</v>
       </c>
       <c r="R29" t="n">
-        <v>7350047</v>
+        <v>7349838</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3533,12 +3533,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -7938,10 +7938,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125373969</v>
+        <v>125374903</v>
       </c>
       <c r="B73" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7950,25 +7950,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7978,13 +7978,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>809650</v>
+        <v>809752</v>
       </c>
       <c r="R73" t="n">
-        <v>7349697</v>
+        <v>7349680</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8028,22 +8028,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125374067</v>
+        <v>125374352</v>
       </c>
       <c r="B74" t="n">
-        <v>92321</v>
+        <v>92293</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8052,25 +8052,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>809743</v>
+        <v>809944</v>
       </c>
       <c r="R74" t="n">
-        <v>7349890</v>
+        <v>7349910</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8130,22 +8130,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374043</v>
+        <v>125374875</v>
       </c>
       <c r="B75" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8154,25 +8154,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8182,10 +8182,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>809396</v>
+        <v>809508</v>
       </c>
       <c r="R75" t="n">
-        <v>7349580</v>
+        <v>7349505</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8226,28 +8226,29 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125376417</v>
+        <v>125373967</v>
       </c>
       <c r="B76" t="n">
-        <v>78547</v>
+        <v>91172</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8256,25 +8257,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8284,13 +8285,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>809807</v>
+        <v>809639</v>
       </c>
       <c r="R76" t="n">
-        <v>7349660</v>
+        <v>7349650</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8328,29 +8329,28 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125374345</v>
+        <v>125374026</v>
       </c>
       <c r="B77" t="n">
-        <v>78547</v>
+        <v>78455</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8363,21 +8363,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8387,13 +8387,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>809504</v>
+        <v>809658</v>
       </c>
       <c r="R77" t="n">
-        <v>7349600</v>
+        <v>7349702</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8437,22 +8437,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125373967</v>
+        <v>125374527</v>
       </c>
       <c r="B78" t="n">
-        <v>91172</v>
+        <v>92490</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8461,25 +8461,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8489,13 +8489,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>809639</v>
+        <v>809621</v>
       </c>
       <c r="R78" t="n">
-        <v>7349650</v>
+        <v>7349643</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8539,22 +8539,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374026</v>
+        <v>125373969</v>
       </c>
       <c r="B79" t="n">
-        <v>78455</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8567,21 +8567,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8591,13 +8591,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>809658</v>
+        <v>809650</v>
       </c>
       <c r="R79" t="n">
-        <v>7349702</v>
+        <v>7349697</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8641,22 +8641,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374527</v>
+        <v>125374067</v>
       </c>
       <c r="B80" t="n">
-        <v>92490</v>
+        <v>92321</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8669,21 +8669,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8693,13 +8693,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>809621</v>
+        <v>809743</v>
       </c>
       <c r="R80" t="n">
-        <v>7349643</v>
+        <v>7349890</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8743,22 +8743,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125374903</v>
+        <v>125374043</v>
       </c>
       <c r="B81" t="n">
-        <v>92293</v>
+        <v>78194</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8767,25 +8767,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>809752</v>
+        <v>809396</v>
       </c>
       <c r="R81" t="n">
-        <v>7349680</v>
+        <v>7349580</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8845,22 +8845,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125374352</v>
+        <v>125376417</v>
       </c>
       <c r="B82" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8869,25 +8869,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>809944</v>
+        <v>809807</v>
       </c>
       <c r="R82" t="n">
-        <v>7349910</v>
+        <v>7349660</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8941,28 +8941,29 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125374875</v>
+        <v>125374345</v>
       </c>
       <c r="B83" t="n">
-        <v>92293</v>
+        <v>78547</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8971,25 +8972,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8999,13 +9000,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>809508</v>
+        <v>809504</v>
       </c>
       <c r="R83" t="n">
-        <v>7349505</v>
+        <v>7349600</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9043,19 +9044,18 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -13760,10 +13760,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125374066</v>
+        <v>125374182</v>
       </c>
       <c r="B130" t="n">
-        <v>56722</v>
+        <v>92293</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13776,21 +13776,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13800,13 +13800,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>809640</v>
+        <v>809522</v>
       </c>
       <c r="R130" t="n">
-        <v>7349862</v>
+        <v>7349734</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13836,11 +13836,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13855,22 +13850,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125373983</v>
+        <v>125374066</v>
       </c>
       <c r="B131" t="n">
-        <v>92293</v>
+        <v>56722</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13883,21 +13878,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13907,13 +13902,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>809717</v>
+        <v>809640</v>
       </c>
       <c r="R131" t="n">
-        <v>7349880</v>
+        <v>7349862</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13943,6 +13938,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13957,19 +13957,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125374534</v>
+        <v>125373983</v>
       </c>
       <c r="B132" t="n">
         <v>92293</v>
@@ -14009,13 +14009,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>809895</v>
+        <v>809717</v>
       </c>
       <c r="R132" t="n">
-        <v>7350016</v>
+        <v>7349880</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14059,19 +14059,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125374881</v>
+        <v>125374534</v>
       </c>
       <c r="B133" t="n">
         <v>92293</v>
@@ -14111,10 +14111,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>809888</v>
+        <v>809895</v>
       </c>
       <c r="R133" t="n">
-        <v>7349802</v>
+        <v>7350016</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14155,26 +14155,25 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125373915</v>
+        <v>125374881</v>
       </c>
       <c r="B134" t="n">
         <v>92293</v>
@@ -14214,13 +14213,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>809967</v>
+        <v>809888</v>
       </c>
       <c r="R134" t="n">
-        <v>7349981</v>
+        <v>7349802</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14258,25 +14257,26 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125374882</v>
+        <v>125373915</v>
       </c>
       <c r="B135" t="n">
         <v>92293</v>
@@ -14316,13 +14316,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>809951</v>
+        <v>809967</v>
       </c>
       <c r="R135" t="n">
-        <v>7349924</v>
+        <v>7349981</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14360,26 +14360,25 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125374182</v>
+        <v>125374882</v>
       </c>
       <c r="B136" t="n">
         <v>92293</v>
@@ -14419,10 +14418,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>809522</v>
+        <v>809951</v>
       </c>
       <c r="R136" t="n">
-        <v>7349734</v>
+        <v>7349924</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14463,28 +14462,29 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125374359</v>
+        <v>125373907</v>
       </c>
       <c r="B137" t="n">
-        <v>92293</v>
+        <v>91172</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14493,25 +14493,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14521,10 +14521,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>809597</v>
+        <v>809608</v>
       </c>
       <c r="R137" t="n">
-        <v>7349492</v>
+        <v>7349636</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -14571,22 +14571,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125374900</v>
+        <v>125374069</v>
       </c>
       <c r="B138" t="n">
-        <v>92293</v>
+        <v>92297</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14595,25 +14595,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14623,13 +14623,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>809462</v>
+        <v>809934</v>
       </c>
       <c r="R138" t="n">
-        <v>7349575</v>
+        <v>7349941</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14667,26 +14667,25 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125374027</v>
+        <v>125374359</v>
       </c>
       <c r="B139" t="n">
         <v>92293</v>
@@ -14726,13 +14725,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>809720</v>
+        <v>809597</v>
       </c>
       <c r="R139" t="n">
-        <v>7349576</v>
+        <v>7349492</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14776,19 +14775,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125374887</v>
+        <v>125374900</v>
       </c>
       <c r="B140" t="n">
         <v>92293</v>
@@ -14828,10 +14827,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>809704</v>
+        <v>809462</v>
       </c>
       <c r="R140" t="n">
-        <v>7349885</v>
+        <v>7349575</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14891,7 +14890,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125374184</v>
+        <v>125374027</v>
       </c>
       <c r="B141" t="n">
         <v>92293</v>
@@ -14931,10 +14930,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>809681</v>
+        <v>809720</v>
       </c>
       <c r="R141" t="n">
-        <v>7349834</v>
+        <v>7349576</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14981,22 +14980,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125374034</v>
+        <v>125374887</v>
       </c>
       <c r="B142" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15005,25 +15004,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15033,10 +15032,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>809797</v>
+        <v>809704</v>
       </c>
       <c r="R142" t="n">
-        <v>7349716</v>
+        <v>7349885</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15077,28 +15076,29 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125373907</v>
+        <v>125374184</v>
       </c>
       <c r="B143" t="n">
-        <v>91172</v>
+        <v>92293</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15107,25 +15107,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15135,13 +15135,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>809608</v>
+        <v>809681</v>
       </c>
       <c r="R143" t="n">
-        <v>7349636</v>
+        <v>7349834</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15185,22 +15185,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125374069</v>
+        <v>125374034</v>
       </c>
       <c r="B144" t="n">
-        <v>92297</v>
+        <v>78194</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15209,25 +15209,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15237,13 +15237,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>809934</v>
+        <v>809797</v>
       </c>
       <c r="R144" t="n">
-        <v>7349941</v>
+        <v>7349716</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15287,12 +15287,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -16319,10 +16319,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125374340</v>
+        <v>125374014</v>
       </c>
       <c r="B155" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16331,25 +16331,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16359,13 +16359,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>809945</v>
+        <v>809857</v>
       </c>
       <c r="R155" t="n">
-        <v>7349970</v>
+        <v>7349814</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16395,11 +16395,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16414,22 +16409,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125374014</v>
+        <v>125374340</v>
       </c>
       <c r="B156" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16438,25 +16433,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16466,13 +16461,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>809857</v>
+        <v>809945</v>
       </c>
       <c r="R156" t="n">
-        <v>7349814</v>
+        <v>7349970</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16502,6 +16497,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16516,12 +16516,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -21957,10 +21957,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125374035</v>
+        <v>125374019</v>
       </c>
       <c r="B210" t="n">
-        <v>78194</v>
+        <v>78546</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -21973,21 +21973,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21997,10 +21997,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>809860</v>
+        <v>809953</v>
       </c>
       <c r="R210" t="n">
-        <v>7349818</v>
+        <v>7349981</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22059,10 +22059,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125374891</v>
+        <v>125373997</v>
       </c>
       <c r="B211" t="n">
-        <v>92293</v>
+        <v>79428</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22071,25 +22071,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22099,10 +22099,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>809618</v>
+        <v>809858</v>
       </c>
       <c r="R211" t="n">
-        <v>7349662</v>
+        <v>7349814</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22143,26 +22143,25 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>125374899</v>
+        <v>125374891</v>
       </c>
       <c r="B212" t="n">
         <v>92293</v>
@@ -22202,10 +22201,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>809489</v>
+        <v>809618</v>
       </c>
       <c r="R212" t="n">
-        <v>7349545</v>
+        <v>7349662</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22265,10 +22264,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>125374036</v>
+        <v>125374899</v>
       </c>
       <c r="B213" t="n">
-        <v>78194</v>
+        <v>92293</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22277,25 +22276,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22305,10 +22304,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>809921</v>
+        <v>809489</v>
       </c>
       <c r="R213" t="n">
-        <v>7349943</v>
+        <v>7349545</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22349,28 +22348,29 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125374019</v>
+        <v>125374036</v>
       </c>
       <c r="B214" t="n">
-        <v>78546</v>
+        <v>78194</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22383,21 +22383,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22407,10 +22407,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>809953</v>
+        <v>809921</v>
       </c>
       <c r="R214" t="n">
-        <v>7349981</v>
+        <v>7349943</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22469,10 +22469,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>125373997</v>
+        <v>125374909</v>
       </c>
       <c r="B215" t="n">
-        <v>79428</v>
+        <v>78194</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22485,21 +22485,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22509,10 +22509,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>809858</v>
+        <v>809524</v>
       </c>
       <c r="R215" t="n">
-        <v>7349814</v>
+        <v>7349656</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22559,19 +22559,19 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>125374909</v>
+        <v>125373931</v>
       </c>
       <c r="B216" t="n">
         <v>78194</v>
@@ -22611,13 +22611,13 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>809524</v>
+        <v>809612</v>
       </c>
       <c r="R216" t="n">
-        <v>7349656</v>
+        <v>7349877</v>
       </c>
       <c r="S216" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -22661,19 +22661,19 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>125373931</v>
+        <v>125373929</v>
       </c>
       <c r="B217" t="n">
         <v>78194</v>
@@ -22713,10 +22713,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>809612</v>
+        <v>809911</v>
       </c>
       <c r="R217" t="n">
-        <v>7349877</v>
+        <v>7349897</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -22775,7 +22775,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>125373929</v>
+        <v>125374035</v>
       </c>
       <c r="B218" t="n">
         <v>78194</v>
@@ -22815,13 +22815,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>809911</v>
+        <v>809860</v>
       </c>
       <c r="R218" t="n">
-        <v>7349897</v>
+        <v>7349818</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -22865,12 +22865,12 @@
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -3951,10 +3951,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125374180</v>
+        <v>125374903</v>
       </c>
       <c r="B34" t="n">
-        <v>92646</v>
+        <v>92448</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3963,25 +3963,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3991,10 +3991,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>809528</v>
+        <v>809752</v>
       </c>
       <c r="R34" t="n">
-        <v>7349612</v>
+        <v>7349680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,19 +4041,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125373910</v>
+        <v>125374100</v>
       </c>
       <c r="B35" t="n">
         <v>92448</v>
@@ -4093,10 +4093,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>809589</v>
+        <v>809918</v>
       </c>
       <c r="R35" t="n">
-        <v>7349496</v>
+        <v>7350040</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4143,19 +4143,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125374903</v>
+        <v>125374532</v>
       </c>
       <c r="B36" t="n">
         <v>92448</v>
@@ -4195,10 +4195,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>809752</v>
+        <v>809812</v>
       </c>
       <c r="R36" t="n">
-        <v>7349680</v>
+        <v>7349817</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,19 +4245,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125374100</v>
+        <v>125374531</v>
       </c>
       <c r="B37" t="n">
         <v>92448</v>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>809918</v>
+        <v>809710</v>
       </c>
       <c r="R37" t="n">
-        <v>7350040</v>
+        <v>7349570</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4347,19 +4347,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125374532</v>
+        <v>125374541</v>
       </c>
       <c r="B38" t="n">
         <v>92448</v>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>809812</v>
+        <v>809384</v>
       </c>
       <c r="R38" t="n">
-        <v>7349817</v>
+        <v>7349553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125374531</v>
+        <v>125373989</v>
       </c>
       <c r="B39" t="n">
         <v>92448</v>
@@ -4501,13 +4501,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>809710</v>
+        <v>809653</v>
       </c>
       <c r="R39" t="n">
-        <v>7349570</v>
+        <v>7349741</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4551,19 +4551,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125374541</v>
+        <v>125374162</v>
       </c>
       <c r="B40" t="n">
         <v>92448</v>
@@ -4599,17 +4599,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>809384</v>
+        <v>809339</v>
       </c>
       <c r="R40" t="n">
-        <v>7349553</v>
+        <v>7349557</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4639,6 +4639,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4653,22 +4658,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125373989</v>
+        <v>125374178</v>
       </c>
       <c r="B41" t="n">
-        <v>92448</v>
+        <v>92476</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4677,25 +4682,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4705,13 +4710,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>809653</v>
+        <v>809681</v>
       </c>
       <c r="R41" t="n">
-        <v>7349741</v>
+        <v>7349834</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4755,22 +4760,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125374162</v>
+        <v>125374180</v>
       </c>
       <c r="B42" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4779,41 +4784,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>809339</v>
+        <v>809528</v>
       </c>
       <c r="R42" t="n">
-        <v>7349557</v>
+        <v>7349612</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4843,11 +4848,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4862,22 +4862,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374178</v>
+        <v>125373910</v>
       </c>
       <c r="B43" t="n">
-        <v>92476</v>
+        <v>92448</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4886,25 +4886,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4914,13 +4914,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809681</v>
+        <v>809589</v>
       </c>
       <c r="R43" t="n">
-        <v>7349834</v>
+        <v>7349496</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4964,12 +4964,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125374091</v>
+        <v>125374029</v>
       </c>
       <c r="B57" t="n">
-        <v>91326</v>
+        <v>92448</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6344,13 +6344,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>809370</v>
+        <v>809716</v>
       </c>
       <c r="R57" t="n">
-        <v>7349556</v>
+        <v>7349870</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6394,22 +6394,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125374549</v>
+        <v>125373927</v>
       </c>
       <c r="B58" t="n">
-        <v>91424</v>
+        <v>78331</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>809658</v>
+        <v>809878</v>
       </c>
       <c r="R58" t="n">
-        <v>7349719</v>
+        <v>7349722</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6496,22 +6496,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125374029</v>
+        <v>125373928</v>
       </c>
       <c r="B59" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6520,25 +6520,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6548,13 +6548,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>809716</v>
+        <v>809661</v>
       </c>
       <c r="R59" t="n">
-        <v>7349870</v>
+        <v>7349566</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6598,22 +6598,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125373927</v>
+        <v>125374857</v>
       </c>
       <c r="B60" t="n">
-        <v>78331</v>
+        <v>79565</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6626,21 +6626,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6650,13 +6650,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>809878</v>
+        <v>809522</v>
       </c>
       <c r="R60" t="n">
-        <v>7349722</v>
+        <v>7349656</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6700,22 +6700,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125373928</v>
+        <v>125374529</v>
       </c>
       <c r="B61" t="n">
-        <v>78331</v>
+        <v>78683</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>809661</v>
+        <v>809607</v>
       </c>
       <c r="R61" t="n">
-        <v>7349566</v>
+        <v>7349630</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6802,22 +6802,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125374857</v>
+        <v>125373972</v>
       </c>
       <c r="B62" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6826,25 +6826,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6854,13 +6854,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>809522</v>
+        <v>809675</v>
       </c>
       <c r="R62" t="n">
-        <v>7349656</v>
+        <v>7349554</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6904,22 +6904,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125374529</v>
+        <v>125374006</v>
       </c>
       <c r="B63" t="n">
-        <v>78683</v>
+        <v>79565</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6932,21 +6932,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>809607</v>
+        <v>809581</v>
       </c>
       <c r="R63" t="n">
-        <v>7349630</v>
+        <v>7349597</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7006,22 +7006,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125373972</v>
+        <v>125373996</v>
       </c>
       <c r="B64" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7030,25 +7030,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>809675</v>
+        <v>809856</v>
       </c>
       <c r="R64" t="n">
-        <v>7349554</v>
+        <v>7349815</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7108,22 +7108,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125374006</v>
+        <v>125374091</v>
       </c>
       <c r="B65" t="n">
-        <v>79565</v>
+        <v>91326</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7132,25 +7132,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>809581</v>
+        <v>809370</v>
       </c>
       <c r="R65" t="n">
-        <v>7349597</v>
+        <v>7349556</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7210,22 +7210,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125373996</v>
+        <v>125374549</v>
       </c>
       <c r="B66" t="n">
-        <v>79565</v>
+        <v>91424</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7234,25 +7234,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>809856</v>
+        <v>809658</v>
       </c>
       <c r="R66" t="n">
-        <v>7349815</v>
+        <v>7349719</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7312,12 +7312,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125373902</v>
+        <v>125376405</v>
       </c>
       <c r="B80" t="n">
-        <v>56836</v>
+        <v>79536</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8672,25 +8672,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>809943</v>
+        <v>809469</v>
       </c>
       <c r="R80" t="n">
-        <v>7349906</v>
+        <v>7349711</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8738,39 +8738,35 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125374536</v>
+        <v>125374015</v>
       </c>
       <c r="B81" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8779,25 +8775,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8807,10 +8803,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>809853</v>
+        <v>809442</v>
       </c>
       <c r="R81" t="n">
-        <v>7350024</v>
+        <v>7349562</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8857,22 +8853,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125374020</v>
+        <v>125373906</v>
       </c>
       <c r="B82" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8885,21 +8881,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8909,13 +8905,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>809655</v>
+        <v>809624</v>
       </c>
       <c r="R82" t="n">
-        <v>7349698</v>
+        <v>7349838</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8959,22 +8955,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125374540</v>
+        <v>125374026</v>
       </c>
       <c r="B83" t="n">
-        <v>92448</v>
+        <v>78592</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8983,25 +8979,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9011,10 +9007,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>809461</v>
+        <v>809658</v>
       </c>
       <c r="R83" t="n">
-        <v>7349612</v>
+        <v>7349702</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9061,22 +9057,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125373951</v>
+        <v>125373902</v>
       </c>
       <c r="B84" t="n">
-        <v>91131</v>
+        <v>56836</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9089,21 +9085,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9113,13 +9109,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>809524</v>
+        <v>809943</v>
       </c>
       <c r="R84" t="n">
-        <v>7349649</v>
+        <v>7349906</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9149,6 +9145,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9163,19 +9164,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125374886</v>
+        <v>125374536</v>
       </c>
       <c r="B85" t="n">
         <v>92448</v>
@@ -9215,10 +9216,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>809748</v>
+        <v>809853</v>
       </c>
       <c r="R85" t="n">
-        <v>7349938</v>
+        <v>7350024</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9259,29 +9260,28 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125374026</v>
+        <v>125374020</v>
       </c>
       <c r="B86" t="n">
-        <v>78592</v>
+        <v>78947</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9294,21 +9294,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>809658</v>
+        <v>809655</v>
       </c>
       <c r="R86" t="n">
-        <v>7349702</v>
+        <v>7349698</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125376405</v>
+        <v>125374540</v>
       </c>
       <c r="B87" t="n">
-        <v>79536</v>
+        <v>92448</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9392,25 +9392,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9420,13 +9420,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>809469</v>
+        <v>809461</v>
       </c>
       <c r="R87" t="n">
-        <v>7349711</v>
+        <v>7349612</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9464,29 +9464,28 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125374015</v>
+        <v>125373951</v>
       </c>
       <c r="B88" t="n">
-        <v>78684</v>
+        <v>91131</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9495,25 +9494,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9523,13 +9522,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>809442</v>
+        <v>809524</v>
       </c>
       <c r="R88" t="n">
-        <v>7349562</v>
+        <v>7349649</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9573,22 +9572,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125373906</v>
+        <v>125374886</v>
       </c>
       <c r="B89" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9597,25 +9596,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9625,13 +9624,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>809624</v>
+        <v>809748</v>
       </c>
       <c r="R89" t="n">
-        <v>7349838</v>
+        <v>7349938</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9669,18 +9668,19 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -12646,7 +12646,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125374905</v>
+        <v>125374107</v>
       </c>
       <c r="B119" t="n">
         <v>92448</v>
@@ -12686,13 +12686,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>809460</v>
+        <v>809651</v>
       </c>
       <c r="R119" t="n">
-        <v>7349561</v>
+        <v>7349687</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12736,22 +12736,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125374548</v>
+        <v>125373957</v>
       </c>
       <c r="B120" t="n">
-        <v>91180</v>
+        <v>92460</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12760,25 +12760,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1204</v>
+        <v>4366</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12788,13 +12788,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>809759</v>
+        <v>809729</v>
       </c>
       <c r="R120" t="n">
-        <v>7349927</v>
+        <v>7349968</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12838,19 +12838,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125374887</v>
+        <v>125374347</v>
       </c>
       <c r="B121" t="n">
         <v>92448</v>
@@ -12890,13 +12890,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>809704</v>
+        <v>809653</v>
       </c>
       <c r="R121" t="n">
-        <v>7349885</v>
+        <v>7349772</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12934,26 +12934,25 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125374107</v>
+        <v>125374349</v>
       </c>
       <c r="B122" t="n">
         <v>92448</v>
@@ -12993,10 +12992,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>809651</v>
+        <v>809624</v>
       </c>
       <c r="R122" t="n">
-        <v>7349687</v>
+        <v>7349547</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13043,22 +13042,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125373957</v>
+        <v>125373899</v>
       </c>
       <c r="B123" t="n">
-        <v>92460</v>
+        <v>79565</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13067,25 +13066,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13095,13 +13094,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>809729</v>
+        <v>809933</v>
       </c>
       <c r="R123" t="n">
-        <v>7349968</v>
+        <v>7349784</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13145,19 +13144,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125374347</v>
+        <v>125374355</v>
       </c>
       <c r="B124" t="n">
         <v>92448</v>
@@ -13197,10 +13196,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>809653</v>
+        <v>809646</v>
       </c>
       <c r="R124" t="n">
-        <v>7349772</v>
+        <v>7349691</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13259,7 +13258,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125374349</v>
+        <v>125374905</v>
       </c>
       <c r="B125" t="n">
         <v>92448</v>
@@ -13299,13 +13298,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>809624</v>
+        <v>809460</v>
       </c>
       <c r="R125" t="n">
-        <v>7349547</v>
+        <v>7349561</v>
       </c>
       <c r="S125" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13349,22 +13348,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125373899</v>
+        <v>125374548</v>
       </c>
       <c r="B126" t="n">
-        <v>79565</v>
+        <v>91180</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13377,21 +13376,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13401,13 +13400,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>809933</v>
+        <v>809759</v>
       </c>
       <c r="R126" t="n">
-        <v>7349784</v>
+        <v>7349927</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13451,19 +13450,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125374355</v>
+        <v>125374887</v>
       </c>
       <c r="B127" t="n">
         <v>92448</v>
@@ -13503,13 +13502,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>809646</v>
+        <v>809704</v>
       </c>
       <c r="R127" t="n">
-        <v>7349691</v>
+        <v>7349885</v>
       </c>
       <c r="S127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13547,18 +13546,19 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
@@ -14900,10 +14900,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125374157</v>
+        <v>125373930</v>
       </c>
       <c r="B141" t="n">
-        <v>92646</v>
+        <v>78331</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14916,37 +14916,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>809837</v>
+        <v>809731</v>
       </c>
       <c r="R141" t="n">
-        <v>7350018</v>
+        <v>7349926</v>
       </c>
       <c r="S141" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14990,22 +14990,22 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125374025</v>
+        <v>125376402</v>
       </c>
       <c r="B142" t="n">
-        <v>78592</v>
+        <v>79565</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15018,21 +15018,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15042,13 +15042,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>809718</v>
+        <v>809636</v>
       </c>
       <c r="R142" t="n">
-        <v>7349928</v>
+        <v>7349511</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15092,22 +15092,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125373912</v>
+        <v>125374032</v>
       </c>
       <c r="B143" t="n">
-        <v>92448</v>
+        <v>77874</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15116,25 +15116,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15144,13 +15144,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>809755</v>
+        <v>809628</v>
       </c>
       <c r="R143" t="n">
-        <v>7349675</v>
+        <v>7349657</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15194,22 +15194,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125376419</v>
+        <v>125374544</v>
       </c>
       <c r="B144" t="n">
-        <v>91424</v>
+        <v>78331</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15218,25 +15218,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>809843</v>
+        <v>809669</v>
       </c>
       <c r="R144" t="n">
-        <v>7349800</v>
+        <v>7349819</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15296,22 +15296,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125376407</v>
+        <v>125376404</v>
       </c>
       <c r="B145" t="n">
-        <v>79536</v>
+        <v>79565</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15324,21 +15324,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15348,10 +15348,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>809670</v>
+        <v>809804</v>
       </c>
       <c r="R145" t="n">
-        <v>7349836</v>
+        <v>7349794</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15392,7 +15392,6 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
@@ -15411,10 +15410,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125374014</v>
+        <v>125374035</v>
       </c>
       <c r="B146" t="n">
-        <v>78684</v>
+        <v>78331</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15427,21 +15426,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15451,10 +15450,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>809857</v>
+        <v>809860</v>
       </c>
       <c r="R146" t="n">
-        <v>7349814</v>
+        <v>7349818</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15513,10 +15512,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125373930</v>
+        <v>125374157</v>
       </c>
       <c r="B147" t="n">
-        <v>78331</v>
+        <v>92646</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15529,37 +15528,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>809731</v>
+        <v>809837</v>
       </c>
       <c r="R147" t="n">
-        <v>7349926</v>
+        <v>7350018</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15603,22 +15602,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125376402</v>
+        <v>125374025</v>
       </c>
       <c r="B148" t="n">
-        <v>79565</v>
+        <v>78592</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15631,21 +15630,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15655,13 +15654,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>809636</v>
+        <v>809718</v>
       </c>
       <c r="R148" t="n">
-        <v>7349511</v>
+        <v>7349928</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -15705,22 +15704,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125374032</v>
+        <v>125373912</v>
       </c>
       <c r="B149" t="n">
-        <v>77874</v>
+        <v>92448</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15729,25 +15728,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15757,13 +15756,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>809628</v>
+        <v>809755</v>
       </c>
       <c r="R149" t="n">
-        <v>7349657</v>
+        <v>7349675</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15807,22 +15806,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125374544</v>
+        <v>125376419</v>
       </c>
       <c r="B150" t="n">
-        <v>78331</v>
+        <v>91424</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15831,25 +15830,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15859,13 +15858,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>809669</v>
+        <v>809843</v>
       </c>
       <c r="R150" t="n">
-        <v>7349819</v>
+        <v>7349800</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15909,22 +15908,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125376404</v>
+        <v>125376407</v>
       </c>
       <c r="B151" t="n">
-        <v>79565</v>
+        <v>79536</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15937,21 +15936,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15961,10 +15960,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>809804</v>
+        <v>809670</v>
       </c>
       <c r="R151" t="n">
-        <v>7349794</v>
+        <v>7349836</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16005,6 +16004,7 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
@@ -16023,10 +16023,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125374035</v>
+        <v>125374014</v>
       </c>
       <c r="B152" t="n">
-        <v>78331</v>
+        <v>78684</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16039,21 +16039,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16063,10 +16063,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>809860</v>
+        <v>809857</v>
       </c>
       <c r="R152" t="n">
-        <v>7349818</v>
+        <v>7349814</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -19803,10 +19803,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125374066</v>
+        <v>125373909</v>
       </c>
       <c r="B189" t="n">
-        <v>56836</v>
+        <v>91424</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19815,25 +19815,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100138</v>
+        <v>65</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19843,10 +19843,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809640</v>
+        <v>809626</v>
       </c>
       <c r="R189" t="n">
-        <v>7349862</v>
+        <v>7349810</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -19881,11 +19881,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
@@ -19898,22 +19893,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125373909</v>
+        <v>125373960</v>
       </c>
       <c r="B190" t="n">
-        <v>91424</v>
+        <v>92646</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19922,25 +19917,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19950,13 +19945,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809626</v>
+        <v>809929</v>
       </c>
       <c r="R190" t="n">
-        <v>7349810</v>
+        <v>7349900</v>
       </c>
       <c r="S190" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20000,22 +19995,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125373960</v>
+        <v>125374066</v>
       </c>
       <c r="B191" t="n">
-        <v>92646</v>
+        <v>56836</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20024,25 +20019,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20052,13 +20047,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809929</v>
+        <v>809640</v>
       </c>
       <c r="R191" t="n">
-        <v>7349900</v>
+        <v>7349862</v>
       </c>
       <c r="S191" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20088,6 +20083,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20102,12 +20102,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -21442,10 +21442,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125374867</v>
+        <v>125374021</v>
       </c>
       <c r="B205" t="n">
-        <v>78684</v>
+        <v>78592</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21458,21 +21458,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21482,10 +21482,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>809521</v>
+        <v>809726</v>
       </c>
       <c r="R205" t="n">
-        <v>7349655</v>
+        <v>7349569</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21532,22 +21532,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>125374021</v>
+        <v>125374895</v>
       </c>
       <c r="B206" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21556,25 +21556,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21584,10 +21584,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>809726</v>
+        <v>809584</v>
       </c>
       <c r="R206" t="n">
-        <v>7349569</v>
+        <v>7349617</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21628,28 +21628,29 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>125374895</v>
+        <v>125374907</v>
       </c>
       <c r="B207" t="n">
-        <v>92448</v>
+        <v>92442</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21658,25 +21659,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21686,10 +21687,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>809584</v>
+        <v>809807</v>
       </c>
       <c r="R207" t="n">
-        <v>7349617</v>
+        <v>7349987</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21724,13 +21725,17 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD207" t="b">
         <v>0</v>
       </c>
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -21749,10 +21754,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>125374907</v>
+        <v>125374881</v>
       </c>
       <c r="B208" t="n">
-        <v>92442</v>
+        <v>92448</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21761,25 +21766,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21789,10 +21794,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>809807</v>
+        <v>809888</v>
       </c>
       <c r="R208" t="n">
-        <v>7349987</v>
+        <v>7349802</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21827,17 +21832,13 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -21856,10 +21857,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>125374881</v>
+        <v>125374867</v>
       </c>
       <c r="B209" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -21868,25 +21869,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21896,10 +21897,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>809888</v>
+        <v>809521</v>
       </c>
       <c r="R209" t="n">
-        <v>7349802</v>
+        <v>7349655</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21940,7 +21941,6 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -4577,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125376417</v>
+        <v>125376411</v>
       </c>
       <c r="B40" t="n">
-        <v>78684</v>
+        <v>92646</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4593,21 +4593,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>809807</v>
+        <v>809462</v>
       </c>
       <c r="R40" t="n">
-        <v>7349660</v>
+        <v>7349673</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4661,7 +4661,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4680,10 +4679,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125373906</v>
+        <v>125374180</v>
       </c>
       <c r="B41" t="n">
-        <v>78684</v>
+        <v>92646</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4696,21 +4695,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4720,13 +4719,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>809624</v>
+        <v>809528</v>
       </c>
       <c r="R41" t="n">
-        <v>7349838</v>
+        <v>7349612</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4770,22 +4769,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125376418</v>
+        <v>125374531</v>
       </c>
       <c r="B42" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4794,25 +4793,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4822,13 +4821,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>809811</v>
+        <v>809710</v>
       </c>
       <c r="R42" t="n">
-        <v>7349819</v>
+        <v>7349570</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4866,29 +4865,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125376411</v>
+        <v>125374885</v>
       </c>
       <c r="B43" t="n">
-        <v>92646</v>
+        <v>92448</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4897,25 +4895,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4925,13 +4923,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809462</v>
+        <v>809841</v>
       </c>
       <c r="R43" t="n">
-        <v>7349673</v>
+        <v>7350026</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4963,34 +4961,40 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374180</v>
+        <v>125374006</v>
       </c>
       <c r="B44" t="n">
-        <v>92646</v>
+        <v>79565</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5003,21 +5007,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5031,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809528</v>
+        <v>809581</v>
       </c>
       <c r="R44" t="n">
-        <v>7349612</v>
+        <v>7349597</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5077,22 +5081,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125374531</v>
+        <v>125373931</v>
       </c>
       <c r="B45" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5101,25 +5105,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5129,13 +5133,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809710</v>
+        <v>809612</v>
       </c>
       <c r="R45" t="n">
-        <v>7349570</v>
+        <v>7349877</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5179,19 +5183,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125374885</v>
+        <v>125373911</v>
       </c>
       <c r="B46" t="n">
         <v>92448</v>
@@ -5231,13 +5235,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809841</v>
+        <v>809707</v>
       </c>
       <c r="R46" t="n">
-        <v>7350026</v>
+        <v>7349576</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5269,40 +5273,34 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374006</v>
+        <v>125376417</v>
       </c>
       <c r="B47" t="n">
-        <v>79565</v>
+        <v>78684</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5315,21 +5313,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5339,13 +5337,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>809581</v>
+        <v>809807</v>
       </c>
       <c r="R47" t="n">
-        <v>7349597</v>
+        <v>7349660</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5383,28 +5381,29 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125373931</v>
+        <v>125373906</v>
       </c>
       <c r="B48" t="n">
-        <v>78331</v>
+        <v>78684</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5417,21 +5416,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5441,10 +5440,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809612</v>
+        <v>809624</v>
       </c>
       <c r="R48" t="n">
-        <v>7349877</v>
+        <v>7349838</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5503,10 +5502,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125373911</v>
+        <v>125376418</v>
       </c>
       <c r="B49" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5515,25 +5514,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5543,10 +5542,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>809707</v>
+        <v>809811</v>
       </c>
       <c r="R49" t="n">
-        <v>7349576</v>
+        <v>7349819</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5587,28 +5586,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125374160</v>
+        <v>125373909</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
+        <v>91424</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5617,41 +5617,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>809654</v>
+        <v>809626</v>
       </c>
       <c r="R50" t="n">
-        <v>7349767</v>
+        <v>7349810</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5695,22 +5695,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125373988</v>
+        <v>125373907</v>
       </c>
       <c r="B51" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5719,25 +5719,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5747,13 +5747,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>809651</v>
+        <v>809608</v>
       </c>
       <c r="R51" t="n">
-        <v>7349747</v>
+        <v>7349636</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5797,22 +5797,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125373933</v>
+        <v>125374024</v>
       </c>
       <c r="B52" t="n">
-        <v>78331</v>
+        <v>78592</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5825,21 +5825,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>809589</v>
+        <v>809741</v>
       </c>
       <c r="R52" t="n">
-        <v>7349641</v>
+        <v>7349907</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5899,22 +5899,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125374875</v>
+        <v>125374160</v>
       </c>
       <c r="B53" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5923,41 +5923,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>809508</v>
+        <v>809654</v>
       </c>
       <c r="R53" t="n">
-        <v>7349505</v>
+        <v>7349767</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5995,29 +5995,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125374175</v>
+        <v>125373988</v>
       </c>
       <c r="B54" t="n">
-        <v>92476</v>
+        <v>92448</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6026,25 +6025,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6054,13 +6053,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>809681</v>
+        <v>809651</v>
       </c>
       <c r="R54" t="n">
-        <v>7349834</v>
+        <v>7349747</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6104,22 +6103,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125373975</v>
+        <v>125373933</v>
       </c>
       <c r="B55" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6128,25 +6127,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6156,13 +6155,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>809751</v>
+        <v>809589</v>
       </c>
       <c r="R55" t="n">
-        <v>7349633</v>
+        <v>7349641</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6206,22 +6205,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125373909</v>
+        <v>125374875</v>
       </c>
       <c r="B56" t="n">
-        <v>91424</v>
+        <v>92448</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6230,25 +6229,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6258,13 +6257,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>809626</v>
+        <v>809508</v>
       </c>
       <c r="R56" t="n">
-        <v>7349810</v>
+        <v>7349505</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6302,28 +6301,29 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125373907</v>
+        <v>125374175</v>
       </c>
       <c r="B57" t="n">
-        <v>91326</v>
+        <v>92476</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6332,25 +6332,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6360,13 +6360,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>809608</v>
+        <v>809681</v>
       </c>
       <c r="R57" t="n">
-        <v>7349636</v>
+        <v>7349834</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6410,22 +6410,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125374024</v>
+        <v>125373975</v>
       </c>
       <c r="B58" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6434,25 +6434,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6462,13 +6462,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>809741</v>
+        <v>809751</v>
       </c>
       <c r="R58" t="n">
-        <v>7349907</v>
+        <v>7349633</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6512,12 +6512,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125373967</v>
+        <v>125374019</v>
       </c>
       <c r="B88" t="n">
-        <v>91326</v>
+        <v>78683</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9506,25 +9506,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9534,13 +9534,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>809639</v>
+        <v>809953</v>
       </c>
       <c r="R88" t="n">
-        <v>7349650</v>
+        <v>7349981</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9584,22 +9584,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125374077</v>
+        <v>125374020</v>
       </c>
       <c r="B89" t="n">
-        <v>92646</v>
+        <v>78947</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9612,21 +9612,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>809749</v>
+        <v>809655</v>
       </c>
       <c r="R89" t="n">
-        <v>7349919</v>
+        <v>7349698</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9686,22 +9686,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125374019</v>
+        <v>125373928</v>
       </c>
       <c r="B90" t="n">
-        <v>78683</v>
+        <v>78331</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9714,21 +9714,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>809953</v>
+        <v>809661</v>
       </c>
       <c r="R90" t="n">
-        <v>7349981</v>
+        <v>7349566</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9788,22 +9788,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125374020</v>
+        <v>125374551</v>
       </c>
       <c r="B91" t="n">
-        <v>78947</v>
+        <v>92448</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9812,25 +9812,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>809655</v>
+        <v>809661</v>
       </c>
       <c r="R91" t="n">
-        <v>7349698</v>
+        <v>7349714</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9890,22 +9890,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125373928</v>
+        <v>125373918</v>
       </c>
       <c r="B92" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9914,25 +9914,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>809661</v>
+        <v>809764</v>
       </c>
       <c r="R92" t="n">
-        <v>7349566</v>
+        <v>7349945</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125374551</v>
+        <v>125374882</v>
       </c>
       <c r="B93" t="n">
         <v>92448</v>
@@ -10044,10 +10044,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>809661</v>
+        <v>809951</v>
       </c>
       <c r="R93" t="n">
-        <v>7349714</v>
+        <v>7349924</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10088,28 +10088,29 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125373918</v>
+        <v>125373967</v>
       </c>
       <c r="B94" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10118,25 +10119,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10146,13 +10147,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>809764</v>
+        <v>809639</v>
       </c>
       <c r="R94" t="n">
-        <v>7349945</v>
+        <v>7349650</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10196,22 +10197,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125374882</v>
+        <v>125374077</v>
       </c>
       <c r="B95" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10220,25 +10221,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10248,13 +10249,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809951</v>
+        <v>809749</v>
       </c>
       <c r="R95" t="n">
-        <v>7349924</v>
+        <v>7349919</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10292,29 +10293,28 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374870</v>
+        <v>125374085</v>
       </c>
       <c r="B96" t="n">
-        <v>91326</v>
+        <v>78684</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10323,25 +10323,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10351,13 +10351,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809852</v>
+        <v>809652</v>
       </c>
       <c r="R96" t="n">
-        <v>7350051</v>
+        <v>7349686</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10401,22 +10401,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125376419</v>
+        <v>125374354</v>
       </c>
       <c r="B97" t="n">
-        <v>91424</v>
+        <v>92448</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10425,25 +10425,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809843</v>
+        <v>809669</v>
       </c>
       <c r="R97" t="n">
-        <v>7349800</v>
+        <v>7349770</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10503,22 +10503,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125374011</v>
+        <v>125373927</v>
       </c>
       <c r="B98" t="n">
-        <v>57632</v>
+        <v>78331</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10531,21 +10531,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10555,13 +10555,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809693</v>
+        <v>809878</v>
       </c>
       <c r="R98" t="n">
-        <v>7349989</v>
+        <v>7349722</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10605,22 +10605,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374085</v>
+        <v>125374028</v>
       </c>
       <c r="B99" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10629,25 +10629,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809652</v>
+        <v>809824</v>
       </c>
       <c r="R99" t="n">
-        <v>7349686</v>
+        <v>7349990</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10707,19 +10707,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125374354</v>
+        <v>125373921</v>
       </c>
       <c r="B100" t="n">
         <v>92448</v>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>809669</v>
+        <v>809595</v>
       </c>
       <c r="R100" t="n">
-        <v>7349770</v>
+        <v>7349628</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10809,22 +10809,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125373927</v>
+        <v>125374881</v>
       </c>
       <c r="B101" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10861,13 +10861,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>809878</v>
+        <v>809888</v>
       </c>
       <c r="R101" t="n">
-        <v>7349722</v>
+        <v>7349802</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10905,28 +10905,29 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125374028</v>
+        <v>125373954</v>
       </c>
       <c r="B102" t="n">
-        <v>92448</v>
+        <v>92460</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10939,21 +10940,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10963,13 +10964,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>809824</v>
+        <v>809809</v>
       </c>
       <c r="R102" t="n">
-        <v>7349990</v>
+        <v>7349982</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11013,19 +11014,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125373921</v>
+        <v>125374187</v>
       </c>
       <c r="B103" t="n">
         <v>92448</v>
@@ -11065,13 +11066,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>809595</v>
+        <v>809659</v>
       </c>
       <c r="R103" t="n">
-        <v>7349628</v>
+        <v>7349773</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11115,22 +11116,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125374881</v>
+        <v>125374870</v>
       </c>
       <c r="B104" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11139,25 +11140,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11167,10 +11168,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>809888</v>
+        <v>809852</v>
       </c>
       <c r="R104" t="n">
-        <v>7349802</v>
+        <v>7350051</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11211,7 +11212,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11230,10 +11230,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125373954</v>
+        <v>125376419</v>
       </c>
       <c r="B105" t="n">
-        <v>92460</v>
+        <v>91424</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11242,25 +11242,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4366</v>
+        <v>65</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11270,13 +11270,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>809809</v>
+        <v>809843</v>
       </c>
       <c r="R105" t="n">
-        <v>7349982</v>
+        <v>7349800</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11320,22 +11320,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125374187</v>
+        <v>125374011</v>
       </c>
       <c r="B106" t="n">
-        <v>92448</v>
+        <v>57632</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11344,25 +11344,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11372,10 +11372,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>809659</v>
+        <v>809693</v>
       </c>
       <c r="R106" t="n">
-        <v>7349773</v>
+        <v>7349989</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11422,22 +11422,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125374157</v>
+        <v>125374345</v>
       </c>
       <c r="B107" t="n">
-        <v>92646</v>
+        <v>78684</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11450,37 +11450,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>809837</v>
+        <v>809504</v>
       </c>
       <c r="R107" t="n">
-        <v>7350018</v>
+        <v>7349600</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11524,22 +11524,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125374872</v>
+        <v>125373930</v>
       </c>
       <c r="B108" t="n">
-        <v>91424</v>
+        <v>78331</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11548,25 +11548,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11576,13 +11576,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>809657</v>
+        <v>809731</v>
       </c>
       <c r="R108" t="n">
-        <v>7349679</v>
+        <v>7349926</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11626,22 +11626,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125374023</v>
+        <v>125374107</v>
       </c>
       <c r="B109" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11650,25 +11650,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11678,13 +11678,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>809936</v>
+        <v>809651</v>
       </c>
       <c r="R109" t="n">
-        <v>7349967</v>
+        <v>7349687</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11728,22 +11728,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125373930</v>
+        <v>125374029</v>
       </c>
       <c r="B110" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11752,25 +11752,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11780,13 +11780,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>809731</v>
+        <v>809716</v>
       </c>
       <c r="R110" t="n">
-        <v>7349926</v>
+        <v>7349870</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11830,22 +11830,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125374107</v>
+        <v>125374062</v>
       </c>
       <c r="B111" t="n">
-        <v>92448</v>
+        <v>91131</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11858,21 +11858,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11882,10 +11882,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>809651</v>
+        <v>809944</v>
       </c>
       <c r="R111" t="n">
-        <v>7349687</v>
+        <v>7349866</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11944,10 +11944,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125374029</v>
+        <v>125374008</v>
       </c>
       <c r="B112" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11956,25 +11956,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11984,10 +11984,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>809716</v>
+        <v>809443</v>
       </c>
       <c r="R112" t="n">
-        <v>7349870</v>
+        <v>7349560</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125374062</v>
+        <v>125374018</v>
       </c>
       <c r="B113" t="n">
-        <v>91131</v>
+        <v>78683</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12058,25 +12058,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12086,13 +12086,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>809944</v>
+        <v>809857</v>
       </c>
       <c r="R113" t="n">
-        <v>7349866</v>
+        <v>7349810</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12136,22 +12136,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125374008</v>
+        <v>125374179</v>
       </c>
       <c r="B114" t="n">
-        <v>79565</v>
+        <v>92476</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12164,21 +12164,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12188,10 +12188,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>809443</v>
+        <v>809720</v>
       </c>
       <c r="R114" t="n">
-        <v>7349560</v>
+        <v>7349861</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12238,22 +12238,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125374018</v>
+        <v>125373914</v>
       </c>
       <c r="B115" t="n">
-        <v>78683</v>
+        <v>92448</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12262,25 +12262,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12290,13 +12290,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>809857</v>
+        <v>809867</v>
       </c>
       <c r="R115" t="n">
-        <v>7349810</v>
+        <v>7349727</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12340,22 +12340,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125374179</v>
+        <v>125374157</v>
       </c>
       <c r="B116" t="n">
-        <v>92476</v>
+        <v>92646</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12368,37 +12368,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>809720</v>
+        <v>809837</v>
       </c>
       <c r="R116" t="n">
-        <v>7349861</v>
+        <v>7350018</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12442,22 +12442,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125373914</v>
+        <v>125374872</v>
       </c>
       <c r="B117" t="n">
-        <v>92448</v>
+        <v>91424</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12466,25 +12466,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12494,13 +12494,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>809867</v>
+        <v>809657</v>
       </c>
       <c r="R117" t="n">
-        <v>7349727</v>
+        <v>7349679</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12544,22 +12544,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125374345</v>
+        <v>125374023</v>
       </c>
       <c r="B118" t="n">
-        <v>78684</v>
+        <v>78592</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12572,21 +12572,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12596,13 +12596,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>809504</v>
+        <v>809936</v>
       </c>
       <c r="R118" t="n">
-        <v>7349600</v>
+        <v>7349967</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12646,12 +12646,12 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
@@ -17359,10 +17359,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125374902</v>
+        <v>125376422</v>
       </c>
       <c r="B165" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17371,25 +17371,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17399,13 +17399,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>809413</v>
+        <v>809622</v>
       </c>
       <c r="R165" t="n">
-        <v>7349595</v>
+        <v>7349883</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17443,29 +17443,28 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125374528</v>
+        <v>125374902</v>
       </c>
       <c r="B166" t="n">
-        <v>91393</v>
+        <v>92448</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17474,25 +17473,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5260</v>
+        <v>4364</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17502,10 +17501,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>809822</v>
+        <v>809413</v>
       </c>
       <c r="R166" t="n">
-        <v>7349799</v>
+        <v>7349595</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17546,28 +17545,29 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125374098</v>
+        <v>125374528</v>
       </c>
       <c r="B167" t="n">
-        <v>92448</v>
+        <v>91393</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17576,25 +17576,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4364</v>
+        <v>5260</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17604,13 +17604,13 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>809810</v>
+        <v>809822</v>
       </c>
       <c r="R167" t="n">
-        <v>7349749</v>
+        <v>7349799</v>
       </c>
       <c r="S167" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -17654,22 +17654,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125373932</v>
+        <v>125374098</v>
       </c>
       <c r="B168" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17678,25 +17678,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17706,10 +17706,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>809662</v>
+        <v>809810</v>
       </c>
       <c r="R168" t="n">
-        <v>7349760</v>
+        <v>7349749</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -17756,22 +17756,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125374540</v>
+        <v>125373932</v>
       </c>
       <c r="B169" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17780,25 +17780,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17808,13 +17808,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>809461</v>
+        <v>809662</v>
       </c>
       <c r="R169" t="n">
-        <v>7349612</v>
+        <v>7349760</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17858,22 +17858,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125374003</v>
+        <v>125374540</v>
       </c>
       <c r="B170" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17882,25 +17882,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17910,10 +17910,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>809619</v>
+        <v>809461</v>
       </c>
       <c r="R170" t="n">
-        <v>7349838</v>
+        <v>7349612</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17960,22 +17960,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125373982</v>
+        <v>125374003</v>
       </c>
       <c r="B171" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17984,25 +17984,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18012,13 +18012,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>809864</v>
+        <v>809619</v>
       </c>
       <c r="R171" t="n">
-        <v>7349953</v>
+        <v>7349838</v>
       </c>
       <c r="S171" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18062,22 +18062,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125374035</v>
+        <v>125373982</v>
       </c>
       <c r="B172" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18086,25 +18086,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18114,13 +18114,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>809860</v>
+        <v>809864</v>
       </c>
       <c r="R172" t="n">
-        <v>7349818</v>
+        <v>7349953</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18164,19 +18164,19 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>125376422</v>
+        <v>125374035</v>
       </c>
       <c r="B173" t="n">
         <v>78331</v>
@@ -18216,13 +18216,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>809622</v>
+        <v>809860</v>
       </c>
       <c r="R173" t="n">
-        <v>7349883</v>
+        <v>7349818</v>
       </c>
       <c r="S173" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18266,12 +18266,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -19401,10 +19401,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125376415</v>
+        <v>125374015</v>
       </c>
       <c r="B185" t="n">
-        <v>92646</v>
+        <v>78684</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19417,21 +19417,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19441,13 +19441,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>809522</v>
+        <v>809442</v>
       </c>
       <c r="R185" t="n">
-        <v>7349621</v>
+        <v>7349562</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -19485,29 +19485,28 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125374883</v>
+        <v>125376415</v>
       </c>
       <c r="B186" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19516,25 +19515,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19544,13 +19543,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>809960</v>
+        <v>809522</v>
       </c>
       <c r="R186" t="n">
-        <v>7349967</v>
+        <v>7349621</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19595,19 +19594,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125374352</v>
+        <v>125374883</v>
       </c>
       <c r="B187" t="n">
         <v>92448</v>
@@ -19647,13 +19646,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>809944</v>
+        <v>809960</v>
       </c>
       <c r="R187" t="n">
-        <v>7349910</v>
+        <v>7349967</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19691,25 +19690,26 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125374097</v>
+        <v>125374352</v>
       </c>
       <c r="B188" t="n">
         <v>92448</v>
@@ -19749,10 +19749,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809532</v>
+        <v>809944</v>
       </c>
       <c r="R188" t="n">
-        <v>7349513</v>
+        <v>7349910</v>
       </c>
       <c r="S188" t="n">
         <v>5</v>
@@ -19799,22 +19799,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125373899</v>
+        <v>125374097</v>
       </c>
       <c r="B189" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19823,25 +19823,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19851,10 +19851,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809933</v>
+        <v>809532</v>
       </c>
       <c r="R189" t="n">
-        <v>7349784</v>
+        <v>7349513</v>
       </c>
       <c r="S189" t="n">
         <v>5</v>
@@ -19901,19 +19901,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125374002</v>
+        <v>125373899</v>
       </c>
       <c r="B190" t="n">
         <v>79565</v>
@@ -19953,13 +19953,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809718</v>
+        <v>809933</v>
       </c>
       <c r="R190" t="n">
-        <v>7349928</v>
+        <v>7349784</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20003,19 +20003,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125374338</v>
+        <v>125374002</v>
       </c>
       <c r="B191" t="n">
         <v>79565</v>
@@ -20055,13 +20055,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809607</v>
+        <v>809718</v>
       </c>
       <c r="R191" t="n">
-        <v>7349621</v>
+        <v>7349928</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20105,22 +20105,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125374886</v>
+        <v>125374338</v>
       </c>
       <c r="B192" t="n">
-        <v>92448</v>
+        <v>79565</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20129,25 +20129,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20157,13 +20157,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809748</v>
+        <v>809607</v>
       </c>
       <c r="R192" t="n">
-        <v>7349938</v>
+        <v>7349621</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -20201,29 +20201,28 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125374043</v>
+        <v>125374886</v>
       </c>
       <c r="B193" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20232,25 +20231,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20260,10 +20259,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809396</v>
+        <v>809748</v>
       </c>
       <c r="R193" t="n">
-        <v>7349580</v>
+        <v>7349938</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20304,28 +20303,29 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125374355</v>
+        <v>125374043</v>
       </c>
       <c r="B194" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20334,25 +20334,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20362,13 +20362,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809646</v>
+        <v>809396</v>
       </c>
       <c r="R194" t="n">
-        <v>7349691</v>
+        <v>7349580</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -20412,19 +20412,19 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125374899</v>
+        <v>125374355</v>
       </c>
       <c r="B195" t="n">
         <v>92448</v>
@@ -20464,13 +20464,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>809489</v>
+        <v>809646</v>
       </c>
       <c r="R195" t="n">
-        <v>7349545</v>
+        <v>7349691</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -20508,29 +20508,28 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125374015</v>
+        <v>125374899</v>
       </c>
       <c r="B196" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20539,25 +20538,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20567,10 +20566,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>809442</v>
+        <v>809489</v>
       </c>
       <c r="R196" t="n">
-        <v>7349562</v>
+        <v>7349545</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20611,18 +20610,19 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -4577,10 +4577,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125376411</v>
+        <v>125376417</v>
       </c>
       <c r="B40" t="n">
-        <v>92646</v>
+        <v>78684</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4593,21 +4593,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>809462</v>
+        <v>809807</v>
       </c>
       <c r="R40" t="n">
-        <v>7349673</v>
+        <v>7349660</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4661,6 +4661,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4679,10 +4680,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125374180</v>
+        <v>125373906</v>
       </c>
       <c r="B41" t="n">
-        <v>92646</v>
+        <v>78684</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4695,21 +4696,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4719,13 +4720,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>809528</v>
+        <v>809624</v>
       </c>
       <c r="R41" t="n">
-        <v>7349612</v>
+        <v>7349838</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4769,22 +4770,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125374531</v>
+        <v>125376418</v>
       </c>
       <c r="B42" t="n">
-        <v>92448</v>
+        <v>78684</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4793,25 +4794,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4821,13 +4822,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>809710</v>
+        <v>809811</v>
       </c>
       <c r="R42" t="n">
-        <v>7349570</v>
+        <v>7349819</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4865,28 +4866,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374885</v>
+        <v>125376411</v>
       </c>
       <c r="B43" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4895,25 +4897,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4923,13 +4925,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809841</v>
+        <v>809462</v>
       </c>
       <c r="R43" t="n">
-        <v>7350026</v>
+        <v>7349673</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4961,40 +4963,34 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374006</v>
+        <v>125374180</v>
       </c>
       <c r="B44" t="n">
-        <v>79565</v>
+        <v>92646</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5007,21 +5003,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5031,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809581</v>
+        <v>809528</v>
       </c>
       <c r="R44" t="n">
-        <v>7349597</v>
+        <v>7349612</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5081,22 +5077,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125373931</v>
+        <v>125374531</v>
       </c>
       <c r="B45" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5105,25 +5101,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5133,13 +5129,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809612</v>
+        <v>809710</v>
       </c>
       <c r="R45" t="n">
-        <v>7349877</v>
+        <v>7349570</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5183,19 +5179,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125373911</v>
+        <v>125374885</v>
       </c>
       <c r="B46" t="n">
         <v>92448</v>
@@ -5235,13 +5231,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809707</v>
+        <v>809841</v>
       </c>
       <c r="R46" t="n">
-        <v>7349576</v>
+        <v>7350026</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5273,34 +5269,40 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125376417</v>
+        <v>125374006</v>
       </c>
       <c r="B47" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5313,21 +5315,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5337,13 +5339,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>809807</v>
+        <v>809581</v>
       </c>
       <c r="R47" t="n">
-        <v>7349660</v>
+        <v>7349597</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5381,29 +5383,28 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125373906</v>
+        <v>125373931</v>
       </c>
       <c r="B48" t="n">
-        <v>78684</v>
+        <v>78331</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5416,21 +5417,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5440,10 +5441,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809624</v>
+        <v>809612</v>
       </c>
       <c r="R48" t="n">
-        <v>7349838</v>
+        <v>7349877</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5502,10 +5503,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125376418</v>
+        <v>125373911</v>
       </c>
       <c r="B49" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5514,25 +5515,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5542,10 +5543,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>809811</v>
+        <v>809707</v>
       </c>
       <c r="R49" t="n">
-        <v>7349819</v>
+        <v>7349576</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5586,19 +5587,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -9494,10 +9494,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125374019</v>
+        <v>125373967</v>
       </c>
       <c r="B88" t="n">
-        <v>78683</v>
+        <v>91326</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9506,25 +9506,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9534,13 +9534,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>809953</v>
+        <v>809639</v>
       </c>
       <c r="R88" t="n">
-        <v>7349981</v>
+        <v>7349650</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9584,22 +9584,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125374020</v>
+        <v>125374077</v>
       </c>
       <c r="B89" t="n">
-        <v>78947</v>
+        <v>92646</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9612,21 +9612,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9636,13 +9636,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>809655</v>
+        <v>809749</v>
       </c>
       <c r="R89" t="n">
-        <v>7349698</v>
+        <v>7349919</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9686,22 +9686,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125373928</v>
+        <v>125374019</v>
       </c>
       <c r="B90" t="n">
-        <v>78331</v>
+        <v>78683</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9714,21 +9714,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9738,13 +9738,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>809661</v>
+        <v>809953</v>
       </c>
       <c r="R90" t="n">
-        <v>7349566</v>
+        <v>7349981</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9788,22 +9788,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125374551</v>
+        <v>125374020</v>
       </c>
       <c r="B91" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9812,25 +9812,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>809661</v>
+        <v>809655</v>
       </c>
       <c r="R91" t="n">
-        <v>7349714</v>
+        <v>7349698</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9890,22 +9890,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125373918</v>
+        <v>125373928</v>
       </c>
       <c r="B92" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9914,25 +9914,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9942,10 +9942,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>809764</v>
+        <v>809661</v>
       </c>
       <c r="R92" t="n">
-        <v>7349945</v>
+        <v>7349566</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10004,7 +10004,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125374882</v>
+        <v>125374551</v>
       </c>
       <c r="B93" t="n">
         <v>92448</v>
@@ -10044,10 +10044,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>809951</v>
+        <v>809661</v>
       </c>
       <c r="R93" t="n">
-        <v>7349924</v>
+        <v>7349714</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10088,29 +10088,28 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125373967</v>
+        <v>125373918</v>
       </c>
       <c r="B94" t="n">
-        <v>91326</v>
+        <v>92448</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10119,25 +10118,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10147,13 +10146,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>809639</v>
+        <v>809764</v>
       </c>
       <c r="R94" t="n">
-        <v>7349650</v>
+        <v>7349945</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10197,22 +10196,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125374077</v>
+        <v>125374882</v>
       </c>
       <c r="B95" t="n">
-        <v>92646</v>
+        <v>92448</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10221,25 +10220,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10249,13 +10248,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809749</v>
+        <v>809951</v>
       </c>
       <c r="R95" t="n">
-        <v>7349919</v>
+        <v>7349924</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10293,28 +10292,29 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374085</v>
+        <v>125374354</v>
       </c>
       <c r="B96" t="n">
-        <v>78684</v>
+        <v>92448</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10323,25 +10323,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10351,10 +10351,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809652</v>
+        <v>809669</v>
       </c>
       <c r="R96" t="n">
-        <v>7349686</v>
+        <v>7349770</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10401,22 +10401,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125374354</v>
+        <v>125373927</v>
       </c>
       <c r="B97" t="n">
-        <v>92448</v>
+        <v>78331</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10425,25 +10425,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10453,10 +10453,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809669</v>
+        <v>809878</v>
       </c>
       <c r="R97" t="n">
-        <v>7349770</v>
+        <v>7349722</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10503,22 +10503,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125373927</v>
+        <v>125374028</v>
       </c>
       <c r="B98" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10527,25 +10527,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10555,13 +10555,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809878</v>
+        <v>809824</v>
       </c>
       <c r="R98" t="n">
-        <v>7349722</v>
+        <v>7349990</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10605,19 +10605,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374028</v>
+        <v>125373921</v>
       </c>
       <c r="B99" t="n">
         <v>92448</v>
@@ -10657,13 +10657,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809824</v>
+        <v>809595</v>
       </c>
       <c r="R99" t="n">
-        <v>7349990</v>
+        <v>7349628</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10707,19 +10707,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125373921</v>
+        <v>125374881</v>
       </c>
       <c r="B100" t="n">
         <v>92448</v>
@@ -10759,13 +10759,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>809595</v>
+        <v>809888</v>
       </c>
       <c r="R100" t="n">
-        <v>7349628</v>
+        <v>7349802</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10803,28 +10803,29 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125374881</v>
+        <v>125373954</v>
       </c>
       <c r="B101" t="n">
-        <v>92448</v>
+        <v>92460</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10837,21 +10838,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10861,13 +10862,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>809888</v>
+        <v>809809</v>
       </c>
       <c r="R101" t="n">
-        <v>7349802</v>
+        <v>7349982</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10905,29 +10906,28 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125373954</v>
+        <v>125374187</v>
       </c>
       <c r="B102" t="n">
-        <v>92460</v>
+        <v>92448</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10940,21 +10940,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10964,13 +10964,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>809809</v>
+        <v>809659</v>
       </c>
       <c r="R102" t="n">
-        <v>7349982</v>
+        <v>7349773</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11014,22 +11014,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125374187</v>
+        <v>125374870</v>
       </c>
       <c r="B103" t="n">
-        <v>92448</v>
+        <v>91326</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11038,25 +11038,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11066,10 +11066,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>809659</v>
+        <v>809852</v>
       </c>
       <c r="R103" t="n">
-        <v>7349773</v>
+        <v>7350051</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11116,22 +11116,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125374870</v>
+        <v>125376419</v>
       </c>
       <c r="B104" t="n">
-        <v>91326</v>
+        <v>91424</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11144,21 +11144,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11168,13 +11168,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>809852</v>
+        <v>809843</v>
       </c>
       <c r="R104" t="n">
-        <v>7350051</v>
+        <v>7349800</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11218,22 +11218,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125376419</v>
+        <v>125374011</v>
       </c>
       <c r="B105" t="n">
-        <v>91424</v>
+        <v>57632</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11242,25 +11242,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>65</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11270,13 +11270,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>809843</v>
+        <v>809693</v>
       </c>
       <c r="R105" t="n">
-        <v>7349800</v>
+        <v>7349989</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11320,22 +11320,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125374011</v>
+        <v>125374085</v>
       </c>
       <c r="B106" t="n">
-        <v>57632</v>
+        <v>78684</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11348,21 +11348,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11372,13 +11372,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>809693</v>
+        <v>809652</v>
       </c>
       <c r="R106" t="n">
-        <v>7349989</v>
+        <v>7349686</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11422,12 +11422,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -13372,10 +13372,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125374343</v>
+        <v>125376402</v>
       </c>
       <c r="B126" t="n">
-        <v>92646</v>
+        <v>79565</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13388,21 +13388,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13412,10 +13412,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>809873</v>
+        <v>809636</v>
       </c>
       <c r="R126" t="n">
-        <v>7350014</v>
+        <v>7349511</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13462,22 +13462,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125374074</v>
+        <v>125373926</v>
       </c>
       <c r="B127" t="n">
-        <v>92646</v>
+        <v>92442</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13490,21 +13490,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13514,10 +13514,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>809849</v>
+        <v>809931</v>
       </c>
       <c r="R127" t="n">
-        <v>7349988</v>
+        <v>7349943</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13564,22 +13564,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125376402</v>
+        <v>125373978</v>
       </c>
       <c r="B128" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13588,25 +13588,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13616,13 +13616,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>809636</v>
+        <v>809758</v>
       </c>
       <c r="R128" t="n">
-        <v>7349511</v>
+        <v>7349662</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13666,22 +13666,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125373926</v>
+        <v>125374890</v>
       </c>
       <c r="B129" t="n">
-        <v>92442</v>
+        <v>92448</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13690,25 +13690,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13718,13 +13718,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>809931</v>
+        <v>809679</v>
       </c>
       <c r="R129" t="n">
-        <v>7349943</v>
+        <v>7349836</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13762,25 +13762,26 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125373978</v>
+        <v>125374359</v>
       </c>
       <c r="B130" t="n">
         <v>92448</v>
@@ -13820,13 +13821,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>809758</v>
+        <v>809597</v>
       </c>
       <c r="R130" t="n">
-        <v>7349662</v>
+        <v>7349492</v>
       </c>
       <c r="S130" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13870,19 +13871,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125374890</v>
+        <v>125374184</v>
       </c>
       <c r="B131" t="n">
         <v>92448</v>
@@ -13922,10 +13923,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>809679</v>
+        <v>809681</v>
       </c>
       <c r="R131" t="n">
-        <v>7349836</v>
+        <v>7349834</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13966,29 +13967,28 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125374359</v>
+        <v>125374343</v>
       </c>
       <c r="B132" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13997,25 +13997,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>809597</v>
+        <v>809873</v>
       </c>
       <c r="R132" t="n">
-        <v>7349492</v>
+        <v>7350014</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14087,10 +14087,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125374184</v>
+        <v>125374074</v>
       </c>
       <c r="B133" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14099,25 +14099,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14127,13 +14127,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>809681</v>
+        <v>809849</v>
       </c>
       <c r="R133" t="n">
-        <v>7349834</v>
+        <v>7349988</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14177,22 +14177,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125373952</v>
+        <v>125374025</v>
       </c>
       <c r="B134" t="n">
-        <v>56836</v>
+        <v>78592</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14201,25 +14201,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14229,13 +14229,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>809809</v>
+        <v>809718</v>
       </c>
       <c r="R134" t="n">
-        <v>7349755</v>
+        <v>7349928</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14265,11 +14265,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14284,22 +14279,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125374100</v>
+        <v>125374549</v>
       </c>
       <c r="B135" t="n">
-        <v>92448</v>
+        <v>91424</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14308,25 +14303,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14336,13 +14331,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>809918</v>
+        <v>809658</v>
       </c>
       <c r="R135" t="n">
-        <v>7350040</v>
+        <v>7349719</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14386,22 +14381,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125374532</v>
+        <v>125374161</v>
       </c>
       <c r="B136" t="n">
-        <v>92448</v>
+        <v>91424</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14410,41 +14405,41 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>809812</v>
+        <v>809457</v>
       </c>
       <c r="R136" t="n">
-        <v>7349817</v>
+        <v>7349587</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14488,22 +14483,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125374876</v>
+        <v>125376410</v>
       </c>
       <c r="B137" t="n">
-        <v>92448</v>
+        <v>92646</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14512,25 +14507,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14540,13 +14535,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>809605</v>
+        <v>809454</v>
       </c>
       <c r="R137" t="n">
-        <v>7349541</v>
+        <v>7349679</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14584,29 +14579,28 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125374536</v>
+        <v>125373952</v>
       </c>
       <c r="B138" t="n">
-        <v>92448</v>
+        <v>56836</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14619,21 +14613,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14643,13 +14637,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>809853</v>
+        <v>809809</v>
       </c>
       <c r="R138" t="n">
-        <v>7350024</v>
+        <v>7349755</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14679,6 +14673,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14693,19 +14692,19 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125374894</v>
+        <v>125374100</v>
       </c>
       <c r="B139" t="n">
         <v>92448</v>
@@ -14745,13 +14744,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>809639</v>
+        <v>809918</v>
       </c>
       <c r="R139" t="n">
-        <v>7349668</v>
+        <v>7350040</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14789,26 +14788,25 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125373912</v>
+        <v>125374532</v>
       </c>
       <c r="B140" t="n">
         <v>92448</v>
@@ -14848,13 +14846,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>809755</v>
+        <v>809812</v>
       </c>
       <c r="R140" t="n">
-        <v>7349675</v>
+        <v>7349817</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14898,19 +14896,19 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125374895</v>
+        <v>125374876</v>
       </c>
       <c r="B141" t="n">
         <v>92448</v>
@@ -14950,10 +14948,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>809584</v>
+        <v>809605</v>
       </c>
       <c r="R141" t="n">
-        <v>7349617</v>
+        <v>7349541</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15013,10 +15011,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125376403</v>
+        <v>125374536</v>
       </c>
       <c r="B142" t="n">
-        <v>79565</v>
+        <v>92448</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15025,25 +15023,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15053,13 +15051,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>809861</v>
+        <v>809853</v>
       </c>
       <c r="R142" t="n">
-        <v>7349763</v>
+        <v>7350024</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15103,22 +15101,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125374067</v>
+        <v>125374894</v>
       </c>
       <c r="B143" t="n">
-        <v>92476</v>
+        <v>92448</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15127,25 +15125,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15155,13 +15153,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>809743</v>
+        <v>809639</v>
       </c>
       <c r="R143" t="n">
-        <v>7349890</v>
+        <v>7349668</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15199,25 +15197,26 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125374534</v>
+        <v>125373912</v>
       </c>
       <c r="B144" t="n">
         <v>92448</v>
@@ -15257,13 +15256,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>809895</v>
+        <v>809755</v>
       </c>
       <c r="R144" t="n">
-        <v>7350016</v>
+        <v>7349675</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15307,22 +15306,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125374038</v>
+        <v>125374895</v>
       </c>
       <c r="B145" t="n">
-        <v>78331</v>
+        <v>92448</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15331,25 +15330,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15359,10 +15358,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>809896</v>
+        <v>809584</v>
       </c>
       <c r="R145" t="n">
-        <v>7350047</v>
+        <v>7349617</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15403,28 +15402,29 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125374089</v>
+        <v>125376403</v>
       </c>
       <c r="B146" t="n">
-        <v>78683</v>
+        <v>79565</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15437,21 +15437,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15461,10 +15461,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>809956</v>
+        <v>809861</v>
       </c>
       <c r="R146" t="n">
-        <v>7349827</v>
+        <v>7349763</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15511,22 +15511,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125374865</v>
+        <v>125374067</v>
       </c>
       <c r="B147" t="n">
-        <v>78684</v>
+        <v>92476</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15539,21 +15539,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15563,13 +15563,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>809649</v>
+        <v>809743</v>
       </c>
       <c r="R147" t="n">
-        <v>7349705</v>
+        <v>7349890</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15613,22 +15613,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125374025</v>
+        <v>125374534</v>
       </c>
       <c r="B148" t="n">
-        <v>78592</v>
+        <v>92448</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15637,25 +15637,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15665,10 +15665,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>809718</v>
+        <v>809895</v>
       </c>
       <c r="R148" t="n">
-        <v>7349928</v>
+        <v>7350016</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15715,22 +15715,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125374549</v>
+        <v>125374038</v>
       </c>
       <c r="B149" t="n">
-        <v>91424</v>
+        <v>78331</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15739,25 +15739,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15767,10 +15767,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>809658</v>
+        <v>809896</v>
       </c>
       <c r="R149" t="n">
-        <v>7349719</v>
+        <v>7350047</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15817,22 +15817,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125374161</v>
+        <v>125374089</v>
       </c>
       <c r="B150" t="n">
-        <v>91424</v>
+        <v>78683</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15841,41 +15841,41 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>65</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>809457</v>
+        <v>809956</v>
       </c>
       <c r="R150" t="n">
-        <v>7349587</v>
+        <v>7349827</v>
       </c>
       <c r="S150" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15919,22 +15919,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125376410</v>
+        <v>125374865</v>
       </c>
       <c r="B151" t="n">
-        <v>92646</v>
+        <v>78684</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15947,21 +15947,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15971,13 +15971,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>809454</v>
+        <v>809649</v>
       </c>
       <c r="R151" t="n">
-        <v>7349679</v>
+        <v>7349705</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16021,12 +16021,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125373921</v>
+        <v>125374176</v>
       </c>
       <c r="B2" t="n">
-        <v>92502</v>
+        <v>92530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>809595</v>
+        <v>809664</v>
       </c>
       <c r="R2" t="n">
-        <v>7349628</v>
+        <v>7349826</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125374896</v>
+        <v>125373932</v>
       </c>
       <c r="B3" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>809526</v>
+        <v>809662</v>
       </c>
       <c r="R3" t="n">
-        <v>7349618</v>
+        <v>7349760</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,19 +851,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1161,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125374176</v>
+        <v>125373921</v>
       </c>
       <c r="B7" t="n">
-        <v>92530</v>
+        <v>92502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>809664</v>
+        <v>809595</v>
       </c>
       <c r="R7" t="n">
-        <v>7349826</v>
+        <v>7349628</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1246,44 +1245,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125373932</v>
+        <v>125374896</v>
       </c>
       <c r="B8" t="n">
-        <v>78373</v>
+        <v>92502</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,13 +1292,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>809662</v>
+        <v>809526</v>
       </c>
       <c r="R8" t="n">
-        <v>7349760</v>
+        <v>7349618</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1337,18 +1336,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2819,32 +2819,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374347</v>
+        <v>125374022</v>
       </c>
       <c r="B24" t="n">
-        <v>92502</v>
+        <v>78634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>809653</v>
+        <v>809927</v>
       </c>
       <c r="R24" t="n">
-        <v>7349772</v>
+        <v>7349959</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,44 +2904,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125373973</v>
+        <v>125374548</v>
       </c>
       <c r="B25" t="n">
-        <v>92502</v>
+        <v>91234</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>809732</v>
+        <v>809759</v>
       </c>
       <c r="R25" t="n">
-        <v>7349587</v>
+        <v>7349927</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,44 +3001,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125373910</v>
+        <v>125376408</v>
       </c>
       <c r="B26" t="n">
-        <v>92502</v>
+        <v>90258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>809589</v>
+        <v>809843</v>
       </c>
       <c r="R26" t="n">
-        <v>7349496</v>
+        <v>7349800</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3098,22 +3098,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125376417</v>
+        <v>125374032</v>
       </c>
       <c r="B27" t="n">
-        <v>78726</v>
+        <v>77916</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>809807</v>
+        <v>809628</v>
       </c>
       <c r="R27" t="n">
-        <v>7349660</v>
+        <v>7349657</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3189,29 +3189,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374022</v>
+        <v>125374041</v>
       </c>
       <c r="B28" t="n">
-        <v>78634</v>
+        <v>78373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3219,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3243,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>809927</v>
+        <v>809655</v>
       </c>
       <c r="R28" t="n">
-        <v>7349959</v>
+        <v>7349694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3305,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374548</v>
+        <v>125374347</v>
       </c>
       <c r="B29" t="n">
-        <v>91234</v>
+        <v>92502</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3340,13 +3339,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>809759</v>
+        <v>809653</v>
       </c>
       <c r="R29" t="n">
-        <v>7349927</v>
+        <v>7349772</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3390,44 +3389,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125376408</v>
+        <v>125373973</v>
       </c>
       <c r="B30" t="n">
-        <v>90258</v>
+        <v>92502</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3437,13 +3436,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>809843</v>
+        <v>809732</v>
       </c>
       <c r="R30" t="n">
-        <v>7349800</v>
+        <v>7349587</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3487,44 +3486,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374032</v>
+        <v>125373910</v>
       </c>
       <c r="B31" t="n">
-        <v>77916</v>
+        <v>92502</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,13 +3533,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>809628</v>
+        <v>809589</v>
       </c>
       <c r="R31" t="n">
-        <v>7349657</v>
+        <v>7349496</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3584,22 +3583,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125374041</v>
+        <v>125376417</v>
       </c>
       <c r="B32" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,21 +3606,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,13 +3630,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>809655</v>
+        <v>809807</v>
       </c>
       <c r="R32" t="n">
-        <v>7349694</v>
+        <v>7349660</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3675,28 +3674,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125374545</v>
+        <v>125374016</v>
       </c>
       <c r="B33" t="n">
-        <v>78373</v>
+        <v>80942</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>809621</v>
+        <v>809629</v>
       </c>
       <c r="R33" t="n">
-        <v>7349643</v>
+        <v>7349656</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3778,44 +3778,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125373951</v>
+        <v>125374015</v>
       </c>
       <c r="B34" t="n">
-        <v>91185</v>
+        <v>78726</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3825,13 +3825,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>809524</v>
+        <v>809442</v>
       </c>
       <c r="R34" t="n">
-        <v>7349649</v>
+        <v>7349562</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3875,22 +3875,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125374035</v>
+        <v>125373905</v>
       </c>
       <c r="B35" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3898,21 +3898,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>809860</v>
+        <v>809845</v>
       </c>
       <c r="R35" t="n">
-        <v>7349818</v>
+        <v>7350064</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3972,22 +3972,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125374015</v>
+        <v>125373926</v>
       </c>
       <c r="B36" t="n">
-        <v>78726</v>
+        <v>92496</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3995,21 +3995,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4019,13 +4019,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>809442</v>
+        <v>809931</v>
       </c>
       <c r="R36" t="n">
-        <v>7349562</v>
+        <v>7349943</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4069,44 +4069,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125373905</v>
+        <v>125374538</v>
       </c>
       <c r="B37" t="n">
-        <v>78726</v>
+        <v>92502</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>809845</v>
+        <v>809697</v>
       </c>
       <c r="R37" t="n">
-        <v>7350064</v>
+        <v>7349868</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4166,44 +4166,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125374016</v>
+        <v>125373919</v>
       </c>
       <c r="B38" t="n">
-        <v>80942</v>
+        <v>92502</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>809629</v>
+        <v>809646</v>
       </c>
       <c r="R38" t="n">
-        <v>7349656</v>
+        <v>7349688</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4263,44 +4263,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125373926</v>
+        <v>125373979</v>
       </c>
       <c r="B39" t="n">
-        <v>92496</v>
+        <v>92502</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4310,13 +4310,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>809931</v>
+        <v>809860</v>
       </c>
       <c r="R39" t="n">
-        <v>7349943</v>
+        <v>7350016</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4360,44 +4360,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125374538</v>
+        <v>125374545</v>
       </c>
       <c r="B40" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>809697</v>
+        <v>809621</v>
       </c>
       <c r="R40" t="n">
-        <v>7349868</v>
+        <v>7349643</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125373919</v>
+        <v>125373951</v>
       </c>
       <c r="B41" t="n">
-        <v>92502</v>
+        <v>91185</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4480,21 +4480,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4504,13 +4504,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>809646</v>
+        <v>809524</v>
       </c>
       <c r="R41" t="n">
-        <v>7349688</v>
+        <v>7349649</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4554,44 +4554,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125373979</v>
+        <v>125374035</v>
       </c>
       <c r="B42" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4604,10 +4604,10 @@
         <v>809860</v>
       </c>
       <c r="R42" t="n">
-        <v>7350016</v>
+        <v>7349818</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4651,12 +4651,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -6706,32 +6706,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125374069</v>
+        <v>125376418</v>
       </c>
       <c r="B64" t="n">
-        <v>92506</v>
+        <v>78726</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4365</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6741,10 +6741,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>809934</v>
+        <v>809811</v>
       </c>
       <c r="R64" t="n">
-        <v>7349941</v>
+        <v>7349819</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6785,50 +6785,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125373957</v>
+        <v>125374025</v>
       </c>
       <c r="B65" t="n">
-        <v>92514</v>
+        <v>78634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4366</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6838,13 +6839,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>809729</v>
+        <v>809718</v>
       </c>
       <c r="R65" t="n">
-        <v>7349968</v>
+        <v>7349928</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6888,44 +6889,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125374899</v>
+        <v>125374338</v>
       </c>
       <c r="B66" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6935,13 +6936,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>809489</v>
+        <v>809607</v>
       </c>
       <c r="R66" t="n">
-        <v>7349545</v>
+        <v>7349621</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6979,51 +6980,50 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125376418</v>
+        <v>125374069</v>
       </c>
       <c r="B67" t="n">
-        <v>78726</v>
+        <v>92506</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>4365</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>809811</v>
+        <v>809934</v>
       </c>
       <c r="R67" t="n">
-        <v>7349819</v>
+        <v>7349941</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7077,51 +7077,50 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125374025</v>
+        <v>125373957</v>
       </c>
       <c r="B68" t="n">
-        <v>78634</v>
+        <v>92514</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>4366</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7131,13 +7130,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>809718</v>
+        <v>809729</v>
       </c>
       <c r="R68" t="n">
-        <v>7349928</v>
+        <v>7349968</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7181,44 +7180,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125374338</v>
+        <v>125374899</v>
       </c>
       <c r="B69" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7228,13 +7227,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>809607</v>
+        <v>809489</v>
       </c>
       <c r="R69" t="n">
-        <v>7349621</v>
+        <v>7349545</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7272,18 +7271,19 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125374072</v>
+        <v>125374856</v>
       </c>
       <c r="B74" t="n">
-        <v>92700</v>
+        <v>79585</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7689,21 +7689,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7713,13 +7713,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>809857</v>
+        <v>809648</v>
       </c>
       <c r="R74" t="n">
-        <v>7350013</v>
+        <v>7349702</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7763,22 +7763,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374077</v>
+        <v>125374007</v>
       </c>
       <c r="B75" t="n">
-        <v>92700</v>
+        <v>79585</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7810,13 +7810,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>809749</v>
+        <v>809505</v>
       </c>
       <c r="R75" t="n">
-        <v>7349919</v>
+        <v>7349593</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7860,22 +7860,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125374024</v>
+        <v>125376400</v>
       </c>
       <c r="B76" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7883,21 +7883,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7907,13 +7907,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>809741</v>
+        <v>809484</v>
       </c>
       <c r="R76" t="n">
-        <v>7349907</v>
+        <v>7349700</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7957,44 +7957,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125376415</v>
+        <v>125374186</v>
       </c>
       <c r="B77" t="n">
-        <v>92700</v>
+        <v>92502</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8004,13 +8004,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>809522</v>
+        <v>809668</v>
       </c>
       <c r="R77" t="n">
-        <v>7349621</v>
+        <v>7349858</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8048,26 +8048,25 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125374186</v>
+        <v>125374097</v>
       </c>
       <c r="B78" t="n">
         <v>92502</v>
@@ -8102,13 +8101,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>809668</v>
+        <v>809532</v>
       </c>
       <c r="R78" t="n">
-        <v>7349858</v>
+        <v>7349513</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8152,19 +8151,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374097</v>
+        <v>125374102</v>
       </c>
       <c r="B79" t="n">
         <v>92502</v>
@@ -8199,10 +8198,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>809532</v>
+        <v>809743</v>
       </c>
       <c r="R79" t="n">
-        <v>7349513</v>
+        <v>7349889</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8261,7 +8260,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374102</v>
+        <v>125374027</v>
       </c>
       <c r="B80" t="n">
         <v>92502</v>
@@ -8296,13 +8295,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>809743</v>
+        <v>809720</v>
       </c>
       <c r="R80" t="n">
-        <v>7349889</v>
+        <v>7349576</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8346,19 +8345,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125374027</v>
+        <v>125373915</v>
       </c>
       <c r="B81" t="n">
         <v>92502</v>
@@ -8393,13 +8392,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>809720</v>
+        <v>809967</v>
       </c>
       <c r="R81" t="n">
-        <v>7349576</v>
+        <v>7349981</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8443,19 +8442,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125373915</v>
+        <v>125374889</v>
       </c>
       <c r="B82" t="n">
         <v>92502</v>
@@ -8490,13 +8489,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>809967</v>
+        <v>809697</v>
       </c>
       <c r="R82" t="n">
-        <v>7349981</v>
+        <v>7349873</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8534,50 +8533,51 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125374889</v>
+        <v>125374072</v>
       </c>
       <c r="B83" t="n">
-        <v>92502</v>
+        <v>92700</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8587,13 +8587,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>809697</v>
+        <v>809857</v>
       </c>
       <c r="R83" t="n">
-        <v>7349873</v>
+        <v>7350013</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8631,29 +8631,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125374856</v>
+        <v>125374077</v>
       </c>
       <c r="B84" t="n">
-        <v>79585</v>
+        <v>92700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8661,21 +8660,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8685,13 +8684,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>809648</v>
+        <v>809749</v>
       </c>
       <c r="R84" t="n">
-        <v>7349702</v>
+        <v>7349919</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8735,22 +8734,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125374007</v>
+        <v>125374024</v>
       </c>
       <c r="B85" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8758,21 +8757,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8782,10 +8781,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>809505</v>
+        <v>809741</v>
       </c>
       <c r="R85" t="n">
-        <v>7349593</v>
+        <v>7349907</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8844,10 +8843,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125376400</v>
+        <v>125376415</v>
       </c>
       <c r="B86" t="n">
-        <v>79585</v>
+        <v>92700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8855,21 +8854,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8879,10 +8878,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>809484</v>
+        <v>809522</v>
       </c>
       <c r="R86" t="n">
-        <v>7349700</v>
+        <v>7349621</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -8923,6 +8922,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9620,10 +9620,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125374909</v>
+        <v>125373960</v>
       </c>
       <c r="B94" t="n">
-        <v>78373</v>
+        <v>92700</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9631,21 +9631,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9655,13 +9655,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>809524</v>
+        <v>809929</v>
       </c>
       <c r="R94" t="n">
-        <v>7349656</v>
+        <v>7349900</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9705,44 +9705,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125374037</v>
+        <v>125374864</v>
       </c>
       <c r="B95" t="n">
-        <v>78373</v>
+        <v>91380</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9752,10 +9752,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809942</v>
+        <v>809790</v>
       </c>
       <c r="R95" t="n">
-        <v>7350024</v>
+        <v>7349726</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9796,66 +9796,67 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374043</v>
+        <v>125374161</v>
       </c>
       <c r="B96" t="n">
-        <v>78373</v>
+        <v>91478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809396</v>
+        <v>809457</v>
       </c>
       <c r="R96" t="n">
-        <v>7349580</v>
+        <v>7349587</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9899,22 +9900,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125373960</v>
+        <v>125374909</v>
       </c>
       <c r="B97" t="n">
-        <v>92700</v>
+        <v>78373</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9922,21 +9923,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9946,13 +9947,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809929</v>
+        <v>809524</v>
       </c>
       <c r="R97" t="n">
-        <v>7349900</v>
+        <v>7349656</v>
       </c>
       <c r="S97" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9996,44 +9997,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125374864</v>
+        <v>125374037</v>
       </c>
       <c r="B98" t="n">
-        <v>91380</v>
+        <v>78373</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10043,10 +10044,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809790</v>
+        <v>809942</v>
       </c>
       <c r="R98" t="n">
-        <v>7349726</v>
+        <v>7350024</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10087,67 +10088,66 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374161</v>
+        <v>125374043</v>
       </c>
       <c r="B99" t="n">
-        <v>91478</v>
+        <v>78373</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809457</v>
+        <v>809396</v>
       </c>
       <c r="R99" t="n">
-        <v>7349587</v>
+        <v>7349580</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10191,12 +10191,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -11275,32 +11275,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125374031</v>
+        <v>125374100</v>
       </c>
       <c r="B111" t="n">
-        <v>77916</v>
+        <v>92502</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11310,13 +11310,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>809617</v>
+        <v>809918</v>
       </c>
       <c r="R111" t="n">
-        <v>7349830</v>
+        <v>7350040</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11360,44 +11360,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125373996</v>
+        <v>125374902</v>
       </c>
       <c r="B112" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>809856</v>
+        <v>809413</v>
       </c>
       <c r="R112" t="n">
-        <v>7349815</v>
+        <v>7349595</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11451,50 +11451,51 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125374089</v>
+        <v>125374541</v>
       </c>
       <c r="B113" t="n">
-        <v>78725</v>
+        <v>92502</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11504,13 +11505,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>809956</v>
+        <v>809384</v>
       </c>
       <c r="R113" t="n">
-        <v>7349827</v>
+        <v>7349553</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11554,19 +11555,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125374100</v>
+        <v>125374895</v>
       </c>
       <c r="B114" t="n">
         <v>92502</v>
@@ -11601,13 +11602,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>809918</v>
+        <v>809584</v>
       </c>
       <c r="R114" t="n">
-        <v>7350040</v>
+        <v>7349617</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11645,25 +11646,26 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125374902</v>
+        <v>125374098</v>
       </c>
       <c r="B115" t="n">
         <v>92502</v>
@@ -11698,13 +11700,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>809413</v>
+        <v>809810</v>
       </c>
       <c r="R115" t="n">
-        <v>7349595</v>
+        <v>7349749</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11742,26 +11744,25 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125374541</v>
+        <v>125374540</v>
       </c>
       <c r="B116" t="n">
         <v>92502</v>
@@ -11796,10 +11797,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>809384</v>
+        <v>809461</v>
       </c>
       <c r="R116" t="n">
-        <v>7349553</v>
+        <v>7349612</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11858,7 +11859,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125374895</v>
+        <v>125373924</v>
       </c>
       <c r="B117" t="n">
         <v>92502</v>
@@ -11893,13 +11894,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>809584</v>
+        <v>809702</v>
       </c>
       <c r="R117" t="n">
-        <v>7349617</v>
+        <v>7349703</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11937,51 +11938,50 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125374098</v>
+        <v>125374011</v>
       </c>
       <c r="B118" t="n">
-        <v>92502</v>
+        <v>57648</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11991,13 +11991,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>809810</v>
+        <v>809693</v>
       </c>
       <c r="R118" t="n">
-        <v>7349749</v>
+        <v>7349989</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12041,44 +12041,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125374540</v>
+        <v>125374031</v>
       </c>
       <c r="B119" t="n">
-        <v>92502</v>
+        <v>77916</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>809461</v>
+        <v>809617</v>
       </c>
       <c r="R119" t="n">
-        <v>7349612</v>
+        <v>7349830</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12138,44 +12138,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125373924</v>
+        <v>125373996</v>
       </c>
       <c r="B120" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12185,13 +12185,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>809702</v>
+        <v>809856</v>
       </c>
       <c r="R120" t="n">
-        <v>7349703</v>
+        <v>7349815</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12235,22 +12235,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125373930</v>
+        <v>125374089</v>
       </c>
       <c r="B121" t="n">
-        <v>78373</v>
+        <v>78725</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12258,21 +12258,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12282,10 +12282,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>809731</v>
+        <v>809956</v>
       </c>
       <c r="R121" t="n">
-        <v>7349926</v>
+        <v>7349827</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12332,19 +12332,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125373933</v>
+        <v>125373930</v>
       </c>
       <c r="B122" t="n">
         <v>78373</v>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>809589</v>
+        <v>809731</v>
       </c>
       <c r="R122" t="n">
-        <v>7349641</v>
+        <v>7349926</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12441,7 +12441,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125374034</v>
+        <v>125373933</v>
       </c>
       <c r="B123" t="n">
         <v>78373</v>
@@ -12476,13 +12476,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>809797</v>
+        <v>809589</v>
       </c>
       <c r="R123" t="n">
-        <v>7349716</v>
+        <v>7349641</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12526,22 +12526,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125374011</v>
+        <v>125374034</v>
       </c>
       <c r="B124" t="n">
-        <v>57648</v>
+        <v>78373</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12549,21 +12549,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12573,10 +12573,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>809693</v>
+        <v>809797</v>
       </c>
       <c r="R124" t="n">
-        <v>7349989</v>
+        <v>7349716</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14490,10 +14490,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125374526</v>
+        <v>125374085</v>
       </c>
       <c r="B144" t="n">
-        <v>92700</v>
+        <v>78726</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14501,21 +14501,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14525,13 +14525,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>809830</v>
+        <v>809652</v>
       </c>
       <c r="R144" t="n">
-        <v>7349803</v>
+        <v>7349686</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14575,19 +14575,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125376410</v>
+        <v>125374526</v>
       </c>
       <c r="B145" t="n">
         <v>92700</v>
@@ -14622,13 +14622,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>809454</v>
+        <v>809830</v>
       </c>
       <c r="R145" t="n">
-        <v>7349679</v>
+        <v>7349803</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14672,22 +14672,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125374002</v>
+        <v>125376410</v>
       </c>
       <c r="B146" t="n">
-        <v>79585</v>
+        <v>92700</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14695,21 +14695,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14719,13 +14719,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>809718</v>
+        <v>809454</v>
       </c>
       <c r="R146" t="n">
-        <v>7349928</v>
+        <v>7349679</v>
       </c>
       <c r="S146" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14769,22 +14769,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125374018</v>
+        <v>125374002</v>
       </c>
       <c r="B147" t="n">
-        <v>78725</v>
+        <v>79585</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14792,21 +14792,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>809857</v>
+        <v>809718</v>
       </c>
       <c r="R147" t="n">
-        <v>7349810</v>
+        <v>7349928</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -14878,10 +14878,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125374033</v>
+        <v>125374018</v>
       </c>
       <c r="B148" t="n">
-        <v>78373</v>
+        <v>78725</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14889,21 +14889,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14913,10 +14913,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>809646</v>
+        <v>809857</v>
       </c>
       <c r="R148" t="n">
-        <v>7349532</v>
+        <v>7349810</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15754,10 +15754,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125374085</v>
+        <v>125374033</v>
       </c>
       <c r="B157" t="n">
-        <v>78726</v>
+        <v>78373</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15765,21 +15765,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15789,13 +15789,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>809652</v>
+        <v>809646</v>
       </c>
       <c r="R157" t="n">
-        <v>7349686</v>
+        <v>7349532</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -15839,12 +15839,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16045,32 +16045,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125374873</v>
+        <v>125373995</v>
       </c>
       <c r="B160" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16080,13 +16080,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>809452</v>
+        <v>809732</v>
       </c>
       <c r="R160" t="n">
-        <v>7349512</v>
+        <v>7349917</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16124,51 +16124,50 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125374182</v>
+        <v>125374179</v>
       </c>
       <c r="B161" t="n">
-        <v>92502</v>
+        <v>92530</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16178,10 +16177,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>809522</v>
+        <v>809720</v>
       </c>
       <c r="R161" t="n">
-        <v>7349734</v>
+        <v>7349861</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16240,32 +16239,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125374352</v>
+        <v>125373906</v>
       </c>
       <c r="B162" t="n">
-        <v>92502</v>
+        <v>78726</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16275,10 +16274,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>809944</v>
+        <v>809624</v>
       </c>
       <c r="R162" t="n">
-        <v>7349910</v>
+        <v>7349838</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -16325,44 +16324,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125373992</v>
+        <v>125373900</v>
       </c>
       <c r="B163" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16372,13 +16371,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>809588</v>
+        <v>809545</v>
       </c>
       <c r="R163" t="n">
-        <v>7349579</v>
+        <v>7349602</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16422,44 +16421,44 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125373982</v>
+        <v>125376402</v>
       </c>
       <c r="B164" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16469,13 +16468,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>809864</v>
+        <v>809636</v>
       </c>
       <c r="R164" t="n">
-        <v>7349953</v>
+        <v>7349511</v>
       </c>
       <c r="S164" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -16519,19 +16518,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125374881</v>
+        <v>125374873</v>
       </c>
       <c r="B165" t="n">
         <v>92502</v>
@@ -16566,10 +16565,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>809888</v>
+        <v>809452</v>
       </c>
       <c r="R165" t="n">
-        <v>7349802</v>
+        <v>7349512</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -16629,7 +16628,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125374187</v>
+        <v>125374182</v>
       </c>
       <c r="B166" t="n">
         <v>92502</v>
@@ -16664,10 +16663,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>809659</v>
+        <v>809522</v>
       </c>
       <c r="R166" t="n">
-        <v>7349773</v>
+        <v>7349734</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -16726,32 +16725,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125373906</v>
+        <v>125374352</v>
       </c>
       <c r="B167" t="n">
-        <v>78726</v>
+        <v>92502</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16761,10 +16760,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>809624</v>
+        <v>809944</v>
       </c>
       <c r="R167" t="n">
-        <v>7349838</v>
+        <v>7349910</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -16811,44 +16810,44 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125373900</v>
+        <v>125373992</v>
       </c>
       <c r="B168" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16858,13 +16857,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>809545</v>
+        <v>809588</v>
       </c>
       <c r="R168" t="n">
-        <v>7349602</v>
+        <v>7349579</v>
       </c>
       <c r="S168" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -16908,44 +16907,44 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125376402</v>
+        <v>125373982</v>
       </c>
       <c r="B169" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -16955,13 +16954,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>809636</v>
+        <v>809864</v>
       </c>
       <c r="R169" t="n">
-        <v>7349511</v>
+        <v>7349953</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17005,44 +17004,44 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125373995</v>
+        <v>125374881</v>
       </c>
       <c r="B170" t="n">
-        <v>78373</v>
+        <v>92502</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17052,13 +17051,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>809732</v>
+        <v>809888</v>
       </c>
       <c r="R170" t="n">
-        <v>7349917</v>
+        <v>7349802</v>
       </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17096,50 +17095,51 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125374179</v>
+        <v>125374187</v>
       </c>
       <c r="B171" t="n">
-        <v>92530</v>
+        <v>92502</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17149,10 +17149,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>809720</v>
+        <v>809659</v>
       </c>
       <c r="R171" t="n">
-        <v>7349861</v>
+        <v>7349773</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18577,10 +18577,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125374063</v>
+        <v>125373997</v>
       </c>
       <c r="B186" t="n">
-        <v>90258</v>
+        <v>79585</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18588,21 +18588,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18612,13 +18612,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>809446</v>
+        <v>809858</v>
       </c>
       <c r="R186" t="n">
-        <v>7349560</v>
+        <v>7349814</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -18662,44 +18662,44 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125373965</v>
+        <v>125374020</v>
       </c>
       <c r="B187" t="n">
-        <v>91380</v>
+        <v>78967</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18709,13 +18709,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>809922</v>
+        <v>809655</v>
       </c>
       <c r="R187" t="n">
-        <v>7349894</v>
+        <v>7349698</v>
       </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18759,22 +18759,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125373959</v>
+        <v>125374865</v>
       </c>
       <c r="B188" t="n">
-        <v>92494</v>
+        <v>78726</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18782,21 +18782,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809701</v>
+        <v>809649</v>
       </c>
       <c r="R188" t="n">
-        <v>7349889</v>
+        <v>7349705</v>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -18856,22 +18856,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125374907</v>
+        <v>125374063</v>
       </c>
       <c r="B189" t="n">
-        <v>92496</v>
+        <v>90258</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18879,21 +18879,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809807</v>
+        <v>809446</v>
       </c>
       <c r="R189" t="n">
-        <v>7349987</v>
+        <v>7349560</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18939,11 +18939,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -18958,44 +18953,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125374533</v>
+        <v>125373965</v>
       </c>
       <c r="B190" t="n">
-        <v>92502</v>
+        <v>91380</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19005,13 +19000,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809958</v>
+        <v>809922</v>
       </c>
       <c r="R190" t="n">
-        <v>7350004</v>
+        <v>7349894</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19055,44 +19050,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125373911</v>
+        <v>125373959</v>
       </c>
       <c r="B191" t="n">
-        <v>92502</v>
+        <v>92494</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19102,13 +19097,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809707</v>
+        <v>809701</v>
       </c>
       <c r="R191" t="n">
-        <v>7349576</v>
+        <v>7349889</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19152,22 +19147,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125374865</v>
+        <v>125374907</v>
       </c>
       <c r="B192" t="n">
-        <v>78726</v>
+        <v>92496</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19175,21 +19170,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19199,10 +19194,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809649</v>
+        <v>809807</v>
       </c>
       <c r="R192" t="n">
-        <v>7349705</v>
+        <v>7349987</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19235,6 +19230,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19261,32 +19261,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125373997</v>
+        <v>125374533</v>
       </c>
       <c r="B193" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19296,10 +19296,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809858</v>
+        <v>809958</v>
       </c>
       <c r="R193" t="n">
-        <v>7349814</v>
+        <v>7350004</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19346,44 +19346,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125374020</v>
+        <v>125373911</v>
       </c>
       <c r="B194" t="n">
-        <v>78967</v>
+        <v>92502</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19393,13 +19393,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809655</v>
+        <v>809707</v>
       </c>
       <c r="R194" t="n">
-        <v>7349698</v>
+        <v>7349576</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19443,12 +19443,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -20238,10 +20238,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125373964</v>
+        <v>125373909</v>
       </c>
       <c r="B203" t="n">
-        <v>98324</v>
+        <v>91478</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20249,21 +20249,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20273,13 +20273,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>809683</v>
+        <v>809626</v>
       </c>
       <c r="R203" t="n">
-        <v>7349980</v>
+        <v>7349810</v>
       </c>
       <c r="S203" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -20323,44 +20323,44 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125374354</v>
+        <v>125373962</v>
       </c>
       <c r="B204" t="n">
-        <v>92502</v>
+        <v>92700</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20370,13 +20370,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>809669</v>
+        <v>809641</v>
       </c>
       <c r="R204" t="n">
-        <v>7349770</v>
+        <v>7349649</v>
       </c>
       <c r="S204" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -20420,44 +20420,44 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125373988</v>
+        <v>125373928</v>
       </c>
       <c r="B205" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -20467,13 +20467,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>809651</v>
+        <v>809661</v>
       </c>
       <c r="R205" t="n">
-        <v>7349747</v>
+        <v>7349566</v>
       </c>
       <c r="S205" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -20517,44 +20517,44 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>125374880</v>
+        <v>125374042</v>
       </c>
       <c r="B206" t="n">
-        <v>92502</v>
+        <v>78373</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -20564,10 +20564,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>809785</v>
+        <v>809583</v>
       </c>
       <c r="R206" t="n">
-        <v>7349769</v>
+        <v>7349591</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -20608,51 +20608,50 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
-      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>125373978</v>
+        <v>125373964</v>
       </c>
       <c r="B207" t="n">
-        <v>92502</v>
+        <v>98324</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -20662,10 +20661,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>809758</v>
+        <v>809683</v>
       </c>
       <c r="R207" t="n">
-        <v>7349662</v>
+        <v>7349980</v>
       </c>
       <c r="S207" t="n">
         <v>1</v>
@@ -20724,32 +20723,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>125374891</v>
+        <v>125374854</v>
       </c>
       <c r="B208" t="n">
-        <v>92502</v>
+        <v>79585</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -20759,10 +20758,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>809618</v>
+        <v>809581</v>
       </c>
       <c r="R208" t="n">
-        <v>7349662</v>
+        <v>7349510</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -20803,7 +20802,6 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -20822,32 +20820,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>125373909</v>
+        <v>125373899</v>
       </c>
       <c r="B209" t="n">
-        <v>91478</v>
+        <v>79585</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -20857,10 +20855,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>809626</v>
+        <v>809933</v>
       </c>
       <c r="R209" t="n">
-        <v>7349810</v>
+        <v>7349784</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -20919,10 +20917,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125373962</v>
+        <v>125374030</v>
       </c>
       <c r="B210" t="n">
-        <v>92700</v>
+        <v>77916</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -20930,21 +20928,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -20954,13 +20952,13 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>809641</v>
+        <v>809944</v>
       </c>
       <c r="R210" t="n">
-        <v>7349649</v>
+        <v>7350018</v>
       </c>
       <c r="S210" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -21004,44 +21002,44 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125374854</v>
+        <v>125374354</v>
       </c>
       <c r="B211" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -21051,13 +21049,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>809581</v>
+        <v>809669</v>
       </c>
       <c r="R211" t="n">
-        <v>7349510</v>
+        <v>7349770</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -21101,44 +21099,44 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>125373899</v>
+        <v>125373988</v>
       </c>
       <c r="B212" t="n">
-        <v>79585</v>
+        <v>92502</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21148,13 +21146,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>809933</v>
+        <v>809651</v>
       </c>
       <c r="R212" t="n">
-        <v>7349784</v>
+        <v>7349747</v>
       </c>
       <c r="S212" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -21198,44 +21196,44 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>125374030</v>
+        <v>125374880</v>
       </c>
       <c r="B213" t="n">
-        <v>77916</v>
+        <v>92502</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21245,10 +21243,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>809944</v>
+        <v>809785</v>
       </c>
       <c r="R213" t="n">
-        <v>7350018</v>
+        <v>7349769</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -21289,50 +21287,51 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125373928</v>
+        <v>125373978</v>
       </c>
       <c r="B214" t="n">
-        <v>78373</v>
+        <v>92502</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21342,13 +21341,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>809661</v>
+        <v>809758</v>
       </c>
       <c r="R214" t="n">
-        <v>7349566</v>
+        <v>7349662</v>
       </c>
       <c r="S214" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -21392,44 +21391,44 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>125374042</v>
+        <v>125374891</v>
       </c>
       <c r="B215" t="n">
-        <v>78373</v>
+        <v>92502</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -21439,10 +21438,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>809583</v>
+        <v>809618</v>
       </c>
       <c r="R215" t="n">
-        <v>7349591</v>
+        <v>7349662</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -21483,18 +21482,19 @@
       <c r="AE215" t="b">
         <v>0</v>
       </c>
+      <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
         <v>0</v>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374041</v>
+        <v>125376417</v>
       </c>
       <c r="B24" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>809655</v>
+        <v>809807</v>
       </c>
       <c r="R24" t="n">
-        <v>7349694</v>
+        <v>7349660</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2898,25 +2898,26 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125373973</v>
+        <v>125374347</v>
       </c>
       <c r="B25" t="n">
         <v>92509</v>
@@ -2951,13 +2952,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>809732</v>
+        <v>809653</v>
       </c>
       <c r="R25" t="n">
-        <v>7349587</v>
+        <v>7349772</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,22 +3002,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374032</v>
+        <v>125374041</v>
       </c>
       <c r="B26" t="n">
-        <v>77916</v>
+        <v>78373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3025,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3049,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>809628</v>
+        <v>809655</v>
       </c>
       <c r="R26" t="n">
-        <v>7349657</v>
+        <v>7349694</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,7 +3111,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125373910</v>
+        <v>125373973</v>
       </c>
       <c r="B27" t="n">
         <v>92509</v>
@@ -3145,13 +3146,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>809589</v>
+        <v>809732</v>
       </c>
       <c r="R27" t="n">
-        <v>7349496</v>
+        <v>7349587</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3195,22 +3196,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374022</v>
+        <v>125374032</v>
       </c>
       <c r="B28" t="n">
-        <v>78634</v>
+        <v>77916</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3219,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3243,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>809927</v>
+        <v>809628</v>
       </c>
       <c r="R28" t="n">
-        <v>7349959</v>
+        <v>7349657</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,32 +3305,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374548</v>
+        <v>125373910</v>
       </c>
       <c r="B29" t="n">
-        <v>91241</v>
+        <v>92509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,13 +3340,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>809759</v>
+        <v>809589</v>
       </c>
       <c r="R29" t="n">
-        <v>7349927</v>
+        <v>7349496</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3389,22 +3390,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125376408</v>
+        <v>125374022</v>
       </c>
       <c r="B30" t="n">
-        <v>90265</v>
+        <v>78634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,21 +3413,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3436,13 +3437,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>809843</v>
+        <v>809927</v>
       </c>
       <c r="R30" t="n">
-        <v>7349800</v>
+        <v>7349959</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3486,44 +3487,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374347</v>
+        <v>125374548</v>
       </c>
       <c r="B31" t="n">
-        <v>92509</v>
+        <v>91241</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,13 +3534,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>809653</v>
+        <v>809759</v>
       </c>
       <c r="R31" t="n">
-        <v>7349772</v>
+        <v>7349927</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3583,22 +3584,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125376417</v>
+        <v>125376408</v>
       </c>
       <c r="B32" t="n">
-        <v>78726</v>
+        <v>90265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,21 +3607,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3630,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>809807</v>
+        <v>809843</v>
       </c>
       <c r="R32" t="n">
-        <v>7349660</v>
+        <v>7349800</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3674,7 +3675,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374093</v>
+        <v>125374876</v>
       </c>
       <c r="B43" t="n">
-        <v>91485</v>
+        <v>92509</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809619</v>
+        <v>809605</v>
       </c>
       <c r="R43" t="n">
-        <v>7349622</v>
+        <v>7349541</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4742,28 +4742,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374180</v>
+        <v>125373927</v>
       </c>
       <c r="B44" t="n">
-        <v>92707</v>
+        <v>78373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4771,21 +4772,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,13 +4796,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809528</v>
+        <v>809878</v>
       </c>
       <c r="R44" t="n">
-        <v>7349612</v>
+        <v>7349722</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4845,19 +4846,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125374876</v>
+        <v>125373918</v>
       </c>
       <c r="B45" t="n">
         <v>92509</v>
@@ -4892,13 +4893,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809605</v>
+        <v>809764</v>
       </c>
       <c r="R45" t="n">
-        <v>7349541</v>
+        <v>7349945</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4936,51 +4937,50 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125373927</v>
+        <v>125374528</v>
       </c>
       <c r="B46" t="n">
-        <v>78373</v>
+        <v>91454</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>5260</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809878</v>
+        <v>809822</v>
       </c>
       <c r="R46" t="n">
-        <v>7349722</v>
+        <v>7349799</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5040,44 +5040,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125373918</v>
+        <v>125374003</v>
       </c>
       <c r="B47" t="n">
-        <v>92509</v>
+        <v>79585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>809764</v>
+        <v>809619</v>
       </c>
       <c r="R47" t="n">
-        <v>7349945</v>
+        <v>7349838</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5137,44 +5137,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125374528</v>
+        <v>125373954</v>
       </c>
       <c r="B48" t="n">
-        <v>91454</v>
+        <v>92521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5260</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809822</v>
+        <v>809809</v>
       </c>
       <c r="R48" t="n">
-        <v>7349799</v>
+        <v>7349982</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5234,44 +5234,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374003</v>
+        <v>125373902</v>
       </c>
       <c r="B49" t="n">
-        <v>79585</v>
+        <v>56843</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>809619</v>
+        <v>809943</v>
       </c>
       <c r="R49" t="n">
-        <v>7349838</v>
+        <v>7349906</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5317,6 +5317,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5331,44 +5336,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125373954</v>
+        <v>125374093</v>
       </c>
       <c r="B50" t="n">
-        <v>92521</v>
+        <v>91485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>65</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5378,13 +5383,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>809809</v>
+        <v>809619</v>
       </c>
       <c r="R50" t="n">
-        <v>7349982</v>
+        <v>7349622</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5428,44 +5433,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125373902</v>
+        <v>125374180</v>
       </c>
       <c r="B51" t="n">
-        <v>56843</v>
+        <v>92707</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5475,13 +5480,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>809943</v>
+        <v>809528</v>
       </c>
       <c r="R51" t="n">
-        <v>7349906</v>
+        <v>7349612</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5511,11 +5516,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5530,12 +5530,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7678,10 +7678,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125374072</v>
+        <v>125374856</v>
       </c>
       <c r="B74" t="n">
-        <v>92707</v>
+        <v>79585</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7689,21 +7689,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7713,13 +7713,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>809857</v>
+        <v>809648</v>
       </c>
       <c r="R74" t="n">
-        <v>7350013</v>
+        <v>7349702</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7763,22 +7763,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374077</v>
+        <v>125374160</v>
       </c>
       <c r="B75" t="n">
-        <v>92707</v>
+        <v>78967</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7786,37 +7786,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>809749</v>
+        <v>809654</v>
       </c>
       <c r="R75" t="n">
-        <v>7349919</v>
+        <v>7349767</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7860,44 +7860,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125374024</v>
+        <v>125374186</v>
       </c>
       <c r="B76" t="n">
-        <v>78634</v>
+        <v>92509</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7907,10 +7907,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>809741</v>
+        <v>809668</v>
       </c>
       <c r="R76" t="n">
-        <v>7349907</v>
+        <v>7349858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7957,44 +7957,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125376415</v>
+        <v>125374097</v>
       </c>
       <c r="B77" t="n">
-        <v>92707</v>
+        <v>92509</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>809522</v>
+        <v>809532</v>
       </c>
       <c r="R77" t="n">
-        <v>7349621</v>
+        <v>7349513</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8048,26 +8048,25 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125374856</v>
+        <v>125374007</v>
       </c>
       <c r="B78" t="n">
         <v>79585</v>
@@ -8102,10 +8101,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>809648</v>
+        <v>809505</v>
       </c>
       <c r="R78" t="n">
-        <v>7349702</v>
+        <v>7349593</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8152,60 +8151,60 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374160</v>
+        <v>125374102</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>809654</v>
+        <v>809743</v>
       </c>
       <c r="R79" t="n">
-        <v>7349767</v>
+        <v>7349889</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8249,44 +8248,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374186</v>
+        <v>125376400</v>
       </c>
       <c r="B80" t="n">
-        <v>92509</v>
+        <v>79585</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8296,13 +8295,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>809668</v>
+        <v>809484</v>
       </c>
       <c r="R80" t="n">
-        <v>7349858</v>
+        <v>7349700</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8346,19 +8345,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125374097</v>
+        <v>125374027</v>
       </c>
       <c r="B81" t="n">
         <v>92509</v>
@@ -8393,13 +8392,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>809532</v>
+        <v>809720</v>
       </c>
       <c r="R81" t="n">
-        <v>7349513</v>
+        <v>7349576</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8443,44 +8442,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125374007</v>
+        <v>125373915</v>
       </c>
       <c r="B82" t="n">
-        <v>79585</v>
+        <v>92509</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8490,13 +8489,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>809505</v>
+        <v>809967</v>
       </c>
       <c r="R82" t="n">
-        <v>7349593</v>
+        <v>7349981</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8540,19 +8539,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125374102</v>
+        <v>125374889</v>
       </c>
       <c r="B83" t="n">
         <v>92509</v>
@@ -8587,13 +8586,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>809743</v>
+        <v>809697</v>
       </c>
       <c r="R83" t="n">
-        <v>7349889</v>
+        <v>7349873</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8631,28 +8630,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125376400</v>
+        <v>125374072</v>
       </c>
       <c r="B84" t="n">
-        <v>79585</v>
+        <v>92707</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8660,21 +8660,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8684,10 +8684,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>809484</v>
+        <v>809857</v>
       </c>
       <c r="R84" t="n">
-        <v>7349700</v>
+        <v>7350013</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8734,44 +8734,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125374027</v>
+        <v>125374077</v>
       </c>
       <c r="B85" t="n">
-        <v>92509</v>
+        <v>92707</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8781,13 +8781,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>809720</v>
+        <v>809749</v>
       </c>
       <c r="R85" t="n">
-        <v>7349576</v>
+        <v>7349919</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8831,44 +8831,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125373915</v>
+        <v>125374024</v>
       </c>
       <c r="B86" t="n">
-        <v>92509</v>
+        <v>78634</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>809967</v>
+        <v>809741</v>
       </c>
       <c r="R86" t="n">
-        <v>7349981</v>
+        <v>7349907</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8928,44 +8928,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125374889</v>
+        <v>125376415</v>
       </c>
       <c r="B87" t="n">
-        <v>92509</v>
+        <v>92707</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -8975,13 +8975,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>809697</v>
+        <v>809522</v>
       </c>
       <c r="R87" t="n">
-        <v>7349873</v>
+        <v>7349621</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9026,12 +9026,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9717,10 +9717,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125373960</v>
+        <v>125374087</v>
       </c>
       <c r="B95" t="n">
-        <v>92707</v>
+        <v>78726</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9728,21 +9728,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9752,13 +9752,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809929</v>
+        <v>809592</v>
       </c>
       <c r="R95" t="n">
-        <v>7349900</v>
+        <v>7349582</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9802,44 +9802,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374864</v>
+        <v>125374081</v>
       </c>
       <c r="B96" t="n">
-        <v>91387</v>
+        <v>78726</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9849,13 +9849,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809790</v>
+        <v>809965</v>
       </c>
       <c r="R96" t="n">
-        <v>7349726</v>
+        <v>7349845</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9893,64 +9893,63 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125374161</v>
+        <v>125373960</v>
       </c>
       <c r="B97" t="n">
-        <v>91485</v>
+        <v>92707</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809457</v>
+        <v>809929</v>
       </c>
       <c r="R97" t="n">
-        <v>7349587</v>
+        <v>7349900</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -9997,44 +9996,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125374087</v>
+        <v>125374864</v>
       </c>
       <c r="B98" t="n">
-        <v>78726</v>
+        <v>91387</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10044,13 +10043,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809592</v>
+        <v>809790</v>
       </c>
       <c r="R98" t="n">
-        <v>7349582</v>
+        <v>7349726</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10088,66 +10087,67 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374081</v>
+        <v>125374161</v>
       </c>
       <c r="B99" t="n">
-        <v>78726</v>
+        <v>91485</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809965</v>
+        <v>809457</v>
       </c>
       <c r="R99" t="n">
-        <v>7349845</v>
+        <v>7349587</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10191,12 +10191,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12635,32 +12635,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125374091</v>
+        <v>125374349</v>
       </c>
       <c r="B125" t="n">
-        <v>91387</v>
+        <v>92509</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12670,10 +12670,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>809370</v>
+        <v>809624</v>
       </c>
       <c r="R125" t="n">
-        <v>7349556</v>
+        <v>7349547</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -12720,22 +12720,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125374023</v>
+        <v>125376403</v>
       </c>
       <c r="B126" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12743,21 +12743,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12767,13 +12767,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>809936</v>
+        <v>809861</v>
       </c>
       <c r="R126" t="n">
-        <v>7349967</v>
+        <v>7349763</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12817,44 +12817,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125374014</v>
+        <v>125374534</v>
       </c>
       <c r="B127" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>809857</v>
+        <v>809895</v>
       </c>
       <c r="R127" t="n">
-        <v>7349814</v>
+        <v>7350016</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12914,19 +12914,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125374349</v>
+        <v>125374162</v>
       </c>
       <c r="B128" t="n">
         <v>92509</v>
@@ -12957,17 +12957,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>809624</v>
+        <v>809339</v>
       </c>
       <c r="R128" t="n">
-        <v>7349547</v>
+        <v>7349557</v>
       </c>
       <c r="S128" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12997,6 +12997,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13011,44 +13016,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125376403</v>
+        <v>125373986</v>
       </c>
       <c r="B129" t="n">
-        <v>79585</v>
+        <v>92509</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13058,13 +13063,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>809861</v>
+        <v>809663</v>
       </c>
       <c r="R129" t="n">
-        <v>7349763</v>
+        <v>7349767</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13108,44 +13113,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125374534</v>
+        <v>125373929</v>
       </c>
       <c r="B130" t="n">
-        <v>92509</v>
+        <v>78373</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13155,13 +13160,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>809895</v>
+        <v>809911</v>
       </c>
       <c r="R130" t="n">
-        <v>7350016</v>
+        <v>7349897</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13205,19 +13210,19 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125374162</v>
+        <v>125374355</v>
       </c>
       <c r="B131" t="n">
         <v>92509</v>
@@ -13248,17 +13253,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>809339</v>
+        <v>809646</v>
       </c>
       <c r="R131" t="n">
-        <v>7349557</v>
+        <v>7349691</v>
       </c>
       <c r="S131" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13288,11 +13293,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Fjolårets</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13307,44 +13307,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125373986</v>
+        <v>125374091</v>
       </c>
       <c r="B132" t="n">
-        <v>92509</v>
+        <v>91387</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13354,13 +13354,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>809663</v>
+        <v>809370</v>
       </c>
       <c r="R132" t="n">
-        <v>7349767</v>
+        <v>7349556</v>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13404,22 +13404,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125373929</v>
+        <v>125374023</v>
       </c>
       <c r="B133" t="n">
-        <v>78373</v>
+        <v>78634</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13427,21 +13427,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13451,13 +13451,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>809911</v>
+        <v>809936</v>
       </c>
       <c r="R133" t="n">
-        <v>7349897</v>
+        <v>7349967</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13501,44 +13501,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125374355</v>
+        <v>125374014</v>
       </c>
       <c r="B134" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -13548,13 +13548,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>809646</v>
+        <v>809857</v>
       </c>
       <c r="R134" t="n">
-        <v>7349691</v>
+        <v>7349814</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13598,44 +13598,44 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125374530</v>
+        <v>125376407</v>
       </c>
       <c r="B135" t="n">
-        <v>92509</v>
+        <v>79556</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13645,13 +13645,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>809468</v>
+        <v>809670</v>
       </c>
       <c r="R135" t="n">
-        <v>7349525</v>
+        <v>7349836</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13689,50 +13689,51 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125374885</v>
+        <v>125374345</v>
       </c>
       <c r="B136" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13742,13 +13743,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>809841</v>
+        <v>809504</v>
       </c>
       <c r="R136" t="n">
-        <v>7350026</v>
+        <v>7349600</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13780,62 +13781,56 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125374543</v>
+        <v>125374530</v>
       </c>
       <c r="B137" t="n">
-        <v>92503</v>
+        <v>92509</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13845,10 +13840,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>809962</v>
+        <v>809468</v>
       </c>
       <c r="R137" t="n">
-        <v>7349982</v>
+        <v>7349525</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -13907,32 +13902,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125374178</v>
+        <v>125374885</v>
       </c>
       <c r="B138" t="n">
-        <v>92537</v>
+        <v>92509</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -13942,10 +13937,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>809681</v>
+        <v>809841</v>
       </c>
       <c r="R138" t="n">
-        <v>7349834</v>
+        <v>7350026</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -13980,34 +13975,40 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125374038</v>
+        <v>125374543</v>
       </c>
       <c r="B139" t="n">
-        <v>78373</v>
+        <v>92503</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14015,21 +14016,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14039,10 +14040,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>809896</v>
+        <v>809962</v>
       </c>
       <c r="R139" t="n">
-        <v>7350047</v>
+        <v>7349982</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14089,22 +14090,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125376407</v>
+        <v>125374178</v>
       </c>
       <c r="B140" t="n">
-        <v>79556</v>
+        <v>92537</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14112,21 +14113,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14136,13 +14137,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>809670</v>
+        <v>809681</v>
       </c>
       <c r="R140" t="n">
-        <v>7349836</v>
+        <v>7349834</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14180,29 +14181,28 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125374345</v>
+        <v>125374038</v>
       </c>
       <c r="B141" t="n">
-        <v>78726</v>
+        <v>78373</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14210,21 +14210,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14234,13 +14234,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>809504</v>
+        <v>809896</v>
       </c>
       <c r="R141" t="n">
-        <v>7349600</v>
+        <v>7350047</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14284,12 +14284,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
@@ -16920,10 +16920,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125374021</v>
+        <v>125373906</v>
       </c>
       <c r="B169" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -16931,21 +16931,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>809726</v>
+        <v>809624</v>
       </c>
       <c r="R169" t="n">
-        <v>7349569</v>
+        <v>7349838</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17005,44 +17005,44 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>125374549</v>
+        <v>125374021</v>
       </c>
       <c r="B170" t="n">
-        <v>91485</v>
+        <v>78634</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17052,10 +17052,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>809658</v>
+        <v>809726</v>
       </c>
       <c r="R170" t="n">
-        <v>7349719</v>
+        <v>7349569</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17102,44 +17102,44 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>125373906</v>
+        <v>125374549</v>
       </c>
       <c r="B171" t="n">
-        <v>78726</v>
+        <v>91485</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17149,13 +17149,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>809624</v>
+        <v>809658</v>
       </c>
       <c r="R171" t="n">
-        <v>7349838</v>
+        <v>7349719</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -17199,12 +17199,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -18086,32 +18086,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125373907</v>
+        <v>125376405</v>
       </c>
       <c r="B181" t="n">
-        <v>91387</v>
+        <v>79556</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>809608</v>
+        <v>809469</v>
       </c>
       <c r="R181" t="n">
-        <v>7349636</v>
+        <v>7349711</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -18165,28 +18165,29 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125374872</v>
+        <v>125373907</v>
       </c>
       <c r="B182" t="n">
-        <v>91485</v>
+        <v>91387</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18194,21 +18195,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18218,13 +18219,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>809657</v>
+        <v>809608</v>
       </c>
       <c r="R182" t="n">
-        <v>7349679</v>
+        <v>7349636</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18268,44 +18269,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125374342</v>
+        <v>125374872</v>
       </c>
       <c r="B183" t="n">
-        <v>92707</v>
+        <v>91485</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18315,13 +18316,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>809935</v>
+        <v>809657</v>
       </c>
       <c r="R183" t="n">
-        <v>7350019</v>
+        <v>7349679</v>
       </c>
       <c r="S183" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -18365,60 +18366,60 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125374153</v>
+        <v>125374342</v>
       </c>
       <c r="B184" t="n">
-        <v>56843</v>
+        <v>92707</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>809919</v>
+        <v>809935</v>
       </c>
       <c r="R184" t="n">
-        <v>7349964</v>
+        <v>7350019</v>
       </c>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -18448,11 +18449,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Spillning rikligt</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -18467,60 +18463,60 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125376405</v>
+        <v>125374153</v>
       </c>
       <c r="B185" t="n">
-        <v>79556</v>
+        <v>56843</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>809469</v>
+        <v>809919</v>
       </c>
       <c r="R185" t="n">
-        <v>7349711</v>
+        <v>7349964</v>
       </c>
       <c r="S185" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -18552,35 +18548,39 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Spillning rikligt</t>
+        </is>
+      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125374063</v>
+        <v>125374865</v>
       </c>
       <c r="B186" t="n">
-        <v>90265</v>
+        <v>78726</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18588,21 +18588,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18612,13 +18612,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>809446</v>
+        <v>809649</v>
       </c>
       <c r="R186" t="n">
-        <v>7349560</v>
+        <v>7349705</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -18662,44 +18662,44 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125373965</v>
+        <v>125374063</v>
       </c>
       <c r="B187" t="n">
-        <v>91387</v>
+        <v>90265</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18709,13 +18709,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>809922</v>
+        <v>809446</v>
       </c>
       <c r="R187" t="n">
-        <v>7349894</v>
+        <v>7349560</v>
       </c>
       <c r="S187" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18759,44 +18759,44 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125374340</v>
+        <v>125373965</v>
       </c>
       <c r="B188" t="n">
-        <v>56843</v>
+        <v>91387</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809945</v>
+        <v>809922</v>
       </c>
       <c r="R188" t="n">
-        <v>7349970</v>
+        <v>7349894</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -18842,11 +18842,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -18861,44 +18856,44 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125374020</v>
+        <v>125374340</v>
       </c>
       <c r="B189" t="n">
-        <v>78967</v>
+        <v>56843</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18908,13 +18903,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809655</v>
+        <v>809945</v>
       </c>
       <c r="R189" t="n">
-        <v>7349698</v>
+        <v>7349970</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18944,6 +18939,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -18958,22 +18958,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125373959</v>
+        <v>125374020</v>
       </c>
       <c r="B190" t="n">
-        <v>92501</v>
+        <v>78967</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18981,21 +18981,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19005,13 +19005,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809701</v>
+        <v>809655</v>
       </c>
       <c r="R190" t="n">
-        <v>7349889</v>
+        <v>7349698</v>
       </c>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19055,22 +19055,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125373997</v>
+        <v>125373959</v>
       </c>
       <c r="B191" t="n">
-        <v>79585</v>
+        <v>92501</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19078,21 +19078,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19102,13 +19102,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809858</v>
+        <v>809701</v>
       </c>
       <c r="R191" t="n">
-        <v>7349814</v>
+        <v>7349889</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19152,22 +19152,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125374907</v>
+        <v>125373997</v>
       </c>
       <c r="B192" t="n">
-        <v>92503</v>
+        <v>79585</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19175,21 +19175,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19199,10 +19199,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809807</v>
+        <v>809858</v>
       </c>
       <c r="R192" t="n">
-        <v>7349987</v>
+        <v>7349814</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19237,11 +19237,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -19254,44 +19249,44 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125374533</v>
+        <v>125374907</v>
       </c>
       <c r="B193" t="n">
-        <v>92509</v>
+        <v>92503</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19301,10 +19296,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809958</v>
+        <v>809807</v>
       </c>
       <c r="R193" t="n">
-        <v>7350004</v>
+        <v>7349987</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19339,6 +19334,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -19351,19 +19351,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125373911</v>
+        <v>125374533</v>
       </c>
       <c r="B194" t="n">
         <v>92509</v>
@@ -19398,13 +19398,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809707</v>
+        <v>809958</v>
       </c>
       <c r="R194" t="n">
-        <v>7349576</v>
+        <v>7350004</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19448,44 +19448,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125374865</v>
+        <v>125373911</v>
       </c>
       <c r="B195" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19495,13 +19495,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>809649</v>
+        <v>809707</v>
       </c>
       <c r="R195" t="n">
-        <v>7349705</v>
+        <v>7349576</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19545,44 +19545,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125376416</v>
+        <v>125374532</v>
       </c>
       <c r="B196" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19592,13 +19592,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>809489</v>
+        <v>809812</v>
       </c>
       <c r="R196" t="n">
-        <v>7349695</v>
+        <v>7349817</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -19636,29 +19636,28 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125374867</v>
+        <v>125374911</v>
       </c>
       <c r="B197" t="n">
-        <v>78726</v>
+        <v>78373</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19666,21 +19665,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19690,10 +19689,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>809521</v>
+        <v>809747</v>
       </c>
       <c r="R197" t="n">
-        <v>7349655</v>
+        <v>7349880</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -19752,7 +19751,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125374532</v>
+        <v>125374883</v>
       </c>
       <c r="B198" t="n">
         <v>92509</v>
@@ -19787,10 +19786,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>809812</v>
+        <v>809960</v>
       </c>
       <c r="R198" t="n">
-        <v>7349817</v>
+        <v>7349967</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -19831,25 +19830,26 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125374911</v>
+        <v>125374036</v>
       </c>
       <c r="B199" t="n">
         <v>78373</v>
@@ -19884,10 +19884,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>809747</v>
+        <v>809921</v>
       </c>
       <c r="R199" t="n">
-        <v>7349880</v>
+        <v>7349943</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -19934,44 +19934,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125374883</v>
+        <v>125376414</v>
       </c>
       <c r="B200" t="n">
-        <v>92509</v>
+        <v>92707</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -19981,13 +19981,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>809960</v>
+        <v>809561</v>
       </c>
       <c r="R200" t="n">
-        <v>7349967</v>
+        <v>7349813</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -20025,29 +20025,28 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125374036</v>
+        <v>125376416</v>
       </c>
       <c r="B201" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20055,21 +20054,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20079,13 +20078,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>809921</v>
+        <v>809489</v>
       </c>
       <c r="R201" t="n">
-        <v>7349943</v>
+        <v>7349695</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20123,28 +20122,29 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125376414</v>
+        <v>125374867</v>
       </c>
       <c r="B202" t="n">
-        <v>92707</v>
+        <v>78726</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20152,21 +20152,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20176,13 +20176,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>809561</v>
+        <v>809521</v>
       </c>
       <c r="R202" t="n">
-        <v>7349813</v>
+        <v>7349655</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20226,12 +20226,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -1549,7 +1549,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125374894</v>
+        <v>125374882</v>
       </c>
       <c r="B11" t="n">
         <v>92509</v>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>809639</v>
+        <v>809951</v>
       </c>
       <c r="R11" t="n">
-        <v>7349668</v>
+        <v>7349924</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,32 +1647,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125373912</v>
+        <v>125374095</v>
       </c>
       <c r="B12" t="n">
-        <v>92509</v>
+        <v>78634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>809755</v>
+        <v>809653</v>
       </c>
       <c r="R12" t="n">
-        <v>7349675</v>
+        <v>7349676</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1732,44 +1732,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125374900</v>
+        <v>125374870</v>
       </c>
       <c r="B13" t="n">
-        <v>92509</v>
+        <v>91387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>809462</v>
+        <v>809852</v>
       </c>
       <c r="R13" t="n">
-        <v>7349575</v>
+        <v>7350051</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,7 +1823,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1842,10 +1841,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125374544</v>
+        <v>125376411</v>
       </c>
       <c r="B14" t="n">
-        <v>78373</v>
+        <v>92707</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1853,21 +1852,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1877,13 +1876,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809669</v>
+        <v>809462</v>
       </c>
       <c r="R14" t="n">
-        <v>7349819</v>
+        <v>7349673</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1927,44 +1926,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125374537</v>
+        <v>125376419</v>
       </c>
       <c r="B15" t="n">
-        <v>92509</v>
+        <v>91485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1974,13 +1973,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809741</v>
+        <v>809843</v>
       </c>
       <c r="R15" t="n">
-        <v>7349887</v>
+        <v>7349800</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2024,44 +2023,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125374882</v>
+        <v>125376406</v>
       </c>
       <c r="B16" t="n">
-        <v>92509</v>
+        <v>79556</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2071,13 +2070,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809951</v>
+        <v>809747</v>
       </c>
       <c r="R16" t="n">
-        <v>7349924</v>
+        <v>7349847</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,22 +2121,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125373914</v>
+        <v>125373952</v>
       </c>
       <c r="B17" t="n">
-        <v>92509</v>
+        <v>56843</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2144,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,13 +2168,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809867</v>
+        <v>809809</v>
       </c>
       <c r="R17" t="n">
-        <v>7349727</v>
+        <v>7349755</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2205,6 +2204,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2219,44 +2223,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125374095</v>
+        <v>125374894</v>
       </c>
       <c r="B18" t="n">
-        <v>78634</v>
+        <v>92509</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,13 +2270,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809653</v>
+        <v>809639</v>
       </c>
       <c r="R18" t="n">
-        <v>7349676</v>
+        <v>7349668</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2310,50 +2314,51 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125374870</v>
+        <v>125373912</v>
       </c>
       <c r="B19" t="n">
-        <v>91387</v>
+        <v>92509</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,13 +2368,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>809852</v>
+        <v>809755</v>
       </c>
       <c r="R19" t="n">
-        <v>7350051</v>
+        <v>7349675</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2413,44 +2418,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125376411</v>
+        <v>125374900</v>
       </c>
       <c r="B20" t="n">
-        <v>92707</v>
+        <v>92509</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2463,10 +2468,10 @@
         <v>809462</v>
       </c>
       <c r="R20" t="n">
-        <v>7349673</v>
+        <v>7349575</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2504,50 +2509,51 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125376419</v>
+        <v>125374544</v>
       </c>
       <c r="B21" t="n">
-        <v>91485</v>
+        <v>78373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,13 +2563,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>809843</v>
+        <v>809669</v>
       </c>
       <c r="R21" t="n">
-        <v>7349800</v>
+        <v>7349819</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2607,22 +2613,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125373952</v>
+        <v>125374537</v>
       </c>
       <c r="B22" t="n">
-        <v>56843</v>
+        <v>92509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2654,13 +2660,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>809809</v>
+        <v>809741</v>
       </c>
       <c r="R22" t="n">
-        <v>7349755</v>
+        <v>7349887</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2690,11 +2696,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2709,44 +2710,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125376406</v>
+        <v>125373914</v>
       </c>
       <c r="B23" t="n">
-        <v>79556</v>
+        <v>92509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>809747</v>
+        <v>809867</v>
       </c>
       <c r="R23" t="n">
-        <v>7349847</v>
+        <v>7349727</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2800,29 +2801,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125376417</v>
+        <v>125374041</v>
       </c>
       <c r="B24" t="n">
-        <v>78726</v>
+        <v>78373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>809807</v>
+        <v>809655</v>
       </c>
       <c r="R24" t="n">
-        <v>7349660</v>
+        <v>7349694</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2898,26 +2898,25 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125374347</v>
+        <v>125373973</v>
       </c>
       <c r="B25" t="n">
         <v>92509</v>
@@ -2952,13 +2951,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>809653</v>
+        <v>809732</v>
       </c>
       <c r="R25" t="n">
-        <v>7349772</v>
+        <v>7349587</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3002,22 +3001,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374041</v>
+        <v>125374032</v>
       </c>
       <c r="B26" t="n">
-        <v>78373</v>
+        <v>77916</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3025,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3049,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>809655</v>
+        <v>809628</v>
       </c>
       <c r="R26" t="n">
-        <v>7349694</v>
+        <v>7349657</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3111,7 +3110,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125373973</v>
+        <v>125373910</v>
       </c>
       <c r="B27" t="n">
         <v>92509</v>
@@ -3146,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>809732</v>
+        <v>809589</v>
       </c>
       <c r="R27" t="n">
-        <v>7349587</v>
+        <v>7349496</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3196,22 +3195,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374032</v>
+        <v>125374022</v>
       </c>
       <c r="B28" t="n">
-        <v>77916</v>
+        <v>78634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3219,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3243,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>809628</v>
+        <v>809927</v>
       </c>
       <c r="R28" t="n">
-        <v>7349657</v>
+        <v>7349959</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3305,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125373910</v>
+        <v>125374548</v>
       </c>
       <c r="B29" t="n">
-        <v>92509</v>
+        <v>91241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3340,13 +3339,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>809589</v>
+        <v>809759</v>
       </c>
       <c r="R29" t="n">
-        <v>7349496</v>
+        <v>7349927</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3390,22 +3389,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125374022</v>
+        <v>125376408</v>
       </c>
       <c r="B30" t="n">
-        <v>78634</v>
+        <v>90265</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3413,21 +3412,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3437,13 +3436,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>809927</v>
+        <v>809843</v>
       </c>
       <c r="R30" t="n">
-        <v>7349959</v>
+        <v>7349800</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3487,44 +3486,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374548</v>
+        <v>125374347</v>
       </c>
       <c r="B31" t="n">
-        <v>91241</v>
+        <v>92509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3534,13 +3533,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>809759</v>
+        <v>809653</v>
       </c>
       <c r="R31" t="n">
-        <v>7349927</v>
+        <v>7349772</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3584,22 +3583,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125376408</v>
+        <v>125376417</v>
       </c>
       <c r="B32" t="n">
-        <v>90265</v>
+        <v>78726</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3607,21 +3606,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3631,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>809843</v>
+        <v>809807</v>
       </c>
       <c r="R32" t="n">
-        <v>7349800</v>
+        <v>7349660</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3675,6 +3674,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374876</v>
+        <v>125374093</v>
       </c>
       <c r="B43" t="n">
-        <v>92509</v>
+        <v>91485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809605</v>
+        <v>809619</v>
       </c>
       <c r="R43" t="n">
-        <v>7349541</v>
+        <v>7349622</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4742,29 +4742,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125373927</v>
+        <v>125374180</v>
       </c>
       <c r="B44" t="n">
-        <v>78373</v>
+        <v>92707</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4772,21 +4771,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4796,13 +4795,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809878</v>
+        <v>809528</v>
       </c>
       <c r="R44" t="n">
-        <v>7349722</v>
+        <v>7349612</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4846,19 +4845,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125373918</v>
+        <v>125374876</v>
       </c>
       <c r="B45" t="n">
         <v>92509</v>
@@ -4893,13 +4892,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809764</v>
+        <v>809605</v>
       </c>
       <c r="R45" t="n">
-        <v>7349945</v>
+        <v>7349541</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4937,50 +4936,51 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125374528</v>
+        <v>125373927</v>
       </c>
       <c r="B46" t="n">
-        <v>91454</v>
+        <v>78373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5260</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809822</v>
+        <v>809878</v>
       </c>
       <c r="R46" t="n">
-        <v>7349799</v>
+        <v>7349722</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5040,44 +5040,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374003</v>
+        <v>125373918</v>
       </c>
       <c r="B47" t="n">
-        <v>79585</v>
+        <v>92509</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>809619</v>
+        <v>809764</v>
       </c>
       <c r="R47" t="n">
-        <v>7349838</v>
+        <v>7349945</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5137,44 +5137,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125373954</v>
+        <v>125374528</v>
       </c>
       <c r="B48" t="n">
-        <v>92521</v>
+        <v>91454</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>5260</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809809</v>
+        <v>809822</v>
       </c>
       <c r="R48" t="n">
-        <v>7349982</v>
+        <v>7349799</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5234,44 +5234,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125373902</v>
+        <v>125374003</v>
       </c>
       <c r="B49" t="n">
-        <v>56843</v>
+        <v>79585</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5281,13 +5281,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>809943</v>
+        <v>809619</v>
       </c>
       <c r="R49" t="n">
-        <v>7349906</v>
+        <v>7349838</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5317,11 +5317,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5336,44 +5331,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125374093</v>
+        <v>125373954</v>
       </c>
       <c r="B50" t="n">
-        <v>91485</v>
+        <v>92521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>65</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5383,13 +5378,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>809619</v>
+        <v>809809</v>
       </c>
       <c r="R50" t="n">
-        <v>7349622</v>
+        <v>7349982</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5433,44 +5428,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125374180</v>
+        <v>125373902</v>
       </c>
       <c r="B51" t="n">
-        <v>92707</v>
+        <v>56843</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5480,13 +5475,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>809528</v>
+        <v>809943</v>
       </c>
       <c r="R51" t="n">
-        <v>7349612</v>
+        <v>7349906</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5516,6 +5511,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5530,12 +5530,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -9717,10 +9717,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125374087</v>
+        <v>125373960</v>
       </c>
       <c r="B95" t="n">
-        <v>78726</v>
+        <v>92707</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9728,21 +9728,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9752,13 +9752,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809592</v>
+        <v>809929</v>
       </c>
       <c r="R95" t="n">
-        <v>7349582</v>
+        <v>7349900</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9802,44 +9802,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374081</v>
+        <v>125374864</v>
       </c>
       <c r="B96" t="n">
-        <v>78726</v>
+        <v>91387</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9849,13 +9849,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809965</v>
+        <v>809790</v>
       </c>
       <c r="R96" t="n">
-        <v>7349845</v>
+        <v>7349726</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9893,63 +9893,64 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125373960</v>
+        <v>125374161</v>
       </c>
       <c r="B97" t="n">
-        <v>92707</v>
+        <v>91485</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809929</v>
+        <v>809457</v>
       </c>
       <c r="R97" t="n">
-        <v>7349900</v>
+        <v>7349587</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -9996,44 +9997,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125374864</v>
+        <v>125374087</v>
       </c>
       <c r="B98" t="n">
-        <v>91387</v>
+        <v>78726</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10043,13 +10044,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809790</v>
+        <v>809592</v>
       </c>
       <c r="R98" t="n">
-        <v>7349726</v>
+        <v>7349582</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10087,67 +10088,66 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374161</v>
+        <v>125374081</v>
       </c>
       <c r="B99" t="n">
-        <v>91485</v>
+        <v>78726</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809457</v>
+        <v>809965</v>
       </c>
       <c r="R99" t="n">
-        <v>7349587</v>
+        <v>7349845</v>
       </c>
       <c r="S99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10191,12 +10191,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -18577,10 +18577,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125374865</v>
+        <v>125374063</v>
       </c>
       <c r="B186" t="n">
-        <v>78726</v>
+        <v>90265</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18588,21 +18588,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18612,13 +18612,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>809649</v>
+        <v>809446</v>
       </c>
       <c r="R186" t="n">
-        <v>7349705</v>
+        <v>7349560</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -18662,44 +18662,44 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125374063</v>
+        <v>125373965</v>
       </c>
       <c r="B187" t="n">
-        <v>90265</v>
+        <v>91387</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18709,13 +18709,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>809446</v>
+        <v>809922</v>
       </c>
       <c r="R187" t="n">
-        <v>7349560</v>
+        <v>7349894</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18759,44 +18759,44 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125373965</v>
+        <v>125374865</v>
       </c>
       <c r="B188" t="n">
-        <v>91387</v>
+        <v>78726</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809922</v>
+        <v>809649</v>
       </c>
       <c r="R188" t="n">
-        <v>7349894</v>
+        <v>7349705</v>
       </c>
       <c r="S188" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -18856,44 +18856,44 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125374340</v>
+        <v>125374020</v>
       </c>
       <c r="B189" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809945</v>
+        <v>809655</v>
       </c>
       <c r="R189" t="n">
-        <v>7349970</v>
+        <v>7349698</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18939,11 +18939,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -18958,22 +18953,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125374020</v>
+        <v>125373959</v>
       </c>
       <c r="B190" t="n">
-        <v>78967</v>
+        <v>92501</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18981,21 +18976,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19005,13 +19000,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809655</v>
+        <v>809701</v>
       </c>
       <c r="R190" t="n">
-        <v>7349698</v>
+        <v>7349889</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19055,22 +19050,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125373959</v>
+        <v>125373997</v>
       </c>
       <c r="B191" t="n">
-        <v>92501</v>
+        <v>79585</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19078,21 +19073,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19102,13 +19097,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809701</v>
+        <v>809858</v>
       </c>
       <c r="R191" t="n">
-        <v>7349889</v>
+        <v>7349814</v>
       </c>
       <c r="S191" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19152,22 +19147,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125373997</v>
+        <v>125374907</v>
       </c>
       <c r="B192" t="n">
-        <v>79585</v>
+        <v>92503</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19175,21 +19170,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19199,10 +19194,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809858</v>
+        <v>809807</v>
       </c>
       <c r="R192" t="n">
-        <v>7349814</v>
+        <v>7349987</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19237,6 +19232,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -19249,44 +19249,44 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125374907</v>
+        <v>125374533</v>
       </c>
       <c r="B193" t="n">
-        <v>92503</v>
+        <v>92509</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19296,10 +19296,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809807</v>
+        <v>809958</v>
       </c>
       <c r="R193" t="n">
-        <v>7349987</v>
+        <v>7350004</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19334,11 +19334,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD193" t="b">
         <v>0</v>
       </c>
@@ -19351,19 +19346,19 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125374533</v>
+        <v>125373911</v>
       </c>
       <c r="B194" t="n">
         <v>92509</v>
@@ -19398,13 +19393,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809958</v>
+        <v>809707</v>
       </c>
       <c r="R194" t="n">
-        <v>7350004</v>
+        <v>7349576</v>
       </c>
       <c r="S194" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19448,22 +19443,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125373911</v>
+        <v>125374340</v>
       </c>
       <c r="B195" t="n">
-        <v>92509</v>
+        <v>56843</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19471,21 +19466,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19495,10 +19490,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>809707</v>
+        <v>809945</v>
       </c>
       <c r="R195" t="n">
-        <v>7349576</v>
+        <v>7349970</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -19533,6 +19528,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
@@ -19545,44 +19545,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125374532</v>
+        <v>125376416</v>
       </c>
       <c r="B196" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19592,13 +19592,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>809812</v>
+        <v>809489</v>
       </c>
       <c r="R196" t="n">
-        <v>7349817</v>
+        <v>7349695</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -19636,28 +19636,29 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125374911</v>
+        <v>125374867</v>
       </c>
       <c r="B197" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19665,21 +19666,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19689,10 +19690,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>809747</v>
+        <v>809521</v>
       </c>
       <c r="R197" t="n">
-        <v>7349880</v>
+        <v>7349655</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -19751,7 +19752,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125374883</v>
+        <v>125374532</v>
       </c>
       <c r="B198" t="n">
         <v>92509</v>
@@ -19786,10 +19787,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>809960</v>
+        <v>809812</v>
       </c>
       <c r="R198" t="n">
-        <v>7349967</v>
+        <v>7349817</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -19830,26 +19831,25 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125374036</v>
+        <v>125374911</v>
       </c>
       <c r="B199" t="n">
         <v>78373</v>
@@ -19884,10 +19884,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>809921</v>
+        <v>809747</v>
       </c>
       <c r="R199" t="n">
-        <v>7349943</v>
+        <v>7349880</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -19934,44 +19934,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125376414</v>
+        <v>125374883</v>
       </c>
       <c r="B200" t="n">
-        <v>92707</v>
+        <v>92509</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -19981,13 +19981,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>809561</v>
+        <v>809960</v>
       </c>
       <c r="R200" t="n">
-        <v>7349813</v>
+        <v>7349967</v>
       </c>
       <c r="S200" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -20025,28 +20025,29 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125376416</v>
+        <v>125374036</v>
       </c>
       <c r="B201" t="n">
-        <v>78726</v>
+        <v>78373</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20054,21 +20055,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20078,13 +20079,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>809489</v>
+        <v>809921</v>
       </c>
       <c r="R201" t="n">
-        <v>7349695</v>
+        <v>7349943</v>
       </c>
       <c r="S201" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20122,29 +20123,28 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125374867</v>
+        <v>125376414</v>
       </c>
       <c r="B202" t="n">
-        <v>78726</v>
+        <v>92707</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20152,21 +20152,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20176,13 +20176,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>809521</v>
+        <v>809561</v>
       </c>
       <c r="R202" t="n">
-        <v>7349655</v>
+        <v>7349813</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20226,12 +20226,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125374176</v>
       </c>
       <c r="B2" t="n">
-        <v>92537</v>
+        <v>92546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125373932</v>
       </c>
       <c r="B3" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125376401</v>
       </c>
       <c r="B4" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125373921</v>
       </c>
       <c r="B5" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125374896</v>
       </c>
       <c r="B6" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>125374026</v>
       </c>
       <c r="B7" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>125376413</v>
       </c>
       <c r="B8" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125376422</v>
+        <v>125374095</v>
       </c>
       <c r="B9" t="n">
-        <v>78373</v>
+        <v>78635</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>809622</v>
+        <v>809653</v>
       </c>
       <c r="R9" t="n">
-        <v>7349883</v>
+        <v>7349676</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1440,44 +1440,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125373999</v>
+        <v>125374870</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>91389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>809730</v>
+        <v>809852</v>
       </c>
       <c r="R10" t="n">
-        <v>7349926</v>
+        <v>7350051</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1537,44 +1537,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125374882</v>
+        <v>125376411</v>
       </c>
       <c r="B11" t="n">
-        <v>92509</v>
+        <v>92710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>809951</v>
+        <v>809462</v>
       </c>
       <c r="R11" t="n">
-        <v>7349924</v>
+        <v>7349673</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1628,51 +1628,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125374095</v>
+        <v>125376419</v>
       </c>
       <c r="B12" t="n">
-        <v>78634</v>
+        <v>91489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>809653</v>
+        <v>809843</v>
       </c>
       <c r="R12" t="n">
-        <v>7349676</v>
+        <v>7349800</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1732,44 +1731,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125374870</v>
+        <v>125373952</v>
       </c>
       <c r="B13" t="n">
-        <v>91387</v>
+        <v>56843</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1779,13 +1778,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>809852</v>
+        <v>809809</v>
       </c>
       <c r="R13" t="n">
-        <v>7350051</v>
+        <v>7349755</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1815,6 +1814,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1829,22 +1833,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125376411</v>
+        <v>125376422</v>
       </c>
       <c r="B14" t="n">
-        <v>92707</v>
+        <v>78374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1852,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1876,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>809462</v>
+        <v>809622</v>
       </c>
       <c r="R14" t="n">
-        <v>7349673</v>
+        <v>7349883</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1938,32 +1942,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125376419</v>
+        <v>125373999</v>
       </c>
       <c r="B15" t="n">
-        <v>91485</v>
+        <v>79586</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1973,13 +1977,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>809843</v>
+        <v>809730</v>
       </c>
       <c r="R15" t="n">
-        <v>7349800</v>
+        <v>7349926</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2023,44 +2027,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125376406</v>
+        <v>125374894</v>
       </c>
       <c r="B16" t="n">
-        <v>79556</v>
+        <v>92518</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2070,13 +2074,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>809747</v>
+        <v>809639</v>
       </c>
       <c r="R16" t="n">
-        <v>7349847</v>
+        <v>7349668</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2121,22 +2125,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125373952</v>
+        <v>125373912</v>
       </c>
       <c r="B17" t="n">
-        <v>56843</v>
+        <v>92518</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2144,21 +2148,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2168,13 +2172,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>809809</v>
+        <v>809755</v>
       </c>
       <c r="R17" t="n">
-        <v>7349755</v>
+        <v>7349675</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2204,11 +2208,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2223,22 +2222,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125374894</v>
+        <v>125374900</v>
       </c>
       <c r="B18" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,10 +2269,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>809639</v>
+        <v>809462</v>
       </c>
       <c r="R18" t="n">
-        <v>7349668</v>
+        <v>7349575</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2333,32 +2332,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125373912</v>
+        <v>125374544</v>
       </c>
       <c r="B19" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2368,13 +2367,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>809755</v>
+        <v>809669</v>
       </c>
       <c r="R19" t="n">
-        <v>7349675</v>
+        <v>7349819</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2418,22 +2417,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125374900</v>
+        <v>125374537</v>
       </c>
       <c r="B20" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2465,10 +2464,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>809462</v>
+        <v>809741</v>
       </c>
       <c r="R20" t="n">
-        <v>7349575</v>
+        <v>7349887</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2509,51 +2508,50 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125374544</v>
+        <v>125374882</v>
       </c>
       <c r="B21" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2563,10 +2561,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>809669</v>
+        <v>809951</v>
       </c>
       <c r="R21" t="n">
-        <v>7349819</v>
+        <v>7349924</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2607,28 +2605,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125374537</v>
+        <v>125373914</v>
       </c>
       <c r="B22" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2660,13 +2659,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>809741</v>
+        <v>809867</v>
       </c>
       <c r="R22" t="n">
-        <v>7349887</v>
+        <v>7349727</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2710,44 +2709,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125373914</v>
+        <v>125376406</v>
       </c>
       <c r="B23" t="n">
-        <v>92509</v>
+        <v>79557</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>809867</v>
+        <v>809747</v>
       </c>
       <c r="R23" t="n">
-        <v>7349727</v>
+        <v>7349847</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2801,50 +2800,51 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125374041</v>
+        <v>125374347</v>
       </c>
       <c r="B24" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>809655</v>
+        <v>809653</v>
       </c>
       <c r="R24" t="n">
-        <v>7349694</v>
+        <v>7349772</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2904,44 +2904,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125373973</v>
+        <v>125374041</v>
       </c>
       <c r="B25" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>809732</v>
+        <v>809655</v>
       </c>
       <c r="R25" t="n">
-        <v>7349587</v>
+        <v>7349694</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,44 +3001,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125374032</v>
+        <v>125373973</v>
       </c>
       <c r="B26" t="n">
-        <v>77916</v>
+        <v>92518</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,13 +3048,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>809628</v>
+        <v>809732</v>
       </c>
       <c r="R26" t="n">
-        <v>7349657</v>
+        <v>7349587</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3098,44 +3098,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125373910</v>
+        <v>125374032</v>
       </c>
       <c r="B27" t="n">
-        <v>92509</v>
+        <v>77917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,13 +3145,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>809589</v>
+        <v>809628</v>
       </c>
       <c r="R27" t="n">
-        <v>7349496</v>
+        <v>7349657</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3195,44 +3195,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125374022</v>
+        <v>125373910</v>
       </c>
       <c r="B28" t="n">
-        <v>78634</v>
+        <v>92518</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,13 +3242,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>809927</v>
+        <v>809589</v>
       </c>
       <c r="R28" t="n">
-        <v>7349959</v>
+        <v>7349496</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3292,22 +3292,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125374548</v>
+        <v>125376417</v>
       </c>
       <c r="B29" t="n">
-        <v>91241</v>
+        <v>78727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,21 +3315,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,13 +3339,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>809759</v>
+        <v>809807</v>
       </c>
       <c r="R29" t="n">
-        <v>7349927</v>
+        <v>7349660</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3383,28 +3383,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125376408</v>
+        <v>125374022</v>
       </c>
       <c r="B30" t="n">
-        <v>90265</v>
+        <v>78635</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,21 +3413,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3436,13 +3437,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>809843</v>
+        <v>809927</v>
       </c>
       <c r="R30" t="n">
-        <v>7349800</v>
+        <v>7349959</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3486,44 +3487,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125374347</v>
+        <v>125374548</v>
       </c>
       <c r="B31" t="n">
-        <v>92509</v>
+        <v>91242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3533,13 +3534,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>809653</v>
+        <v>809759</v>
       </c>
       <c r="R31" t="n">
-        <v>7349772</v>
+        <v>7349927</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3583,22 +3584,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125376417</v>
+        <v>125376408</v>
       </c>
       <c r="B32" t="n">
-        <v>78726</v>
+        <v>90266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,21 +3607,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3630,10 +3631,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>809807</v>
+        <v>809843</v>
       </c>
       <c r="R32" t="n">
-        <v>7349660</v>
+        <v>7349800</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3674,7 +3675,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>125374545</v>
       </c>
       <c r="B33" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>125373926</v>
       </c>
       <c r="B34" t="n">
-        <v>92503</v>
+        <v>92512</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>125374538</v>
       </c>
       <c r="B35" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
         <v>125373951</v>
       </c>
       <c r="B36" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>125373919</v>
       </c>
       <c r="B37" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>125374035</v>
       </c>
       <c r="B38" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>125373979</v>
       </c>
       <c r="B39" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         <v>125374016</v>
       </c>
       <c r="B40" t="n">
-        <v>80942</v>
+        <v>80943</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>125374015</v>
       </c>
       <c r="B41" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>125373905</v>
       </c>
       <c r="B42" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374093</v>
+        <v>125374876</v>
       </c>
       <c r="B43" t="n">
-        <v>91485</v>
+        <v>92518</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809619</v>
+        <v>809605</v>
       </c>
       <c r="R43" t="n">
-        <v>7349622</v>
+        <v>7349541</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4742,28 +4742,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374180</v>
+        <v>125373927</v>
       </c>
       <c r="B44" t="n">
-        <v>92707</v>
+        <v>78374</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4771,21 +4772,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,13 +4796,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809528</v>
+        <v>809878</v>
       </c>
       <c r="R44" t="n">
-        <v>7349612</v>
+        <v>7349722</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4845,22 +4846,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125374876</v>
+        <v>125373918</v>
       </c>
       <c r="B45" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4892,13 +4893,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809605</v>
+        <v>809764</v>
       </c>
       <c r="R45" t="n">
-        <v>7349541</v>
+        <v>7349945</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4936,51 +4937,50 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125373927</v>
+        <v>125374528</v>
       </c>
       <c r="B46" t="n">
-        <v>78373</v>
+        <v>91458</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>5260</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809878</v>
+        <v>809822</v>
       </c>
       <c r="R46" t="n">
-        <v>7349722</v>
+        <v>7349799</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5040,44 +5040,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125373918</v>
+        <v>125374003</v>
       </c>
       <c r="B47" t="n">
-        <v>92509</v>
+        <v>79586</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>809764</v>
+        <v>809619</v>
       </c>
       <c r="R47" t="n">
-        <v>7349945</v>
+        <v>7349838</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5137,44 +5137,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125374528</v>
+        <v>125373954</v>
       </c>
       <c r="B48" t="n">
-        <v>91454</v>
+        <v>92530</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5260</v>
+        <v>4366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809822</v>
+        <v>809809</v>
       </c>
       <c r="R48" t="n">
-        <v>7349799</v>
+        <v>7349982</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5234,44 +5234,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374003</v>
+        <v>125374093</v>
       </c>
       <c r="B49" t="n">
-        <v>79585</v>
+        <v>91489</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         <v>809619</v>
       </c>
       <c r="R49" t="n">
-        <v>7349838</v>
+        <v>7349622</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5331,44 +5331,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125373954</v>
+        <v>125374180</v>
       </c>
       <c r="B50" t="n">
-        <v>92521</v>
+        <v>92710</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>809809</v>
+        <v>809528</v>
       </c>
       <c r="R50" t="n">
-        <v>7349982</v>
+        <v>7349612</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5428,12 +5428,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5545,7 +5545,7 @@
         <v>125374083</v>
       </c>
       <c r="B52" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         <v>125374104</v>
       </c>
       <c r="B53" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>125374531</v>
       </c>
       <c r="B54" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>125374551</v>
       </c>
       <c r="B55" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>125373916</v>
       </c>
       <c r="B56" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>125373972</v>
       </c>
       <c r="B57" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>125376404</v>
       </c>
       <c r="B58" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>125373975</v>
       </c>
       <c r="B59" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>125374039</v>
       </c>
       <c r="B60" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>125374157</v>
       </c>
       <c r="B61" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>125374071</v>
       </c>
       <c r="B62" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>125374343</v>
       </c>
       <c r="B63" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6709,7 +6709,7 @@
         <v>125374069</v>
       </c>
       <c r="B64" t="n">
-        <v>92513</v>
+        <v>92522</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>125373969</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>125373957</v>
       </c>
       <c r="B66" t="n">
-        <v>92521</v>
+        <v>92530</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>125374529</v>
       </c>
       <c r="B67" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7097,7 +7097,7 @@
         <v>125374062</v>
       </c>
       <c r="B68" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>125373931</v>
       </c>
       <c r="B69" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>125374338</v>
       </c>
       <c r="B70" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>125374899</v>
       </c>
       <c r="B71" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>125374025</v>
       </c>
       <c r="B72" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>125376418</v>
       </c>
       <c r="B73" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>125374856</v>
       </c>
       <c r="B74" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>125374160</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>125374186</v>
       </c>
       <c r="B76" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>125374097</v>
       </c>
       <c r="B77" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>125374007</v>
       </c>
       <c r="B78" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>125374102</v>
       </c>
       <c r="B79" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>125376400</v>
       </c>
       <c r="B80" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>125374027</v>
       </c>
       <c r="B81" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8457,7 +8457,7 @@
         <v>125373915</v>
       </c>
       <c r="B82" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>125374889</v>
       </c>
       <c r="B83" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>125374072</v>
       </c>
       <c r="B84" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>125374077</v>
       </c>
       <c r="B85" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>125374024</v>
       </c>
       <c r="B86" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>125376415</v>
       </c>
       <c r="B87" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>125374903</v>
       </c>
       <c r="B88" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>125374005</v>
       </c>
       <c r="B89" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>125373913</v>
       </c>
       <c r="B90" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>125374909</v>
       </c>
       <c r="B91" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>125374037</v>
       </c>
       <c r="B92" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>125374043</v>
       </c>
       <c r="B93" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>125374350</v>
       </c>
       <c r="B94" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9717,10 +9717,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125373960</v>
+        <v>125374087</v>
       </c>
       <c r="B95" t="n">
-        <v>92707</v>
+        <v>78727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9728,21 +9728,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9752,13 +9752,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809929</v>
+        <v>809592</v>
       </c>
       <c r="R95" t="n">
-        <v>7349900</v>
+        <v>7349582</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9802,44 +9802,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374864</v>
+        <v>125374081</v>
       </c>
       <c r="B96" t="n">
-        <v>91387</v>
+        <v>78727</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9849,13 +9849,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809790</v>
+        <v>809965</v>
       </c>
       <c r="R96" t="n">
-        <v>7349726</v>
+        <v>7349845</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9893,64 +9893,63 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125374161</v>
+        <v>125373960</v>
       </c>
       <c r="B97" t="n">
-        <v>91485</v>
+        <v>92710</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809457</v>
+        <v>809929</v>
       </c>
       <c r="R97" t="n">
-        <v>7349587</v>
+        <v>7349900</v>
       </c>
       <c r="S97" t="n">
         <v>1</v>
@@ -9997,44 +9996,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125374087</v>
+        <v>125374864</v>
       </c>
       <c r="B98" t="n">
-        <v>78726</v>
+        <v>91389</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10044,13 +10043,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809592</v>
+        <v>809790</v>
       </c>
       <c r="R98" t="n">
-        <v>7349582</v>
+        <v>7349726</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10088,66 +10087,67 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374081</v>
+        <v>125374161</v>
       </c>
       <c r="B99" t="n">
-        <v>78726</v>
+        <v>91489</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809965</v>
+        <v>809457</v>
       </c>
       <c r="R99" t="n">
-        <v>7349845</v>
+        <v>7349587</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10191,12 +10191,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
         <v>125374905</v>
       </c>
       <c r="B100" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>125374107</v>
       </c>
       <c r="B101" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>125373998</v>
       </c>
       <c r="B102" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>125374857</v>
       </c>
       <c r="B103" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>125374006</v>
       </c>
       <c r="B104" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>125374067</v>
       </c>
       <c r="B105" t="n">
-        <v>92537</v>
+        <v>92546</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>125373922</v>
       </c>
       <c r="B106" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>125374013</v>
       </c>
       <c r="B107" t="n">
-        <v>78991</v>
+        <v>78992</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10979,32 +10979,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125373903</v>
+        <v>125374066</v>
       </c>
       <c r="B108" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>809878</v>
+        <v>809640</v>
       </c>
       <c r="R108" t="n">
-        <v>7349722</v>
+        <v>7349862</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11052,6 +11052,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11064,44 +11069,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125374066</v>
+        <v>125373903</v>
       </c>
       <c r="B109" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11111,10 +11116,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>809640</v>
+        <v>809878</v>
       </c>
       <c r="R109" t="n">
-        <v>7349862</v>
+        <v>7349722</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11149,11 +11154,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -11166,44 +11166,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125374011</v>
+        <v>125373924</v>
       </c>
       <c r="B110" t="n">
-        <v>57648</v>
+        <v>92518</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11213,13 +11213,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>809693</v>
+        <v>809702</v>
       </c>
       <c r="R110" t="n">
-        <v>7349989</v>
+        <v>7349703</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11263,22 +11263,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125373930</v>
+        <v>125374089</v>
       </c>
       <c r="B111" t="n">
-        <v>78373</v>
+        <v>78726</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>809731</v>
+        <v>809956</v>
       </c>
       <c r="R111" t="n">
-        <v>7349926</v>
+        <v>7349827</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11360,44 +11360,44 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125374100</v>
+        <v>125374011</v>
       </c>
       <c r="B112" t="n">
-        <v>92509</v>
+        <v>57648</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11407,13 +11407,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>809918</v>
+        <v>809693</v>
       </c>
       <c r="R112" t="n">
-        <v>7350040</v>
+        <v>7349989</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11457,44 +11457,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125374902</v>
+        <v>125373930</v>
       </c>
       <c r="B113" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11504,13 +11504,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>809413</v>
+        <v>809731</v>
       </c>
       <c r="R113" t="n">
-        <v>7349595</v>
+        <v>7349926</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11548,29 +11548,28 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125374541</v>
+        <v>125374100</v>
       </c>
       <c r="B114" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11602,13 +11601,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>809384</v>
+        <v>809918</v>
       </c>
       <c r="R114" t="n">
-        <v>7349553</v>
+        <v>7350040</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11652,44 +11651,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125374031</v>
+        <v>125374902</v>
       </c>
       <c r="B115" t="n">
-        <v>77916</v>
+        <v>92518</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11699,10 +11698,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>809617</v>
+        <v>809413</v>
       </c>
       <c r="R115" t="n">
-        <v>7349830</v>
+        <v>7349595</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11743,28 +11742,29 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125374895</v>
+        <v>125374541</v>
       </c>
       <c r="B116" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11796,10 +11796,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>809584</v>
+        <v>809384</v>
       </c>
       <c r="R116" t="n">
-        <v>7349617</v>
+        <v>7349553</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11840,29 +11840,28 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125373933</v>
+        <v>125374031</v>
       </c>
       <c r="B117" t="n">
-        <v>78373</v>
+        <v>77917</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11870,21 +11869,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11894,13 +11893,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>809589</v>
+        <v>809617</v>
       </c>
       <c r="R117" t="n">
-        <v>7349641</v>
+        <v>7349830</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11944,22 +11943,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125374098</v>
+        <v>125374895</v>
       </c>
       <c r="B118" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11991,13 +11990,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>809810</v>
+        <v>809584</v>
       </c>
       <c r="R118" t="n">
-        <v>7349749</v>
+        <v>7349617</v>
       </c>
       <c r="S118" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12035,28 +12034,29 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125373996</v>
+        <v>125373933</v>
       </c>
       <c r="B119" t="n">
-        <v>79585</v>
+        <v>78374</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12064,21 +12064,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12088,13 +12088,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>809856</v>
+        <v>809589</v>
       </c>
       <c r="R119" t="n">
-        <v>7349815</v>
+        <v>7349641</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12138,22 +12138,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125374540</v>
+        <v>125374098</v>
       </c>
       <c r="B120" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12185,13 +12185,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>809461</v>
+        <v>809810</v>
       </c>
       <c r="R120" t="n">
-        <v>7349612</v>
+        <v>7349749</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12235,44 +12235,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125373924</v>
+        <v>125373996</v>
       </c>
       <c r="B121" t="n">
-        <v>92509</v>
+        <v>79586</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12282,13 +12282,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>809702</v>
+        <v>809856</v>
       </c>
       <c r="R121" t="n">
-        <v>7349703</v>
+        <v>7349815</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12332,44 +12332,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125374089</v>
+        <v>125374540</v>
       </c>
       <c r="B122" t="n">
-        <v>78725</v>
+        <v>92518</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12379,13 +12379,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>809956</v>
+        <v>809461</v>
       </c>
       <c r="R122" t="n">
-        <v>7349827</v>
+        <v>7349612</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12429,12 +12429,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -12444,7 +12444,7 @@
         <v>125374034</v>
       </c>
       <c r="B123" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>125374527</v>
       </c>
       <c r="B124" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12638,7 +12638,7 @@
         <v>125374349</v>
       </c>
       <c r="B125" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>125376403</v>
       </c>
       <c r="B126" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>125374534</v>
       </c>
       <c r="B127" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>125374162</v>
       </c>
       <c r="B128" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>125373986</v>
       </c>
       <c r="B129" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>125373929</v>
       </c>
       <c r="B130" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>125374355</v>
       </c>
       <c r="B131" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>125374091</v>
       </c>
       <c r="B132" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>125374023</v>
       </c>
       <c r="B133" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>125374014</v>
       </c>
       <c r="B134" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13610,32 +13610,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125376407</v>
+        <v>125374530</v>
       </c>
       <c r="B135" t="n">
-        <v>79556</v>
+        <v>92518</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13645,13 +13645,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>809670</v>
+        <v>809468</v>
       </c>
       <c r="R135" t="n">
-        <v>7349836</v>
+        <v>7349525</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13689,51 +13689,50 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125374345</v>
+        <v>125374885</v>
       </c>
       <c r="B136" t="n">
-        <v>78726</v>
+        <v>92518</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13743,13 +13742,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>809504</v>
+        <v>809841</v>
       </c>
       <c r="R136" t="n">
-        <v>7349600</v>
+        <v>7350026</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13781,56 +13780,62 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125374530</v>
+        <v>125374543</v>
       </c>
       <c r="B137" t="n">
-        <v>92509</v>
+        <v>92512</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13840,10 +13845,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>809468</v>
+        <v>809962</v>
       </c>
       <c r="R137" t="n">
-        <v>7349525</v>
+        <v>7349982</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -13902,32 +13907,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125374885</v>
+        <v>125374178</v>
       </c>
       <c r="B138" t="n">
-        <v>92509</v>
+        <v>92546</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -13937,10 +13942,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>809841</v>
+        <v>809681</v>
       </c>
       <c r="R138" t="n">
-        <v>7350026</v>
+        <v>7349834</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -13975,40 +13980,34 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125374543</v>
+        <v>125374038</v>
       </c>
       <c r="B139" t="n">
-        <v>92503</v>
+        <v>78374</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14016,21 +14015,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14040,10 +14039,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>809962</v>
+        <v>809896</v>
       </c>
       <c r="R139" t="n">
-        <v>7349982</v>
+        <v>7350047</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14090,44 +14089,44 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125374178</v>
+        <v>125373967</v>
       </c>
       <c r="B140" t="n">
-        <v>92537</v>
+        <v>91389</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5449</v>
+        <v>1503</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14137,13 +14136,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>809681</v>
+        <v>809639</v>
       </c>
       <c r="R140" t="n">
-        <v>7349834</v>
+        <v>7349650</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14187,22 +14186,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125374038</v>
+        <v>125374079</v>
       </c>
       <c r="B141" t="n">
-        <v>78373</v>
+        <v>92710</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14210,21 +14209,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14234,13 +14233,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>809896</v>
+        <v>809474</v>
       </c>
       <c r="R141" t="n">
-        <v>7350047</v>
+        <v>7349542</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -14284,44 +14283,44 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125373967</v>
+        <v>125376407</v>
       </c>
       <c r="B142" t="n">
-        <v>91387</v>
+        <v>79557</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14331,13 +14330,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>809639</v>
+        <v>809670</v>
       </c>
       <c r="R142" t="n">
-        <v>7349650</v>
+        <v>7349836</v>
       </c>
       <c r="S142" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14375,28 +14374,29 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>125374079</v>
+        <v>125374345</v>
       </c>
       <c r="B143" t="n">
-        <v>92707</v>
+        <v>78727</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14404,21 +14404,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>809474</v>
+        <v>809504</v>
       </c>
       <c r="R143" t="n">
-        <v>7349542</v>
+        <v>7349600</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -14478,44 +14478,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>125374357</v>
+        <v>125374085</v>
       </c>
       <c r="B144" t="n">
-        <v>92509</v>
+        <v>78727</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14525,7 +14525,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>809654</v>
+        <v>809652</v>
       </c>
       <c r="R144" t="n">
         <v>7349686</v>
@@ -14575,22 +14575,22 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>125374536</v>
+        <v>125374357</v>
       </c>
       <c r="B145" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14622,13 +14622,13 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>809853</v>
+        <v>809654</v>
       </c>
       <c r="R145" t="n">
-        <v>7350024</v>
+        <v>7349686</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14672,22 +14672,22 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>125373920</v>
+        <v>125374536</v>
       </c>
       <c r="B146" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14719,13 +14719,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>809653</v>
+        <v>809853</v>
       </c>
       <c r="R146" t="n">
-        <v>7349680</v>
+        <v>7350024</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14769,22 +14769,22 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125374890</v>
+        <v>125373920</v>
       </c>
       <c r="B147" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>809679</v>
+        <v>809653</v>
       </c>
       <c r="R147" t="n">
-        <v>7349836</v>
+        <v>7349680</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14860,29 +14860,28 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>125374359</v>
+        <v>125373989</v>
       </c>
       <c r="B148" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14914,13 +14913,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>809597</v>
+        <v>809653</v>
       </c>
       <c r="R148" t="n">
-        <v>7349492</v>
+        <v>7349741</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14964,22 +14963,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125373989</v>
+        <v>125374890</v>
       </c>
       <c r="B149" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15011,13 +15010,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>809653</v>
+        <v>809679</v>
       </c>
       <c r="R149" t="n">
-        <v>7349741</v>
+        <v>7349836</v>
       </c>
       <c r="S149" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -15055,50 +15054,51 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125374002</v>
+        <v>125374359</v>
       </c>
       <c r="B150" t="n">
-        <v>79585</v>
+        <v>92518</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15108,13 +15108,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>809718</v>
+        <v>809597</v>
       </c>
       <c r="R150" t="n">
-        <v>7349928</v>
+        <v>7349492</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -15158,22 +15158,22 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125374018</v>
+        <v>125374002</v>
       </c>
       <c r="B151" t="n">
-        <v>78725</v>
+        <v>79586</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15181,21 +15181,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15205,10 +15205,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>809857</v>
+        <v>809718</v>
       </c>
       <c r="R151" t="n">
-        <v>7349810</v>
+        <v>7349928</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15267,32 +15267,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>125374878</v>
+        <v>125374018</v>
       </c>
       <c r="B152" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15302,10 +15302,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>809856</v>
+        <v>809857</v>
       </c>
       <c r="R152" t="n">
-        <v>7349729</v>
+        <v>7349810</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15346,51 +15346,50 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>125374033</v>
+        <v>125374878</v>
       </c>
       <c r="B153" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15400,10 +15399,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>809646</v>
+        <v>809856</v>
       </c>
       <c r="R153" t="n">
-        <v>7349532</v>
+        <v>7349729</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15444,50 +15443,51 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>125374887</v>
+        <v>125374033</v>
       </c>
       <c r="B154" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15497,10 +15497,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>809704</v>
+        <v>809646</v>
       </c>
       <c r="R154" t="n">
-        <v>7349885</v>
+        <v>7349532</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -15541,51 +15541,50 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>125374526</v>
+        <v>125374887</v>
       </c>
       <c r="B155" t="n">
-        <v>92707</v>
+        <v>92518</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15595,10 +15594,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>809830</v>
+        <v>809704</v>
       </c>
       <c r="R155" t="n">
-        <v>7349803</v>
+        <v>7349885</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -15639,28 +15638,29 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125376410</v>
+        <v>125374526</v>
       </c>
       <c r="B156" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15692,13 +15692,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>809454</v>
+        <v>809830</v>
       </c>
       <c r="R156" t="n">
-        <v>7349679</v>
+        <v>7349803</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -15742,22 +15742,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>125374085</v>
+        <v>125376410</v>
       </c>
       <c r="B157" t="n">
-        <v>78726</v>
+        <v>92710</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15765,21 +15765,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>809652</v>
+        <v>809454</v>
       </c>
       <c r="R157" t="n">
-        <v>7349686</v>
+        <v>7349679</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -15839,22 +15839,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>125373900</v>
+        <v>125373906</v>
       </c>
       <c r="B158" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15862,21 +15862,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -15886,10 +15886,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>809545</v>
+        <v>809624</v>
       </c>
       <c r="R158" t="n">
-        <v>7349602</v>
+        <v>7349838</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -15948,10 +15948,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>125376402</v>
+        <v>125373900</v>
       </c>
       <c r="B159" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -15983,10 +15983,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>809636</v>
+        <v>809545</v>
       </c>
       <c r="R159" t="n">
-        <v>7349511</v>
+        <v>7349602</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -16033,44 +16033,44 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>125374873</v>
+        <v>125376402</v>
       </c>
       <c r="B160" t="n">
-        <v>92509</v>
+        <v>79586</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16080,13 +16080,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>809452</v>
+        <v>809636</v>
       </c>
       <c r="R160" t="n">
-        <v>7349512</v>
+        <v>7349511</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16124,29 +16124,28 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>125374182</v>
+        <v>125374873</v>
       </c>
       <c r="B161" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16178,10 +16177,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>809522</v>
+        <v>809452</v>
       </c>
       <c r="R161" t="n">
-        <v>7349734</v>
+        <v>7349512</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16222,28 +16221,29 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>125374352</v>
+        <v>125374182</v>
       </c>
       <c r="B162" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16275,13 +16275,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>809944</v>
+        <v>809522</v>
       </c>
       <c r="R162" t="n">
-        <v>7349910</v>
+        <v>7349734</v>
       </c>
       <c r="S162" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16325,22 +16325,22 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>125373992</v>
+        <v>125374352</v>
       </c>
       <c r="B163" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16372,13 +16372,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>809588</v>
+        <v>809944</v>
       </c>
       <c r="R163" t="n">
-        <v>7349579</v>
+        <v>7349910</v>
       </c>
       <c r="S163" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -16422,44 +16422,44 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>125373995</v>
+        <v>125373992</v>
       </c>
       <c r="B164" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16469,10 +16469,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>809732</v>
+        <v>809588</v>
       </c>
       <c r="R164" t="n">
-        <v>7349917</v>
+        <v>7349579</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
@@ -16531,32 +16531,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125373982</v>
+        <v>125373995</v>
       </c>
       <c r="B165" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>809864</v>
+        <v>809732</v>
       </c>
       <c r="R165" t="n">
-        <v>7349953</v>
+        <v>7349917</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -16628,32 +16628,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125374179</v>
+        <v>125373982</v>
       </c>
       <c r="B166" t="n">
-        <v>92537</v>
+        <v>92518</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16663,13 +16663,13 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>809720</v>
+        <v>809864</v>
       </c>
       <c r="R166" t="n">
-        <v>7349861</v>
+        <v>7349953</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -16713,44 +16713,44 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>125374881</v>
+        <v>125374179</v>
       </c>
       <c r="B167" t="n">
-        <v>92509</v>
+        <v>92546</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16760,10 +16760,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>809888</v>
+        <v>809720</v>
       </c>
       <c r="R167" t="n">
-        <v>7349802</v>
+        <v>7349861</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -16804,29 +16804,28 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>125374187</v>
+        <v>125374881</v>
       </c>
       <c r="B168" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16858,10 +16857,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>809659</v>
+        <v>809888</v>
       </c>
       <c r="R168" t="n">
-        <v>7349773</v>
+        <v>7349802</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -16902,50 +16901,51 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>125373906</v>
+        <v>125374187</v>
       </c>
       <c r="B169" t="n">
-        <v>78726</v>
+        <v>92518</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>809624</v>
+        <v>809659</v>
       </c>
       <c r="R169" t="n">
-        <v>7349838</v>
+        <v>7349773</v>
       </c>
       <c r="S169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17005,12 +17005,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
@@ -17020,7 +17020,7 @@
         <v>125374021</v>
       </c>
       <c r="B170" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>125374549</v>
       </c>
       <c r="B171" t="n">
-        <v>91485</v>
+        <v>91489</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>125374019</v>
       </c>
       <c r="B172" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>125374539</v>
       </c>
       <c r="B173" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>125374177</v>
       </c>
       <c r="B174" t="n">
-        <v>92537</v>
+        <v>92546</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>125373983</v>
       </c>
       <c r="B175" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>125373993</v>
       </c>
       <c r="B176" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>125374008</v>
       </c>
       <c r="B177" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>125374875</v>
       </c>
       <c r="B178" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>125374886</v>
       </c>
       <c r="B179" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>125374184</v>
       </c>
       <c r="B180" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18086,32 +18086,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>125376405</v>
+        <v>125373907</v>
       </c>
       <c r="B181" t="n">
-        <v>79556</v>
+        <v>91389</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18121,10 +18121,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>809469</v>
+        <v>809608</v>
       </c>
       <c r="R181" t="n">
-        <v>7349711</v>
+        <v>7349636</v>
       </c>
       <c r="S181" t="n">
         <v>5</v>
@@ -18165,29 +18165,28 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>125373907</v>
+        <v>125374872</v>
       </c>
       <c r="B182" t="n">
-        <v>91387</v>
+        <v>91489</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18195,21 +18194,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18219,13 +18218,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>809608</v>
+        <v>809657</v>
       </c>
       <c r="R182" t="n">
-        <v>7349636</v>
+        <v>7349679</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18269,44 +18268,44 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>125374872</v>
+        <v>125374342</v>
       </c>
       <c r="B183" t="n">
-        <v>91485</v>
+        <v>92710</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18316,13 +18315,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>809657</v>
+        <v>809935</v>
       </c>
       <c r="R183" t="n">
-        <v>7349679</v>
+        <v>7350019</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -18366,60 +18365,60 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>125374342</v>
+        <v>125374153</v>
       </c>
       <c r="B184" t="n">
-        <v>92707</v>
+        <v>56843</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>809935</v>
+        <v>809919</v>
       </c>
       <c r="R184" t="n">
-        <v>7350019</v>
+        <v>7349964</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -18449,6 +18448,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Spillning rikligt</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -18463,60 +18467,60 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>125374153</v>
+        <v>125376405</v>
       </c>
       <c r="B185" t="n">
-        <v>56843</v>
+        <v>79557</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>809919</v>
+        <v>809469</v>
       </c>
       <c r="R185" t="n">
-        <v>7349964</v>
+        <v>7349711</v>
       </c>
       <c r="S185" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -18548,29 +18552,25 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Spillning rikligt</t>
-        </is>
-      </c>
       <c r="AD185" t="b">
         <v>0</v>
       </c>
       <c r="AE185" t="b">
         <v>0</v>
       </c>
+      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
@@ -18580,7 +18580,7 @@
         <v>125374063</v>
       </c>
       <c r="B186" t="n">
-        <v>90265</v>
+        <v>90266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>125373965</v>
       </c>
       <c r="B187" t="n">
-        <v>91387</v>
+        <v>91389</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18771,10 +18771,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125374865</v>
+        <v>125374020</v>
       </c>
       <c r="B188" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18782,21 +18782,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18806,10 +18806,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809649</v>
+        <v>809655</v>
       </c>
       <c r="R188" t="n">
-        <v>7349705</v>
+        <v>7349698</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -18856,22 +18856,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125374020</v>
+        <v>125373959</v>
       </c>
       <c r="B189" t="n">
-        <v>78967</v>
+        <v>92510</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18879,21 +18879,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809655</v>
+        <v>809701</v>
       </c>
       <c r="R189" t="n">
-        <v>7349698</v>
+        <v>7349889</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18953,22 +18953,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125373959</v>
+        <v>125373997</v>
       </c>
       <c r="B190" t="n">
-        <v>92501</v>
+        <v>79586</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -18976,21 +18976,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19000,13 +19000,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809701</v>
+        <v>809858</v>
       </c>
       <c r="R190" t="n">
-        <v>7349889</v>
+        <v>7349814</v>
       </c>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19050,22 +19050,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125373997</v>
+        <v>125374907</v>
       </c>
       <c r="B191" t="n">
-        <v>79585</v>
+        <v>92512</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19073,21 +19073,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19097,10 +19097,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809858</v>
+        <v>809807</v>
       </c>
       <c r="R191" t="n">
-        <v>7349814</v>
+        <v>7349987</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -19135,6 +19135,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
+        </is>
+      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
@@ -19147,44 +19152,44 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125374907</v>
+        <v>125374533</v>
       </c>
       <c r="B192" t="n">
-        <v>92503</v>
+        <v>92518</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19194,10 +19199,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809807</v>
+        <v>809958</v>
       </c>
       <c r="R192" t="n">
-        <v>7349987</v>
+        <v>7350004</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -19232,11 +19237,6 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
@@ -19249,22 +19249,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125374533</v>
+        <v>125373911</v>
       </c>
       <c r="B193" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19296,13 +19296,13 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809958</v>
+        <v>809707</v>
       </c>
       <c r="R193" t="n">
-        <v>7350004</v>
+        <v>7349576</v>
       </c>
       <c r="S193" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -19346,22 +19346,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125373911</v>
+        <v>125374340</v>
       </c>
       <c r="B194" t="n">
-        <v>92509</v>
+        <v>56843</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19369,21 +19369,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19393,10 +19393,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809707</v>
+        <v>809945</v>
       </c>
       <c r="R194" t="n">
-        <v>7349576</v>
+        <v>7349970</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -19431,6 +19431,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD194" t="b">
         <v>0</v>
       </c>
@@ -19443,44 +19448,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125374340</v>
+        <v>125374865</v>
       </c>
       <c r="B195" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19490,13 +19495,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>809945</v>
+        <v>809649</v>
       </c>
       <c r="R195" t="n">
-        <v>7349970</v>
+        <v>7349705</v>
       </c>
       <c r="S195" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19526,11 +19531,6 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -19545,44 +19545,44 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125376416</v>
+        <v>125374532</v>
       </c>
       <c r="B196" t="n">
-        <v>78726</v>
+        <v>92518</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19592,13 +19592,13 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>809489</v>
+        <v>809812</v>
       </c>
       <c r="R196" t="n">
-        <v>7349695</v>
+        <v>7349817</v>
       </c>
       <c r="S196" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -19636,29 +19636,28 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125374867</v>
+        <v>125374911</v>
       </c>
       <c r="B197" t="n">
-        <v>78726</v>
+        <v>78374</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19666,21 +19665,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19690,10 +19689,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>809521</v>
+        <v>809747</v>
       </c>
       <c r="R197" t="n">
-        <v>7349655</v>
+        <v>7349880</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -19752,10 +19751,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125374532</v>
+        <v>125374883</v>
       </c>
       <c r="B198" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19787,10 +19786,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>809812</v>
+        <v>809960</v>
       </c>
       <c r="R198" t="n">
-        <v>7349817</v>
+        <v>7349967</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -19831,28 +19830,29 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125374911</v>
+        <v>125374036</v>
       </c>
       <c r="B199" t="n">
-        <v>78373</v>
+        <v>78374</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19884,10 +19884,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>809747</v>
+        <v>809921</v>
       </c>
       <c r="R199" t="n">
-        <v>7349880</v>
+        <v>7349943</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -19934,44 +19934,44 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125374883</v>
+        <v>125376414</v>
       </c>
       <c r="B200" t="n">
-        <v>92509</v>
+        <v>92710</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -19981,13 +19981,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>809960</v>
+        <v>809561</v>
       </c>
       <c r="R200" t="n">
-        <v>7349967</v>
+        <v>7349813</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -20025,29 +20025,28 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125374036</v>
+        <v>125376416</v>
       </c>
       <c r="B201" t="n">
-        <v>78373</v>
+        <v>78727</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20055,21 +20054,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -20079,13 +20078,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>809921</v>
+        <v>809489</v>
       </c>
       <c r="R201" t="n">
-        <v>7349943</v>
+        <v>7349695</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -20123,28 +20122,29 @@
       <c r="AE201" t="b">
         <v>0</v>
       </c>
+      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125376414</v>
+        <v>125374867</v>
       </c>
       <c r="B202" t="n">
-        <v>92707</v>
+        <v>78727</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -20152,21 +20152,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20176,13 +20176,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>809561</v>
+        <v>809521</v>
       </c>
       <c r="R202" t="n">
-        <v>7349813</v>
+        <v>7349655</v>
       </c>
       <c r="S202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -20226,44 +20226,44 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125373909</v>
+        <v>125374354</v>
       </c>
       <c r="B203" t="n">
-        <v>91485</v>
+        <v>92518</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -20273,10 +20273,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>809626</v>
+        <v>809669</v>
       </c>
       <c r="R203" t="n">
-        <v>7349810</v>
+        <v>7349770</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -20323,22 +20323,22 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>125373962</v>
+        <v>125373928</v>
       </c>
       <c r="B204" t="n">
-        <v>92707</v>
+        <v>78374</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -20346,21 +20346,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -20370,13 +20370,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>809641</v>
+        <v>809661</v>
       </c>
       <c r="R204" t="n">
-        <v>7349649</v>
+        <v>7349566</v>
       </c>
       <c r="S204" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -20420,22 +20420,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>125374354</v>
+        <v>125373988</v>
       </c>
       <c r="B205" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -20467,13 +20467,13 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>809669</v>
+        <v>809651</v>
       </c>
       <c r="R205" t="n">
-        <v>7349770</v>
+        <v>7349747</v>
       </c>
       <c r="S205" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -20517,44 +20517,44 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>125373928</v>
+        <v>125374880</v>
       </c>
       <c r="B206" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -20564,13 +20564,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>809661</v>
+        <v>809785</v>
       </c>
       <c r="R206" t="n">
-        <v>7349566</v>
+        <v>7349769</v>
       </c>
       <c r="S206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -20608,28 +20608,29 @@
       <c r="AE206" t="b">
         <v>0</v>
       </c>
+      <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>125373988</v>
+        <v>125373978</v>
       </c>
       <c r="B207" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -20661,10 +20662,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>809651</v>
+        <v>809758</v>
       </c>
       <c r="R207" t="n">
-        <v>7349747</v>
+        <v>7349662</v>
       </c>
       <c r="S207" t="n">
         <v>1</v>
@@ -20723,32 +20724,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>125374880</v>
+        <v>125374042</v>
       </c>
       <c r="B208" t="n">
-        <v>92509</v>
+        <v>78374</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -20758,10 +20759,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>809785</v>
+        <v>809583</v>
       </c>
       <c r="R208" t="n">
-        <v>7349769</v>
+        <v>7349591</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -20802,51 +20803,50 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>125373978</v>
+        <v>125374854</v>
       </c>
       <c r="B209" t="n">
-        <v>92509</v>
+        <v>79586</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -20856,13 +20856,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>809758</v>
+        <v>809581</v>
       </c>
       <c r="R209" t="n">
-        <v>7349662</v>
+        <v>7349510</v>
       </c>
       <c r="S209" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -20906,44 +20906,44 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125374042</v>
+        <v>125374891</v>
       </c>
       <c r="B210" t="n">
-        <v>78373</v>
+        <v>92518</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -20953,10 +20953,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>809583</v>
+        <v>809618</v>
       </c>
       <c r="R210" t="n">
-        <v>7349591</v>
+        <v>7349662</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -20997,28 +20997,29 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
+      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125374854</v>
+        <v>125373899</v>
       </c>
       <c r="B211" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -21050,13 +21051,13 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>809581</v>
+        <v>809933</v>
       </c>
       <c r="R211" t="n">
-        <v>7349510</v>
+        <v>7349784</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -21100,44 +21101,44 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>125374891</v>
+        <v>125374030</v>
       </c>
       <c r="B212" t="n">
-        <v>92509</v>
+        <v>77917</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -21147,10 +21148,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>809618</v>
+        <v>809944</v>
       </c>
       <c r="R212" t="n">
-        <v>7349662</v>
+        <v>7350018</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -21191,51 +21192,50 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>125373899</v>
+        <v>125373909</v>
       </c>
       <c r="B213" t="n">
-        <v>79585</v>
+        <v>91489</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -21245,10 +21245,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>809933</v>
+        <v>809626</v>
       </c>
       <c r="R213" t="n">
-        <v>7349784</v>
+        <v>7349810</v>
       </c>
       <c r="S213" t="n">
         <v>5</v>
@@ -21307,10 +21307,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>125374030</v>
+        <v>125373962</v>
       </c>
       <c r="B214" t="n">
-        <v>77916</v>
+        <v>92710</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -21318,21 +21318,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -21342,13 +21342,13 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>809944</v>
+        <v>809641</v>
       </c>
       <c r="R214" t="n">
-        <v>7350018</v>
+        <v>7349649</v>
       </c>
       <c r="S214" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -21392,12 +21392,12 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
@@ -21407,7 +21407,7 @@
         <v>125373964</v>
       </c>
       <c r="B215" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>125374029</v>
       </c>
       <c r="B216" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -21601,7 +21601,7 @@
         <v>125374028</v>
       </c>
       <c r="B217" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -21698,7 +21698,7 @@
         <v>125373985</v>
       </c>
       <c r="B218" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>125374074</v>
       </c>
       <c r="B219" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374876</v>
+        <v>125374093</v>
       </c>
       <c r="B43" t="n">
-        <v>92518</v>
+        <v>91489</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809605</v>
+        <v>809619</v>
       </c>
       <c r="R43" t="n">
-        <v>7349541</v>
+        <v>7349622</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4742,29 +4742,28 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125373927</v>
+        <v>125374180</v>
       </c>
       <c r="B44" t="n">
-        <v>78374</v>
+        <v>92710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4772,21 +4771,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4796,13 +4795,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809878</v>
+        <v>809528</v>
       </c>
       <c r="R44" t="n">
-        <v>7349722</v>
+        <v>7349612</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4846,19 +4845,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125373918</v>
+        <v>125374876</v>
       </c>
       <c r="B45" t="n">
         <v>92518</v>
@@ -4893,13 +4892,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809764</v>
+        <v>809605</v>
       </c>
       <c r="R45" t="n">
-        <v>7349945</v>
+        <v>7349541</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4937,50 +4936,51 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125374528</v>
+        <v>125373927</v>
       </c>
       <c r="B46" t="n">
-        <v>91458</v>
+        <v>78374</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5260</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4990,13 +4990,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809822</v>
+        <v>809878</v>
       </c>
       <c r="R46" t="n">
-        <v>7349799</v>
+        <v>7349722</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5040,44 +5040,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374003</v>
+        <v>125373918</v>
       </c>
       <c r="B47" t="n">
-        <v>79586</v>
+        <v>92518</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>809619</v>
+        <v>809764</v>
       </c>
       <c r="R47" t="n">
-        <v>7349838</v>
+        <v>7349945</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5137,44 +5137,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125373954</v>
+        <v>125374528</v>
       </c>
       <c r="B48" t="n">
-        <v>92530</v>
+        <v>91458</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4366</v>
+        <v>5260</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809809</v>
+        <v>809822</v>
       </c>
       <c r="R48" t="n">
-        <v>7349982</v>
+        <v>7349799</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5234,44 +5234,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374093</v>
+        <v>125374003</v>
       </c>
       <c r="B49" t="n">
-        <v>91489</v>
+        <v>79586</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5284,10 +5284,10 @@
         <v>809619</v>
       </c>
       <c r="R49" t="n">
-        <v>7349622</v>
+        <v>7349838</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5331,44 +5331,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125374180</v>
+        <v>125373954</v>
       </c>
       <c r="B50" t="n">
-        <v>92710</v>
+        <v>92530</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>809528</v>
+        <v>809809</v>
       </c>
       <c r="R50" t="n">
-        <v>7349612</v>
+        <v>7349982</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5428,12 +5428,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -11178,32 +11178,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125373924</v>
+        <v>125373930</v>
       </c>
       <c r="B110" t="n">
-        <v>92518</v>
+        <v>78374</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>809702</v>
+        <v>809731</v>
       </c>
       <c r="R110" t="n">
-        <v>7349703</v>
+        <v>7349926</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11275,32 +11275,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125374089</v>
+        <v>125374100</v>
       </c>
       <c r="B111" t="n">
-        <v>78726</v>
+        <v>92518</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>809956</v>
+        <v>809918</v>
       </c>
       <c r="R111" t="n">
-        <v>7349827</v>
+        <v>7350040</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11372,32 +11372,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125374011</v>
+        <v>125374902</v>
       </c>
       <c r="B112" t="n">
-        <v>57648</v>
+        <v>92518</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11407,10 +11407,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>809693</v>
+        <v>809413</v>
       </c>
       <c r="R112" t="n">
-        <v>7349989</v>
+        <v>7349595</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11451,50 +11451,51 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125373930</v>
+        <v>125374541</v>
       </c>
       <c r="B113" t="n">
-        <v>78374</v>
+        <v>92518</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11504,13 +11505,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>809731</v>
+        <v>809384</v>
       </c>
       <c r="R113" t="n">
-        <v>7349926</v>
+        <v>7349553</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11554,44 +11555,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125374100</v>
+        <v>125374031</v>
       </c>
       <c r="B114" t="n">
-        <v>92518</v>
+        <v>77917</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11601,13 +11602,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>809918</v>
+        <v>809617</v>
       </c>
       <c r="R114" t="n">
-        <v>7350040</v>
+        <v>7349830</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11651,19 +11652,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125374902</v>
+        <v>125374895</v>
       </c>
       <c r="B115" t="n">
         <v>92518</v>
@@ -11698,10 +11699,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>809413</v>
+        <v>809584</v>
       </c>
       <c r="R115" t="n">
-        <v>7349595</v>
+        <v>7349617</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11761,32 +11762,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125374541</v>
+        <v>125373933</v>
       </c>
       <c r="B116" t="n">
-        <v>92518</v>
+        <v>78374</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11796,13 +11797,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>809384</v>
+        <v>809589</v>
       </c>
       <c r="R116" t="n">
-        <v>7349553</v>
+        <v>7349641</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11846,44 +11847,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125374031</v>
+        <v>125374098</v>
       </c>
       <c r="B117" t="n">
-        <v>77917</v>
+        <v>92518</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11893,13 +11894,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>809617</v>
+        <v>809810</v>
       </c>
       <c r="R117" t="n">
-        <v>7349830</v>
+        <v>7349749</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11943,44 +11944,44 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125374895</v>
+        <v>125373996</v>
       </c>
       <c r="B118" t="n">
-        <v>92518</v>
+        <v>79586</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -11990,10 +11991,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>809584</v>
+        <v>809856</v>
       </c>
       <c r="R118" t="n">
-        <v>7349617</v>
+        <v>7349815</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12034,51 +12035,50 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125373933</v>
+        <v>125374540</v>
       </c>
       <c r="B119" t="n">
-        <v>78374</v>
+        <v>92518</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12088,13 +12088,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>809589</v>
+        <v>809461</v>
       </c>
       <c r="R119" t="n">
-        <v>7349641</v>
+        <v>7349612</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12138,19 +12138,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125374098</v>
+        <v>125373924</v>
       </c>
       <c r="B120" t="n">
         <v>92518</v>
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>809810</v>
+        <v>809702</v>
       </c>
       <c r="R120" t="n">
-        <v>7349749</v>
+        <v>7349703</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12235,22 +12235,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125373996</v>
+        <v>125374089</v>
       </c>
       <c r="B121" t="n">
-        <v>79586</v>
+        <v>78726</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12258,21 +12258,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12282,13 +12282,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>809856</v>
+        <v>809956</v>
       </c>
       <c r="R121" t="n">
-        <v>7349815</v>
+        <v>7349827</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12332,44 +12332,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125374540</v>
+        <v>125374034</v>
       </c>
       <c r="B122" t="n">
-        <v>92518</v>
+        <v>78374</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12379,10 +12379,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>809461</v>
+        <v>809797</v>
       </c>
       <c r="R122" t="n">
-        <v>7349612</v>
+        <v>7349716</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12429,22 +12429,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125374034</v>
+        <v>125374527</v>
       </c>
       <c r="B123" t="n">
-        <v>78374</v>
+        <v>92710</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12452,21 +12452,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12476,10 +12476,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>809797</v>
+        <v>809621</v>
       </c>
       <c r="R123" t="n">
-        <v>7349716</v>
+        <v>7349643</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12526,22 +12526,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125374527</v>
+        <v>125374011</v>
       </c>
       <c r="B124" t="n">
-        <v>92710</v>
+        <v>57648</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12549,21 +12549,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2079</v>
+        <v>100049</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12573,10 +12573,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>809621</v>
+        <v>809693</v>
       </c>
       <c r="R124" t="n">
-        <v>7349643</v>
+        <v>7349989</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12623,12 +12623,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -18577,10 +18577,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125374063</v>
+        <v>125374020</v>
       </c>
       <c r="B186" t="n">
-        <v>90266</v>
+        <v>78968</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18588,21 +18588,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18612,13 +18612,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>809446</v>
+        <v>809655</v>
       </c>
       <c r="R186" t="n">
-        <v>7349560</v>
+        <v>7349698</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -18662,44 +18662,44 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125373965</v>
+        <v>125373959</v>
       </c>
       <c r="B187" t="n">
-        <v>91389</v>
+        <v>92510</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1503</v>
+        <v>4361</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18709,10 +18709,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>809922</v>
+        <v>809701</v>
       </c>
       <c r="R187" t="n">
-        <v>7349894</v>
+        <v>7349889</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -18771,10 +18771,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125374020</v>
+        <v>125373997</v>
       </c>
       <c r="B188" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18782,21 +18782,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18806,10 +18806,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809655</v>
+        <v>809858</v>
       </c>
       <c r="R188" t="n">
-        <v>7349698</v>
+        <v>7349814</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -18868,10 +18868,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125373959</v>
+        <v>125374907</v>
       </c>
       <c r="B189" t="n">
-        <v>92510</v>
+        <v>92512</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18879,21 +18879,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809701</v>
+        <v>809807</v>
       </c>
       <c r="R189" t="n">
-        <v>7349889</v>
+        <v>7349987</v>
       </c>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18939,6 +18939,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -18953,44 +18958,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125373997</v>
+        <v>125374533</v>
       </c>
       <c r="B190" t="n">
-        <v>79586</v>
+        <v>92518</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19000,10 +19005,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809858</v>
+        <v>809958</v>
       </c>
       <c r="R190" t="n">
-        <v>7349814</v>
+        <v>7350004</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19050,44 +19055,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125374907</v>
+        <v>125373911</v>
       </c>
       <c r="B191" t="n">
-        <v>92512</v>
+        <v>92518</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19097,13 +19102,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809807</v>
+        <v>809707</v>
       </c>
       <c r="R191" t="n">
-        <v>7349987</v>
+        <v>7349576</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19133,11 +19138,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -19152,22 +19152,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125374533</v>
+        <v>125374340</v>
       </c>
       <c r="B192" t="n">
-        <v>92518</v>
+        <v>56843</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19175,21 +19175,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19199,13 +19199,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809958</v>
+        <v>809945</v>
       </c>
       <c r="R192" t="n">
-        <v>7350004</v>
+        <v>7349970</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -19235,6 +19235,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19249,44 +19254,44 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125373911</v>
+        <v>125374063</v>
       </c>
       <c r="B193" t="n">
-        <v>92518</v>
+        <v>90266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19296,10 +19301,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809707</v>
+        <v>809446</v>
       </c>
       <c r="R193" t="n">
-        <v>7349576</v>
+        <v>7349560</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -19346,44 +19351,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125374340</v>
+        <v>125373965</v>
       </c>
       <c r="B194" t="n">
-        <v>56843</v>
+        <v>91389</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19393,13 +19398,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809945</v>
+        <v>809922</v>
       </c>
       <c r="R194" t="n">
-        <v>7349970</v>
+        <v>7349894</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19429,11 +19434,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -19448,12 +19448,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -4663,32 +4663,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125374093</v>
+        <v>125374876</v>
       </c>
       <c r="B43" t="n">
-        <v>91493</v>
+        <v>92522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4698,13 +4698,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>809619</v>
+        <v>809605</v>
       </c>
       <c r="R43" t="n">
-        <v>7349622</v>
+        <v>7349541</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4742,50 +4742,51 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125374180</v>
+        <v>125373918</v>
       </c>
       <c r="B44" t="n">
-        <v>92714</v>
+        <v>92522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4795,13 +4796,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>809528</v>
+        <v>809764</v>
       </c>
       <c r="R44" t="n">
-        <v>7349612</v>
+        <v>7349945</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4845,44 +4846,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125373927</v>
+        <v>125373954</v>
       </c>
       <c r="B45" t="n">
-        <v>78378</v>
+        <v>92534</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>4366</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4892,13 +4893,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>809878</v>
+        <v>809809</v>
       </c>
       <c r="R45" t="n">
-        <v>7349722</v>
+        <v>7349982</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4942,44 +4943,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125374528</v>
+        <v>125373902</v>
       </c>
       <c r="B46" t="n">
-        <v>91462</v>
+        <v>56843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5260</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lateritticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Postia lateritia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Renvall</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4989,13 +4990,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>809822</v>
+        <v>809943</v>
       </c>
       <c r="R46" t="n">
-        <v>7349799</v>
+        <v>7349906</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5025,6 +5026,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5039,44 +5045,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125374003</v>
+        <v>125374093</v>
       </c>
       <c r="B47" t="n">
-        <v>79590</v>
+        <v>91493</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5089,10 +5095,10 @@
         <v>809619</v>
       </c>
       <c r="R47" t="n">
-        <v>7349838</v>
+        <v>7349622</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5136,44 +5142,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125373902</v>
+        <v>125374180</v>
       </c>
       <c r="B48" t="n">
-        <v>56843</v>
+        <v>92714</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5183,13 +5189,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>809943</v>
+        <v>809528</v>
       </c>
       <c r="R48" t="n">
-        <v>7349906</v>
+        <v>7349612</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5219,11 +5225,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5238,22 +5239,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125374083</v>
+        <v>125373927</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>78378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5261,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5285,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>809931</v>
+        <v>809878</v>
       </c>
       <c r="R49" t="n">
-        <v>7350019</v>
+        <v>7349722</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5335,44 +5336,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125374876</v>
+        <v>125374528</v>
       </c>
       <c r="B50" t="n">
-        <v>92522</v>
+        <v>91462</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5260</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lateritticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Postia lateritia</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Renvall</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5382,10 +5383,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>809605</v>
+        <v>809822</v>
       </c>
       <c r="R50" t="n">
-        <v>7349541</v>
+        <v>7349799</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5426,51 +5427,50 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125373918</v>
+        <v>125374003</v>
       </c>
       <c r="B51" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5480,13 +5480,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>809764</v>
+        <v>809619</v>
       </c>
       <c r="R51" t="n">
-        <v>7349945</v>
+        <v>7349838</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5530,44 +5530,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125373954</v>
+        <v>125374083</v>
       </c>
       <c r="B52" t="n">
-        <v>92534</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5577,13 +5577,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>809809</v>
+        <v>809931</v>
       </c>
       <c r="R52" t="n">
-        <v>7349982</v>
+        <v>7350019</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6706,10 +6706,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125374025</v>
+        <v>125376418</v>
       </c>
       <c r="B64" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6717,21 +6717,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6741,13 +6741,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>809718</v>
+        <v>809811</v>
       </c>
       <c r="R64" t="n">
-        <v>7349928</v>
+        <v>7349819</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6785,50 +6785,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125374069</v>
+        <v>125374025</v>
       </c>
       <c r="B65" t="n">
-        <v>92526</v>
+        <v>78639</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4365</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6838,13 +6839,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>809934</v>
+        <v>809718</v>
       </c>
       <c r="R65" t="n">
-        <v>7349941</v>
+        <v>7349928</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6888,44 +6889,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125373957</v>
+        <v>125374069</v>
       </c>
       <c r="B66" t="n">
-        <v>92534</v>
+        <v>92526</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6935,13 +6936,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>809729</v>
+        <v>809934</v>
       </c>
       <c r="R66" t="n">
-        <v>7349968</v>
+        <v>7349941</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6985,22 +6986,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125374899</v>
+        <v>125373957</v>
       </c>
       <c r="B67" t="n">
-        <v>92522</v>
+        <v>92534</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7008,21 +7009,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7032,13 +7033,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>809489</v>
+        <v>809729</v>
       </c>
       <c r="R67" t="n">
-        <v>7349545</v>
+        <v>7349968</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7076,51 +7077,50 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125373969</v>
+        <v>125374899</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7130,13 +7130,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>809650</v>
+        <v>809489</v>
       </c>
       <c r="R68" t="n">
-        <v>7349697</v>
+        <v>7349545</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7174,28 +7174,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125374529</v>
+        <v>125373969</v>
       </c>
       <c r="B69" t="n">
-        <v>78730</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7203,21 +7204,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7227,13 +7228,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>809607</v>
+        <v>809650</v>
       </c>
       <c r="R69" t="n">
-        <v>7349630</v>
+        <v>7349697</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7277,44 +7278,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125374062</v>
+        <v>125374529</v>
       </c>
       <c r="B70" t="n">
-        <v>91197</v>
+        <v>78730</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7324,13 +7325,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>809944</v>
+        <v>809607</v>
       </c>
       <c r="R70" t="n">
-        <v>7349866</v>
+        <v>7349630</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7374,44 +7375,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125373931</v>
+        <v>125374062</v>
       </c>
       <c r="B71" t="n">
-        <v>78378</v>
+        <v>91197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7421,10 +7422,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>809612</v>
+        <v>809944</v>
       </c>
       <c r="R71" t="n">
-        <v>7349877</v>
+        <v>7349866</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7471,22 +7472,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125374338</v>
+        <v>125373931</v>
       </c>
       <c r="B72" t="n">
-        <v>79590</v>
+        <v>78378</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7495,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7518,10 +7519,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>809607</v>
+        <v>809612</v>
       </c>
       <c r="R72" t="n">
-        <v>7349621</v>
+        <v>7349877</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7568,22 +7569,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125376418</v>
+        <v>125374338</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7591,21 +7592,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7615,10 +7616,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>809811</v>
+        <v>809607</v>
       </c>
       <c r="R73" t="n">
-        <v>7349819</v>
+        <v>7349621</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7659,51 +7660,50 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125374186</v>
+        <v>125374072</v>
       </c>
       <c r="B74" t="n">
-        <v>92522</v>
+        <v>92714</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7713,13 +7713,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>809668</v>
+        <v>809857</v>
       </c>
       <c r="R74" t="n">
-        <v>7349858</v>
+        <v>7350013</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7763,44 +7763,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anne Järvinen</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125374097</v>
+        <v>125374077</v>
       </c>
       <c r="B75" t="n">
-        <v>92522</v>
+        <v>92714</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>809532</v>
+        <v>809749</v>
       </c>
       <c r="R75" t="n">
-        <v>7349513</v>
+        <v>7349919</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7872,32 +7872,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125374102</v>
+        <v>125374024</v>
       </c>
       <c r="B76" t="n">
-        <v>92522</v>
+        <v>78639</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7907,13 +7907,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>809743</v>
+        <v>809741</v>
       </c>
       <c r="R76" t="n">
-        <v>7349889</v>
+        <v>7349907</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7957,44 +7957,44 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125374027</v>
+        <v>125376415</v>
       </c>
       <c r="B77" t="n">
-        <v>92522</v>
+        <v>92714</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8004,13 +8004,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>809720</v>
+        <v>809522</v>
       </c>
       <c r="R77" t="n">
-        <v>7349576</v>
+        <v>7349621</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8048,25 +8048,26 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125373915</v>
+        <v>125374186</v>
       </c>
       <c r="B78" t="n">
         <v>92522</v>
@@ -8101,13 +8102,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>809967</v>
+        <v>809668</v>
       </c>
       <c r="R78" t="n">
-        <v>7349981</v>
+        <v>7349858</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8151,19 +8152,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Anne Järvinen</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125374889</v>
+        <v>125374097</v>
       </c>
       <c r="B79" t="n">
         <v>92522</v>
@@ -8198,13 +8199,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>809697</v>
+        <v>809532</v>
       </c>
       <c r="R79" t="n">
-        <v>7349873</v>
+        <v>7349513</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8242,51 +8243,50 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125374856</v>
+        <v>125374102</v>
       </c>
       <c r="B80" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>809648</v>
+        <v>809743</v>
       </c>
       <c r="R80" t="n">
-        <v>7349702</v>
+        <v>7349889</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8346,44 +8346,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125374072</v>
+        <v>125374027</v>
       </c>
       <c r="B81" t="n">
-        <v>92714</v>
+        <v>92522</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8393,13 +8393,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>809857</v>
+        <v>809720</v>
       </c>
       <c r="R81" t="n">
-        <v>7350013</v>
+        <v>7349576</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8443,44 +8443,44 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125374077</v>
+        <v>125373915</v>
       </c>
       <c r="B82" t="n">
-        <v>92714</v>
+        <v>92522</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8490,10 +8490,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>809749</v>
+        <v>809967</v>
       </c>
       <c r="R82" t="n">
-        <v>7349919</v>
+        <v>7349981</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8540,44 +8540,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125374024</v>
+        <v>125374889</v>
       </c>
       <c r="B83" t="n">
-        <v>78639</v>
+        <v>92522</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8587,10 +8587,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>809741</v>
+        <v>809697</v>
       </c>
       <c r="R83" t="n">
-        <v>7349907</v>
+        <v>7349873</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8631,28 +8631,29 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125376415</v>
+        <v>125374160</v>
       </c>
       <c r="B84" t="n">
-        <v>92714</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8660,37 +8661,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>809522</v>
+        <v>809654</v>
       </c>
       <c r="R84" t="n">
-        <v>7349621</v>
+        <v>7349767</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8728,29 +8729,28 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125374160</v>
+        <v>125374007</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8758,37 +8758,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>809654</v>
+        <v>809505</v>
       </c>
       <c r="R85" t="n">
-        <v>7349767</v>
+        <v>7349593</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8832,19 +8832,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125374007</v>
+        <v>125376400</v>
       </c>
       <c r="B86" t="n">
         <v>79590</v>
@@ -8879,13 +8879,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>809505</v>
+        <v>809484</v>
       </c>
       <c r="R86" t="n">
-        <v>7349593</v>
+        <v>7349700</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8929,19 +8929,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Heike Kontermann</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125376400</v>
+        <v>125374856</v>
       </c>
       <c r="B87" t="n">
         <v>79590</v>
@@ -8976,13 +8976,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>809484</v>
+        <v>809648</v>
       </c>
       <c r="R87" t="n">
-        <v>7349700</v>
+        <v>7349702</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9026,12 +9026,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Heike Kontermann</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9232,32 +9232,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125374005</v>
+        <v>125374903</v>
       </c>
       <c r="B90" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9267,10 +9267,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>809615</v>
+        <v>809752</v>
       </c>
       <c r="R90" t="n">
-        <v>7349663</v>
+        <v>7349680</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9317,44 +9317,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125374909</v>
+        <v>125373913</v>
       </c>
       <c r="B91" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9364,13 +9364,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>809524</v>
+        <v>809798</v>
       </c>
       <c r="R91" t="n">
-        <v>7349656</v>
+        <v>7349720</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9414,44 +9414,44 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125374037</v>
+        <v>125374350</v>
       </c>
       <c r="B92" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9461,13 +9461,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>809942</v>
+        <v>809853</v>
       </c>
       <c r="R92" t="n">
-        <v>7350024</v>
+        <v>7349814</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9511,22 +9511,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125374043</v>
+        <v>125373960</v>
       </c>
       <c r="B93" t="n">
-        <v>78378</v>
+        <v>92714</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9534,21 +9534,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9558,13 +9558,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>809396</v>
+        <v>809929</v>
       </c>
       <c r="R93" t="n">
-        <v>7349580</v>
+        <v>7349900</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9608,44 +9608,44 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125373960</v>
+        <v>125374864</v>
       </c>
       <c r="B94" t="n">
-        <v>92714</v>
+        <v>91393</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9655,13 +9655,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>809929</v>
+        <v>809790</v>
       </c>
       <c r="R94" t="n">
-        <v>7349900</v>
+        <v>7349726</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9699,28 +9699,29 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125374864</v>
+        <v>125374161</v>
       </c>
       <c r="B95" t="n">
-        <v>91393</v>
+        <v>91493</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9728,37 +9729,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Röråtjärnen, Nb</t>
+          <t>Röråsen, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>809790</v>
+        <v>809457</v>
       </c>
       <c r="R95" t="n">
-        <v>7349726</v>
+        <v>7349587</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9796,67 +9797,66 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anna Öhlund</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125374161</v>
+        <v>125374005</v>
       </c>
       <c r="B96" t="n">
-        <v>91493</v>
+        <v>79590</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Röråsen, Nb</t>
+          <t>Röråtjärnen, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>809457</v>
+        <v>809615</v>
       </c>
       <c r="R96" t="n">
-        <v>7349587</v>
+        <v>7349663</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9900,44 +9900,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna Öhlund</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125374903</v>
+        <v>125374909</v>
       </c>
       <c r="B97" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9947,10 +9947,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>809752</v>
+        <v>809524</v>
       </c>
       <c r="R97" t="n">
-        <v>7349680</v>
+        <v>7349656</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10009,32 +10009,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125373913</v>
+        <v>125374037</v>
       </c>
       <c r="B98" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10044,13 +10044,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>809798</v>
+        <v>809942</v>
       </c>
       <c r="R98" t="n">
-        <v>7349720</v>
+        <v>7350024</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10094,44 +10094,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125374350</v>
+        <v>125374043</v>
       </c>
       <c r="B99" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10141,13 +10141,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>809853</v>
+        <v>809396</v>
       </c>
       <c r="R99" t="n">
-        <v>7349814</v>
+        <v>7349580</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10191,44 +10191,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125374905</v>
+        <v>125373998</v>
       </c>
       <c r="B100" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10238,10 +10238,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>809460</v>
+        <v>809955</v>
       </c>
       <c r="R100" t="n">
-        <v>7349561</v>
+        <v>7349993</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10288,44 +10288,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125374107</v>
+        <v>125374067</v>
       </c>
       <c r="B101" t="n">
-        <v>92522</v>
+        <v>92550</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10335,10 +10335,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>809651</v>
+        <v>809743</v>
       </c>
       <c r="R101" t="n">
-        <v>7349687</v>
+        <v>7349890</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10397,32 +10397,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125373922</v>
+        <v>125374857</v>
       </c>
       <c r="B102" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10432,13 +10432,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>809390</v>
+        <v>809522</v>
       </c>
       <c r="R102" t="n">
-        <v>7349574</v>
+        <v>7349656</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10482,44 +10482,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125374857</v>
+        <v>125374066</v>
       </c>
       <c r="B103" t="n">
-        <v>79590</v>
+        <v>56843</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10529,13 +10529,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>809522</v>
+        <v>809640</v>
       </c>
       <c r="R103" t="n">
-        <v>7349656</v>
+        <v>7349862</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10565,6 +10565,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10579,44 +10584,44 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125374066</v>
+        <v>125374006</v>
       </c>
       <c r="B104" t="n">
-        <v>56843</v>
+        <v>79590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10626,13 +10631,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>809640</v>
+        <v>809581</v>
       </c>
       <c r="R104" t="n">
-        <v>7349862</v>
+        <v>7349597</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10662,11 +10667,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10681,44 +10681,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125373998</v>
+        <v>125374013</v>
       </c>
       <c r="B105" t="n">
-        <v>79590</v>
+        <v>78996</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10728,10 +10728,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>809955</v>
+        <v>809808</v>
       </c>
       <c r="R105" t="n">
-        <v>7349993</v>
+        <v>7349757</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10790,32 +10790,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125374006</v>
+        <v>125374905</v>
       </c>
       <c r="B106" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10825,10 +10825,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>809581</v>
+        <v>809460</v>
       </c>
       <c r="R106" t="n">
-        <v>7349597</v>
+        <v>7349561</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10875,44 +10875,44 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125374067</v>
+        <v>125374107</v>
       </c>
       <c r="B107" t="n">
-        <v>92550</v>
+        <v>92522</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10922,10 +10922,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>809743</v>
+        <v>809651</v>
       </c>
       <c r="R107" t="n">
-        <v>7349890</v>
+        <v>7349687</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -10984,10 +10984,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125374013</v>
+        <v>125373922</v>
       </c>
       <c r="B108" t="n">
-        <v>78996</v>
+        <v>92522</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10995,21 +10995,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11019,13 +11019,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>809808</v>
+        <v>809390</v>
       </c>
       <c r="R108" t="n">
-        <v>7349757</v>
+        <v>7349574</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11069,12 +11069,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -11178,10 +11178,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125374031</v>
+        <v>125374527</v>
       </c>
       <c r="B110" t="n">
-        <v>77921</v>
+        <v>92714</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11189,21 +11189,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11213,10 +11213,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>809617</v>
+        <v>809621</v>
       </c>
       <c r="R110" t="n">
-        <v>7349830</v>
+        <v>7349643</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11263,22 +11263,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125374011</v>
+        <v>125373930</v>
       </c>
       <c r="B111" t="n">
-        <v>57648</v>
+        <v>78378</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11286,21 +11286,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11310,13 +11310,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>809693</v>
+        <v>809731</v>
       </c>
       <c r="R111" t="n">
-        <v>7349989</v>
+        <v>7349926</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11360,22 +11360,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125374527</v>
+        <v>125373933</v>
       </c>
       <c r="B112" t="n">
-        <v>92714</v>
+        <v>78378</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11383,21 +11383,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11407,13 +11407,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>809621</v>
+        <v>809589</v>
       </c>
       <c r="R112" t="n">
-        <v>7349643</v>
+        <v>7349641</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11457,44 +11457,44 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125374100</v>
+        <v>125373996</v>
       </c>
       <c r="B113" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11504,13 +11504,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>809918</v>
+        <v>809856</v>
       </c>
       <c r="R113" t="n">
-        <v>7350040</v>
+        <v>7349815</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11554,44 +11554,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125374902</v>
+        <v>125374089</v>
       </c>
       <c r="B114" t="n">
-        <v>92522</v>
+        <v>78730</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11601,13 +11601,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>809413</v>
+        <v>809956</v>
       </c>
       <c r="R114" t="n">
-        <v>7349595</v>
+        <v>7349827</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11645,51 +11645,50 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125374541</v>
+        <v>125374034</v>
       </c>
       <c r="B115" t="n">
-        <v>92522</v>
+        <v>78378</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11699,10 +11698,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>809384</v>
+        <v>809797</v>
       </c>
       <c r="R115" t="n">
-        <v>7349553</v>
+        <v>7349716</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11749,44 +11748,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125374895</v>
+        <v>125374031</v>
       </c>
       <c r="B116" t="n">
-        <v>92522</v>
+        <v>77921</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11796,10 +11795,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>809584</v>
+        <v>809617</v>
       </c>
       <c r="R116" t="n">
-        <v>7349617</v>
+        <v>7349830</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11840,51 +11839,50 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125374098</v>
+        <v>125374011</v>
       </c>
       <c r="B117" t="n">
-        <v>92522</v>
+        <v>57648</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11894,13 +11892,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>809810</v>
+        <v>809693</v>
       </c>
       <c r="R117" t="n">
-        <v>7349749</v>
+        <v>7349989</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11944,19 +11942,19 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125374540</v>
+        <v>125374100</v>
       </c>
       <c r="B118" t="n">
         <v>92522</v>
@@ -11991,13 +11989,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>809461</v>
+        <v>809918</v>
       </c>
       <c r="R118" t="n">
-        <v>7349612</v>
+        <v>7350040</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12041,19 +12039,19 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125373924</v>
+        <v>125374902</v>
       </c>
       <c r="B119" t="n">
         <v>92522</v>
@@ -12088,13 +12086,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>809702</v>
+        <v>809413</v>
       </c>
       <c r="R119" t="n">
-        <v>7349703</v>
+        <v>7349595</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12132,50 +12130,51 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125373930</v>
+        <v>125374541</v>
       </c>
       <c r="B120" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12185,13 +12184,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>809731</v>
+        <v>809384</v>
       </c>
       <c r="R120" t="n">
-        <v>7349926</v>
+        <v>7349553</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12235,44 +12234,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125373933</v>
+        <v>125374895</v>
       </c>
       <c r="B121" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12282,13 +12281,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>809589</v>
+        <v>809584</v>
       </c>
       <c r="R121" t="n">
-        <v>7349641</v>
+        <v>7349617</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12326,50 +12325,51 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125373996</v>
+        <v>125374098</v>
       </c>
       <c r="B122" t="n">
-        <v>79590</v>
+        <v>92522</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12379,13 +12379,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>809856</v>
+        <v>809810</v>
       </c>
       <c r="R122" t="n">
-        <v>7349815</v>
+        <v>7349749</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12429,44 +12429,44 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125374089</v>
+        <v>125374540</v>
       </c>
       <c r="B123" t="n">
-        <v>78730</v>
+        <v>92522</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12476,13 +12476,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>809956</v>
+        <v>809461</v>
       </c>
       <c r="R123" t="n">
-        <v>7349827</v>
+        <v>7349612</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12526,44 +12526,44 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125374034</v>
+        <v>125373924</v>
       </c>
       <c r="B124" t="n">
-        <v>78378</v>
+        <v>92522</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12573,13 +12573,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>809797</v>
+        <v>809702</v>
       </c>
       <c r="R124" t="n">
-        <v>7349716</v>
+        <v>7349703</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12623,12 +12623,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -18577,10 +18577,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>125374020</v>
+        <v>125374063</v>
       </c>
       <c r="B186" t="n">
-        <v>78972</v>
+        <v>90270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18588,21 +18588,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18612,13 +18612,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>809655</v>
+        <v>809446</v>
       </c>
       <c r="R186" t="n">
-        <v>7349698</v>
+        <v>7349560</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -18662,44 +18662,44 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>125373997</v>
+        <v>125373965</v>
       </c>
       <c r="B187" t="n">
-        <v>79590</v>
+        <v>91393</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18709,13 +18709,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>809858</v>
+        <v>809922</v>
       </c>
       <c r="R187" t="n">
-        <v>7349814</v>
+        <v>7349894</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -18759,44 +18759,44 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>125374340</v>
+        <v>125374865</v>
       </c>
       <c r="B188" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18806,13 +18806,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>809945</v>
+        <v>809649</v>
       </c>
       <c r="R188" t="n">
-        <v>7349970</v>
+        <v>7349705</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -18842,11 +18842,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -18861,22 +18856,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Hannes Weiss</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125374063</v>
+        <v>125373959</v>
       </c>
       <c r="B189" t="n">
-        <v>90270</v>
+        <v>92514</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18884,21 +18879,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18908,13 +18903,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>809446</v>
+        <v>809701</v>
       </c>
       <c r="R189" t="n">
-        <v>7349560</v>
+        <v>7349889</v>
       </c>
       <c r="S189" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -18958,44 +18953,44 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125373965</v>
+        <v>125374907</v>
       </c>
       <c r="B190" t="n">
-        <v>91393</v>
+        <v>92516</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1503</v>
+        <v>4362</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19005,13 +19000,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>809922</v>
+        <v>809807</v>
       </c>
       <c r="R190" t="n">
-        <v>7349894</v>
+        <v>7349987</v>
       </c>
       <c r="S190" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -19041,6 +19036,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -19055,44 +19055,44 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125373959</v>
+        <v>125374533</v>
       </c>
       <c r="B191" t="n">
-        <v>92514</v>
+        <v>92522</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19102,13 +19102,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>809701</v>
+        <v>809958</v>
       </c>
       <c r="R191" t="n">
-        <v>7349889</v>
+        <v>7350004</v>
       </c>
       <c r="S191" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -19152,44 +19152,44 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>125374907</v>
+        <v>125373911</v>
       </c>
       <c r="B192" t="n">
-        <v>92516</v>
+        <v>92522</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19199,13 +19199,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>809807</v>
+        <v>809707</v>
       </c>
       <c r="R192" t="n">
-        <v>7349987</v>
+        <v>7349576</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -19235,11 +19235,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2025-05-24</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Fjolårets fruktkroppar i så pass gott skick att de gick att identifiera.</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -19254,44 +19249,44 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Sara Sand</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>125374533</v>
+        <v>125374020</v>
       </c>
       <c r="B193" t="n">
-        <v>92522</v>
+        <v>78972</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19301,10 +19296,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>809958</v>
+        <v>809655</v>
       </c>
       <c r="R193" t="n">
-        <v>7350004</v>
+        <v>7349698</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -19351,44 +19346,44 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125373911</v>
+        <v>125373997</v>
       </c>
       <c r="B194" t="n">
-        <v>92522</v>
+        <v>79590</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19398,13 +19393,13 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>809707</v>
+        <v>809858</v>
       </c>
       <c r="R194" t="n">
-        <v>7349576</v>
+        <v>7349814</v>
       </c>
       <c r="S194" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -19448,44 +19443,44 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Sara Sand</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125374865</v>
+        <v>125374340</v>
       </c>
       <c r="B195" t="n">
-        <v>78731</v>
+        <v>56843</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19495,13 +19490,13 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>809649</v>
+        <v>809945</v>
       </c>
       <c r="R195" t="n">
-        <v>7349705</v>
+        <v>7349970</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -19531,6 +19526,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-05-24</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -19545,12 +19545,12 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Hannes Weiss</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>125373952</v>
       </c>
       <c r="B22" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>125373902</v>
       </c>
       <c r="B51" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>125374066</v>
       </c>
       <c r="B108" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>125374153</v>
       </c>
       <c r="B181" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>125374340</v>
       </c>
       <c r="B192" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>125373952</v>
       </c>
       <c r="B22" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>125373902</v>
       </c>
       <c r="B51" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>125374066</v>
       </c>
       <c r="B108" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>125374153</v>
       </c>
       <c r="B181" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>125374340</v>
       </c>
       <c r="B192" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>125373952</v>
       </c>
       <c r="B22" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>125373902</v>
       </c>
       <c r="B51" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>125374066</v>
       </c>
       <c r="B108" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>125374153</v>
       </c>
       <c r="B181" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>125374340</v>
       </c>
       <c r="B192" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>

--- a/artfynd/A 46993-2024 artfynd.xlsx
+++ b/artfynd/A 46993-2024 artfynd.xlsx
@@ -2622,7 +2622,7 @@
         <v>125373952</v>
       </c>
       <c r="B22" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>125373902</v>
       </c>
       <c r="B51" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>125374066</v>
       </c>
       <c r="B108" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>125374153</v>
       </c>
       <c r="B181" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>125374340</v>
       </c>
       <c r="B192" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
